--- a/database/animalia.xlsx
+++ b/database/animalia.xlsx
@@ -673,19 +673,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/7/72/Bengal_tiger_looking_at_the_camera.jpg</v>
       </c>
       <c r="AE2" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Panthera_tigris_altaica_13_-_Buffalo_Zoo.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Bengal_tiger_looking_at_the_camera.jpg</v>
       </c>
       <c r="AF2" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG2" t="str">
-        <v>https://www.youtube.com/watch?v=lONZdiuuQAs</v>
+        <v>https://www.youtube.com/watch?v=U1LhgusHlA8</v>
       </c>
       <c r="AH2" t="str">
-        <v>lONZdiuuQAs</v>
+        <v>U1LhgusHlA8</v>
       </c>
       <c r="AI2" t="str">
-        <v>Animal World 4K - Scenic Wildlife Film With Calming Music</v>
+        <v>The Sumatran Tiger - The Last of Their Kind | Free Documentary Nature</v>
       </c>
       <c r="AJ2" t="str">
         <v>4K</v>
@@ -697,7 +697,7 @@
         <v>cozymuseum-foundation | gbif | wikipedia-en | wikipedia-vi | youtube | wikimedia | inaturalist</v>
       </c>
       <c r="AM2" t="str">
-        <v>2026-08-01T15:09:45.156Z</v>
+        <v>2026-08-01T16:40:43.521Z</v>
       </c>
       <c r="AN2">
         <v>0.99</v>
@@ -745,16 +745,16 @@
         <v/>
       </c>
       <c r="BC2">
-        <v>3222</v>
+        <v>12000</v>
       </c>
       <c r="BD2">
-        <v>2184</v>
+        <v>8000</v>
       </c>
       <c r="BE2" t="str">
-        <v>Full HD</v>
+        <v>4K</v>
       </c>
       <c r="BF2" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG2" t="str">
         <v>rights-free</v>
@@ -852,22 +852,22 @@
         <v/>
       </c>
       <c r="AD3" t="str">
-        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/245572394/original.jpeg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/6/69/Canis_lupus_laying_in_grass.jpg</v>
       </c>
       <c r="AE3" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Canis_lupus_lupus_in_Alpenzoo,_Innsbruck.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Canis_lupus_laying_in_grass.jpg</v>
       </c>
       <c r="AF3" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG3" t="str">
-        <v>https://www.youtube.com/watch?v=0yH1AkW-djs</v>
+        <v>https://www.youtube.com/watch?v=4hu8FSxLfm8</v>
       </c>
       <c r="AH3" t="str">
-        <v>0yH1AkW-djs</v>
+        <v>4hu8FSxLfm8</v>
       </c>
       <c r="AI3" t="str">
-        <v>Wolves | European Wolf | Wildlife Documentary | 4K Ultra HD Video</v>
+        <v>Grey Wolf - Scientific Name Canis Lupus - Canada Wildlife in 4K, Pack of Wolves Howling at the Moon</v>
       </c>
       <c r="AJ3" t="str">
         <v>4K</v>
@@ -879,7 +879,7 @@
         <v>cozymuseum-foundation | gbif | wikipedia-en | wikipedia-vi | youtube | wikimedia | inaturalist</v>
       </c>
       <c r="AM3" t="str">
-        <v>2026-08-01T14:55:18.789Z</v>
+        <v>2026-08-01T16:40:49.682Z</v>
       </c>
       <c r="AN3">
         <v>0.99</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="BC3">
-        <v>8256</v>
+        <v>3000</v>
       </c>
       <c r="BD3">
-        <v>5504</v>
+        <v>2004</v>
       </c>
       <c r="BE3" t="str">
-        <v>4K</v>
+        <v>Full HD</v>
       </c>
       <c r="BF3" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG3" t="str">
         <v>rights-free</v>
@@ -1037,19 +1037,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/3/31/Common_Bottlenose_Dolphin_%28Tursiops_truncatus%29_Catalina_swimming_in_front_of_boat.jpg</v>
       </c>
       <c r="AE4" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Tursiops_truncatus_01-cropped.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Common_Bottlenose_Dolphin_(Tursiops_truncatus)_Catalina_swimming_in_front_of_boat.jpg</v>
       </c>
       <c r="AF4" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG4" t="str">
-        <v>https://www.youtube.com/watch?v=2j5fGbQ34qo</v>
+        <v>https://www.youtube.com/watch?v=8O0Y4LO56E4</v>
       </c>
       <c r="AH4" t="str">
-        <v>2j5fGbQ34qo</v>
+        <v>8O0Y4LO56E4</v>
       </c>
       <c r="AI4" t="str">
-        <v>Different types of Dolphins Documentary in 4K Ultra HD | Playful &amp; Intelligent Dolphins</v>
+        <v>Exploring the Secret Lives of Dolphins | 4K Nature Documentary</v>
       </c>
       <c r="AJ4" t="str">
         <v>4K</v>
@@ -1061,7 +1061,7 @@
         <v>cozymuseum-foundation | gbif | youtube | inaturalist | wikimedia</v>
       </c>
       <c r="AM4" t="str">
-        <v>2026-08-01T15:09:52.095Z</v>
+        <v>2026-08-01T16:40:53.455Z</v>
       </c>
       <c r="AN4">
         <v>0.97</v>
@@ -1109,16 +1109,16 @@
         <v/>
       </c>
       <c r="BC4">
-        <v>1200</v>
+        <v>4608</v>
       </c>
       <c r="BD4">
-        <v>800</v>
+        <v>3072</v>
       </c>
       <c r="BE4" t="str">
-        <v>HD</v>
+        <v>4K</v>
       </c>
       <c r="BF4" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG4" t="str">
         <v>rights-free</v>
@@ -1219,19 +1219,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/a/a9/2007_Snow-Hill-Island_Luyten-De-Hauwere-Emperor-Penguin-95.jpg</v>
       </c>
       <c r="AE5" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Penguin-lifecycle-ar.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:2007_Snow-Hill-Island_Luyten-De-Hauwere-Emperor-Penguin-95.jpg</v>
       </c>
       <c r="AF5" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG5" t="str">
-        <v>https://www.youtube.com/watch?v=qe-kAfESlCs</v>
+        <v>https://www.youtube.com/watch?v=uJ7AfPrfqB0</v>
       </c>
       <c r="AH5" t="str">
-        <v>qe-kAfESlCs</v>
+        <v>uJ7AfPrfqB0</v>
       </c>
       <c r="AI5" t="str">
-        <v>Penguins Surviving Antarctica🐧 | The Ultimate Survival Story | 4K Ultra HD Wildlife Documentary 2026</v>
+        <v>South Georgia - Penguin Paradise of the South Atlantic | Free Documentary Nature</v>
       </c>
       <c r="AJ5" t="str">
         <v>4K</v>
@@ -1243,7 +1243,7 @@
         <v>cozymuseum-foundation | gbif | youtube | wikimedia | inaturalist</v>
       </c>
       <c r="AM5" t="str">
-        <v>2026-08-01T15:09:54.811Z</v>
+        <v>2026-08-01T16:40:57.599Z</v>
       </c>
       <c r="AN5">
         <v>0.99</v>
@@ -1291,13 +1291,13 @@
         <v/>
       </c>
       <c r="BC5">
-        <v>1800</v>
+        <v>2442</v>
       </c>
       <c r="BD5">
-        <v>1216</v>
+        <v>1455</v>
       </c>
       <c r="BE5" t="str">
-        <v>HD</v>
+        <v>Full HD</v>
       </c>
       <c r="BF5" t="str">
         <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
@@ -1401,19 +1401,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/c/c3/False_Clownfish_1a.jpg</v>
       </c>
       <c r="AE6" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Black_storm_Clownfish_among_coral.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:False_Clownfish_1a.jpg</v>
       </c>
       <c r="AF6" t="str">
         <v>CC0</v>
       </c>
       <c r="AG6" t="str">
-        <v>https://www.youtube.com/watch?v=4OgGm5qWvNw</v>
+        <v>https://www.youtube.com/watch?v=KLp_dH-JhnU</v>
       </c>
       <c r="AH6" t="str">
-        <v>4OgGm5qWvNw</v>
+        <v>KLp_dH-JhnU</v>
       </c>
       <c r="AI6" t="str">
-        <v>🐠 Clown Fish &amp; Sea Anemone 🐠 Nature Meditation &amp; Anxiety Relief, 4K Video &amp; Relaxing Water Sounds</v>
+        <v>Clownfish: Beyond Nemo | Life in the Anemone – 4K Ocean Documentary</v>
       </c>
       <c r="AJ6" t="str">
         <v>4K</v>
@@ -1425,7 +1425,7 @@
         <v>cozymuseum-foundation | gbif | wikimedia | youtube</v>
       </c>
       <c r="AM6" t="str">
-        <v>2026-08-01T15:09:56.669Z</v>
+        <v>2026-08-01T16:41:01.023Z</v>
       </c>
       <c r="AN6">
         <v>1</v>
@@ -1473,13 +1473,13 @@
         <v/>
       </c>
       <c r="BC6">
-        <v>4032</v>
+        <v>2605</v>
       </c>
       <c r="BD6">
-        <v>3024</v>
+        <v>2398</v>
       </c>
       <c r="BE6" t="str">
-        <v>4K</v>
+        <v>Full HD</v>
       </c>
       <c r="BF6" t="str">
         <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
@@ -1580,22 +1580,22 @@
         <v/>
       </c>
       <c r="AD7" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/9/96/Albino_Great_white_shark_pup_South_Africa_3.jpg</v>
+        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/591556939/original.jpg</v>
       </c>
       <c r="AE7" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Carcharodon_carcharias_skeleton_(flipped).jpg</v>
+        <v>https://www.inaturalist.org/photos/591556939</v>
       </c>
       <c r="AF7" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG7" t="str">
-        <v>https://www.youtube.com/watch?v=028ZSYc411g</v>
+        <v>https://www.youtube.com/watch?v=tX3Z3jnHlbc</v>
       </c>
       <c r="AH7" t="str">
-        <v>028ZSYc411g</v>
+        <v>tX3Z3jnHlbc</v>
       </c>
       <c r="AI7" t="str">
-        <v>THE OCEAN’S DEADLIEST — Great White Sharks in Documentary 4K Ultra HD | Dolby Vision OLED (TV Demo)</v>
+        <v>WILD COASTAL | Orca vs Great White Shark: The Day Ocean Kings Fell (Full 4K Nature Documentary)</v>
       </c>
       <c r="AJ7" t="str">
         <v>4K</v>
@@ -1607,7 +1607,7 @@
         <v>cozymuseum-foundation | gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM7" t="str">
-        <v>2026-08-01T15:09:58.636Z</v>
+        <v>2026-08-01T16:41:06.476Z</v>
       </c>
       <c r="AN7">
         <v>0.99</v>
@@ -1655,16 +1655,16 @@
         <v/>
       </c>
       <c r="BC7">
+        <v>1600</v>
+      </c>
+      <c r="BD7">
         <v>1200</v>
-      </c>
-      <c r="BD7">
-        <v>432</v>
       </c>
       <c r="BE7" t="str">
         <v>HD</v>
       </c>
       <c r="BF7" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG7" t="str">
         <v>rights-free</v>
@@ -1762,22 +1762,22 @@
         <v/>
       </c>
       <c r="AD8" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/f/f8/Bromeliads_with_hand-painted_sign_at_Marjorie_McNeely_Conservatory.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/a/ab/Dendrobates_pumilio.jpg</v>
       </c>
       <c r="AE8" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Blue-poison.dart.frog.and.Yellow-banded.dart.frog.arp.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Dendrobates_pumilio.jpg</v>
       </c>
       <c r="AF8" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG8" t="str">
-        <v>https://www.youtube.com/watch?v=BVdYhcLbZ5M</v>
+        <v>https://www.youtube.com/watch?v=7w0QFthGh5c</v>
       </c>
       <c r="AH8" t="str">
-        <v>BVdYhcLbZ5M</v>
+        <v>7w0QFthGh5c</v>
       </c>
       <c r="AI8" t="str">
-        <v>"Poison Dart Frog in 4K | BBC Prime Wildlife Documentary"</v>
+        <v>The Incredible Parenting of Poison Dart Frogs | Rainforest Documentary 4K</v>
       </c>
       <c r="AJ8" t="str">
         <v>4K</v>
@@ -1789,7 +1789,7 @@
         <v>cozymuseum-foundation | gbif | youtube | wikimedia</v>
       </c>
       <c r="AM8" t="str">
-        <v>2026-08-01T15:10:00.548Z</v>
+        <v>2026-08-01T16:41:10.448Z</v>
       </c>
       <c r="AN8">
         <v>0.94</v>
@@ -1837,10 +1837,10 @@
         <v/>
       </c>
       <c r="BC8">
-        <v>3008</v>
+        <v>1000</v>
       </c>
       <c r="BD8">
-        <v>2000</v>
+        <v>709</v>
       </c>
       <c r="BE8" t="str">
         <v>HD</v>
@@ -1953,13 +1953,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG9" t="str">
-        <v>https://www.youtube.com/watch?v=dF1X13Oo0pg</v>
+        <v>https://www.youtube.com/watch?v=TzjP6FyXdb0</v>
       </c>
       <c r="AH9" t="str">
-        <v>dF1X13Oo0pg</v>
+        <v>TzjP6FyXdb0</v>
       </c>
       <c r="AI9" t="str">
-        <v>10 Hours of Epic 4K Wildlife Documentary: Crocodiles Buffaloes &amp; Nature’s Greatest Battles #wildlife</v>
+        <v>Bee Wild! – The Secret Life of Wild Honey Bees | Full Documentary</v>
       </c>
       <c r="AJ9" t="str">
         <v>4K</v>
@@ -1971,7 +1971,7 @@
         <v>cozymuseum-foundation | gbif | wikipedia-en | wikipedia-vi | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM9" t="str">
-        <v>2026-08-01T15:10:03.292Z</v>
+        <v>2026-08-01T16:41:14.860Z</v>
       </c>
       <c r="AN9">
         <v>0.99</v>
@@ -2135,16 +2135,16 @@
         <v>Public Domain</v>
       </c>
       <c r="AG10" t="str">
-        <v>https://www.youtube.com/watch?v=VJxre0Zc96o</v>
+        <v>https://www.youtube.com/watch?v=cN5c8uXCoMk</v>
       </c>
       <c r="AH10" t="str">
-        <v>VJxre0Zc96o</v>
+        <v>cN5c8uXCoMk</v>
       </c>
       <c r="AI10" t="str">
-        <v>4K Ultra HD Rare Praying Mantis Close Up Stunning Wildlife Documentary</v>
+        <v>Praying mantis, Scorpions, dragonfly, Insect Eaters, Nature 2018 HD Documentary.</v>
       </c>
       <c r="AJ10" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK10" t="str">
         <v>https://en.wikipedia.org/wiki/Mantis</v>
@@ -2153,7 +2153,7 @@
         <v>cozymuseum-foundation | gbif | wikipedia-en | wikipedia-vi | wikimedia | youtube</v>
       </c>
       <c r="AM10" t="str">
-        <v>2026-08-01T13:41:45.187Z</v>
+        <v>2026-08-01T16:41:19.053Z</v>
       </c>
       <c r="AN10">
         <v>0.94</v>
@@ -2308,13 +2308,13 @@
         <v/>
       </c>
       <c r="AD11" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/4/4d/Maratus_volans_1874.jpg</v>
+        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/75502676/original.jpeg</v>
       </c>
       <c r="AE11" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Maratus_volans_1874.jpg</v>
+        <v>https://www.inaturalist.org/photos/75502676</v>
       </c>
       <c r="AF11" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG11" t="str">
         <v>https://www.youtube.com/watch?v=qyTgt6NysKE</v>
@@ -2335,7 +2335,7 @@
         <v>cozymuseum-foundation | gbif | wikipedia-en | wikipedia-vi | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM11" t="str">
-        <v>2026-08-01T15:10:08.496Z</v>
+        <v>2026-08-01T16:41:22.611Z</v>
       </c>
       <c r="AN11">
         <v>0.99</v>
@@ -2383,16 +2383,16 @@
         <v/>
       </c>
       <c r="BC11">
-        <v>460</v>
+        <v>1080</v>
       </c>
       <c r="BD11">
-        <v>412</v>
+        <v>1080</v>
       </c>
       <c r="BE11" t="str">
         <v/>
       </c>
       <c r="BF11" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG11" t="str">
         <v>rights-free</v>
@@ -2490,7 +2490,7 @@
         <v/>
       </c>
       <c r="AD12" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/d/d0/Claws_of_locust_mantis_shrimp_-_Philip_Henry_Gosse_-_809_1997_27.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/3/39/OdontodactylusScyllarus2.jpg</v>
       </c>
       <c r="AE12" t="str">
         <v>https://commons.wikimedia.org/wiki/File:OdontodactylusScyllarus2.jpg</v>
@@ -2517,7 +2517,7 @@
         <v>cozymuseum-foundation | gbif | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM12" t="str">
-        <v>2026-08-01T14:37:46.002Z</v>
+        <v>2026-08-01T16:41:26.219Z</v>
       </c>
       <c r="AN12">
         <v>0.94</v>
@@ -2565,10 +2565,10 @@
         <v/>
       </c>
       <c r="BC12">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="BD12">
-        <v>2480</v>
+        <v>890</v>
       </c>
       <c r="BE12" t="str">
         <v>HD</v>
@@ -2675,19 +2675,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/5/52/Enteroctopus_dofleini_in_aquarium_rotated.jpg</v>
       </c>
       <c r="AE13" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Enteroctopus_dolfeini.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Enteroctopus_dofleini_in_aquarium_rotated.jpg</v>
       </c>
       <c r="AF13" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG13" t="str">
-        <v>https://www.youtube.com/watch?v=m5Hl4B0hLgk</v>
+        <v>https://www.youtube.com/watch?v=8bP_-eqL5Wc</v>
       </c>
       <c r="AH13" t="str">
-        <v>m5Hl4B0hLgk</v>
+        <v>8bP_-eqL5Wc</v>
       </c>
       <c r="AI13" t="str">
-        <v>Secrets Of Cephalopod: Squid, Octopus, And Cuttlefish Unveiled (4K Documentary)</v>
+        <v>Giant Pacific Octopus - The insidious monster of the Ocean [4K] WILD Earth</v>
       </c>
       <c r="AJ13" t="str">
         <v>4K</v>
@@ -2699,7 +2699,7 @@
         <v>cozymuseum-foundation | gbif | youtube | wikimedia | inaturalist</v>
       </c>
       <c r="AM13" t="str">
-        <v>2026-08-01T15:10:13.103Z</v>
+        <v>2026-08-01T16:41:29.351Z</v>
       </c>
       <c r="AN13">
         <v>0.99</v>
@@ -2747,16 +2747,16 @@
         <v/>
       </c>
       <c r="BC13">
+        <v>2560</v>
+      </c>
+      <c r="BD13">
         <v>1920</v>
-      </c>
-      <c r="BD13">
-        <v>2560</v>
       </c>
       <c r="BE13" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF13" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG13" t="str">
         <v>rights-free</v>
@@ -2854,25 +2854,25 @@
         <v/>
       </c>
       <c r="AD14" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/6/64/Artist_impression_of_hermit_crab_with_anemone.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/3/33/LA2-NSRW-3-0335.jpg</v>
       </c>
       <c r="AE14" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Nautilus_Shell,_1927,_by_Edward_Weston,_edit.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:LA2-NSRW-3-0335.jpg</v>
       </c>
       <c r="AF14" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG14" t="str">
-        <v>https://www.youtube.com/watch?v=Ceww6yLijFc</v>
+        <v>https://www.youtube.com/watch?v=wF7IJd_z7os</v>
       </c>
       <c r="AH14" t="str">
-        <v>Ceww6yLijFc</v>
+        <v>wF7IJd_z7os</v>
       </c>
       <c r="AI14" t="str">
-        <v>The Depths of the North Sea: Life in the Cold Abyss | Secrets of the Seas Ep. 1 | 4K UHD Documentary</v>
+        <v>The Dark Ocean - Paper Nautilus - Wildlife Documentary HD</v>
       </c>
       <c r="AJ14" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK14" t="str">
         <v>https://en.wikipedia.org/wiki/Nautilus</v>
@@ -2881,7 +2881,7 @@
         <v>cozymuseum-foundation | gbif | wikimedia | youtube</v>
       </c>
       <c r="AM14" t="str">
-        <v>2026-08-01T15:10:14.933Z</v>
+        <v>2026-08-01T16:41:32.732Z</v>
       </c>
       <c r="AN14">
         <v>0.94</v>
@@ -2929,10 +2929,10 @@
         <v/>
       </c>
       <c r="BC14">
-        <v>2600</v>
+        <v>1866</v>
       </c>
       <c r="BD14">
-        <v>3200</v>
+        <v>2807</v>
       </c>
       <c r="BE14" t="str">
         <v>Full HD</v>
@@ -3039,19 +3039,19 @@
         <v>https://inaturalist-open-data.s3.amazonaws.com/photos/305558239/original.jpeg</v>
       </c>
       <c r="AE15" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Aurelia-aurita-3.jpg</v>
+        <v>https://www.inaturalist.org/photos/305558239</v>
       </c>
       <c r="AF15" t="str">
         <v>CC0</v>
       </c>
       <c r="AG15" t="str">
-        <v>https://www.youtube.com/watch?v=q2EHrfU-aNU</v>
+        <v>https://www.youtube.com/watch?v=7aitfYYr3eE</v>
       </c>
       <c r="AH15" t="str">
-        <v>q2EHrfU-aNU</v>
+        <v>7aitfYYr3eE</v>
       </c>
       <c r="AI15" t="str">
-        <v>The Dance of the Little Trevally and the Jellyfish - Documentary 4K</v>
+        <v>Jellyfish rule - Nature of things</v>
       </c>
       <c r="AJ15" t="str">
         <v>4K</v>
@@ -3063,7 +3063,7 @@
         <v>cozymuseum-foundation | gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM15" t="str">
-        <v>2026-08-01T14:55:38.586Z</v>
+        <v>2026-08-01T16:41:36.525Z</v>
       </c>
       <c r="AN15">
         <v>0.99</v>
@@ -3111,16 +3111,16 @@
         <v/>
       </c>
       <c r="BC15">
-        <v>2560</v>
+        <v>2048</v>
       </c>
       <c r="BD15">
-        <v>1920</v>
+        <v>1155</v>
       </c>
       <c r="BE15" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF15" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG15" t="str">
         <v>rights-free</v>
@@ -3227,13 +3227,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG16" t="str">
-        <v>https://www.youtube.com/watch?v=2tyLK9OB7Jc</v>
+        <v>https://www.youtube.com/watch?v=nXBoOam5xJs</v>
       </c>
       <c r="AH16" t="str">
-        <v>2tyLK9OB7Jc</v>
+        <v>nXBoOam5xJs</v>
       </c>
       <c r="AI16" t="str">
-        <v>Breathtaking Ocean Wildlife In 4K | BBC Earth</v>
+        <v>The Deadly Portuguese Man O' War | 4K UHD | Blue Planet II | BBC Earth</v>
       </c>
       <c r="AJ16" t="str">
         <v>4K</v>
@@ -3245,7 +3245,7 @@
         <v>cozymuseum-foundation | gbif | youtube | inaturalist | wikimedia</v>
       </c>
       <c r="AM16" t="str">
-        <v>2026-08-01T15:10:18.914Z</v>
+        <v>2026-08-01T16:41:40.194Z</v>
       </c>
       <c r="AN16">
         <v>0.99</v>
@@ -3293,10 +3293,10 @@
         <v/>
       </c>
       <c r="BC16">
-        <v>2048</v>
+        <v>1100</v>
       </c>
       <c r="BD16">
-        <v>1536</v>
+        <v>1508</v>
       </c>
       <c r="BE16" t="str">
         <v>HD</v>
@@ -3400,7 +3400,7 @@
         <v/>
       </c>
       <c r="AD17" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/f/f8/L%C3%A9opard_des_neiges_14081.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/a/a5/Irbis4.JPG</v>
       </c>
       <c r="AE17" t="str">
         <v>https://commons.wikimedia.org/wiki/File:Irbis4.JPG</v>
@@ -3409,13 +3409,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG17" t="str">
-        <v>https://www.youtube.com/watch?v=jqzLjbP4cls</v>
+        <v>https://www.youtube.com/watch?v=oFqccD6_X_I</v>
       </c>
       <c r="AH17" t="str">
-        <v>jqzLjbP4cls</v>
+        <v>oFqccD6_X_I</v>
       </c>
       <c r="AI17" t="str">
-        <v>Big Cats Of The World 4K - Scenic Wildlife Film With Inspiring Music</v>
+        <v>Snow Leopard - The Silent Hunter (Best Wildlife Documentary)</v>
       </c>
       <c r="AJ17" t="str">
         <v>4K</v>
@@ -3427,7 +3427,7 @@
         <v>cozymuseum-foundation | gbif | wikipedia-en | wikipedia-vi | inaturalist | youtube | wikimedia</v>
       </c>
       <c r="AM17" t="str">
-        <v>2026-08-01T15:10:21.109Z</v>
+        <v>2026-08-01T16:41:44.381Z</v>
       </c>
       <c r="AN17">
         <v>0.98</v>
@@ -3475,10 +3475,10 @@
         <v/>
       </c>
       <c r="BC17">
-        <v>2048</v>
+        <v>1575</v>
       </c>
       <c r="BD17">
-        <v>1536</v>
+        <v>1181</v>
       </c>
       <c r="BE17" t="str">
         <v>HD</v>
@@ -3585,7 +3585,7 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/8/8b/Humpback_whales_in_singing_position.jpg</v>
       </c>
       <c r="AE18" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Humpback_Whale_underwater_shot.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Humpback_whales_in_singing_position.jpg</v>
       </c>
       <c r="AF18" t="str">
         <v>Public Domain</v>
@@ -3609,7 +3609,7 @@
         <v>cozymuseum-foundation | gbif | wikipedia-en | wikipedia-vi | inaturalist | youtube | wikimedia</v>
       </c>
       <c r="AM18" t="str">
-        <v>2026-08-01T15:10:23.561Z</v>
+        <v>2026-08-01T16:41:48.720Z</v>
       </c>
       <c r="AN18">
         <v>0.97</v>
@@ -3657,13 +3657,13 @@
         <v/>
       </c>
       <c r="BC18">
-        <v>2048</v>
+        <v>1736</v>
       </c>
       <c r="BD18">
-        <v>1536</v>
+        <v>1172</v>
       </c>
       <c r="BE18" t="str">
-        <v>Full HD</v>
+        <v>HD</v>
       </c>
       <c r="BF18" t="str">
         <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
@@ -3767,22 +3767,22 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/0/0a/Woolly-mammoth-100k-4096-occlusion_%28Smithsonian_Institution%29.jpg</v>
       </c>
       <c r="AE19" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Siegsdorfer_Mammut.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Woolly-mammoth-100k-4096-occlusion_(Smithsonian_Institution).jpg</v>
       </c>
       <c r="AF19" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG19" t="str">
-        <v>https://www.youtube.com/watch?v=1asF9k6lCD4</v>
+        <v>https://www.youtube.com/watch?v=9Gex_weJ8Q0</v>
       </c>
       <c r="AH19" t="str">
-        <v>1asF9k6lCD4</v>
+        <v>9Gex_weJ8Q0</v>
       </c>
       <c r="AI19" t="str">
-        <v>Woolly Mammoth: Giants of the Ice Age | Epic Prehistoric Wildlife | 4K Documentary | Dino Era 040</v>
+        <v>Mammoth – The Giant Mammal From The Past / Documentary (English/HD)</v>
       </c>
       <c r="AJ19" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK19" t="str">
         <v>https://en.wikipedia.org/wiki/Woolly_mammoth</v>
@@ -3791,7 +3791,7 @@
         <v>gbif | wikipedia | youtube | wikimedia</v>
       </c>
       <c r="AM19" t="str">
-        <v>2026-08-01T15:10:25.424Z</v>
+        <v>2026-08-01T16:41:52.447Z</v>
       </c>
       <c r="AN19">
         <v>0.99</v>
@@ -3848,7 +3848,7 @@
         <v>4K</v>
       </c>
       <c r="BF19" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG19" t="str">
         <v>rights-free</v>
@@ -3946,22 +3946,22 @@
         <v/>
       </c>
       <c r="AD20" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/f/fe/Extinctbirds1907_P24_Didus_cucullatus0329.png</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/0/08/Dodo_head_Dinkel.jpg</v>
       </c>
       <c r="AE20" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Dronte_dodo_Raphus_cucullatus.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Dodo_head_Dinkel.jpg</v>
       </c>
       <c r="AF20" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG20" t="str">
-        <v>https://www.youtube.com/watch?v=jMXtHBvAwWs</v>
+        <v>https://www.youtube.com/watch?v=FO9Lvc2Blus</v>
       </c>
       <c r="AH20" t="str">
-        <v>jMXtHBvAwWs</v>
+        <v>FO9Lvc2Blus</v>
       </c>
       <c r="AI20" t="str">
-        <v>The Last Dodo The Final Journey of an Extinct Bird 4K Wildlife Documentary</v>
+        <v>The Real Reason Why Dodo Birds Went Extinct | Dodo Bird Documentary</v>
       </c>
       <c r="AJ20" t="str">
         <v>4K</v>
@@ -3973,7 +3973,7 @@
         <v>gbif | wikipedia | youtube | wikimedia</v>
       </c>
       <c r="AM20" t="str">
-        <v>2026-08-01T15:10:27.786Z</v>
+        <v>2026-08-01T16:41:56.445Z</v>
       </c>
       <c r="AN20">
         <v>0.99</v>
@@ -4021,16 +4021,16 @@
         <v/>
       </c>
       <c r="BC20">
-        <v>2096</v>
+        <v>1727</v>
       </c>
       <c r="BD20">
-        <v>2240</v>
+        <v>2084</v>
       </c>
       <c r="BE20" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF20" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG20" t="str">
         <v>rights-free</v>
@@ -4128,22 +4128,22 @@
         <v/>
       </c>
       <c r="AD21" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/8/80/Emu_and_thylacines.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/0/05/Mammaliatheirva00figu_orig_0047.png</v>
       </c>
       <c r="AE21" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Thylacinus.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Mammaliatheirva00figu_orig_0047.png</v>
       </c>
       <c r="AF21" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG21" t="str">
-        <v>https://www.youtube.com/watch?v=J3dYjV1wqV0</v>
+        <v>https://www.youtube.com/watch?v=jYY9JHF37HI</v>
       </c>
       <c r="AH21" t="str">
-        <v>J3dYjV1wqV0</v>
+        <v>jYY9JHF37HI</v>
       </c>
       <c r="AI21" t="str">
-        <v>Tasmania Documentary 4K | Wildlife | Australia Landscapes and Nature | Original Documentary</v>
+        <v>Thylacine (Tasmanian Tiger) Documentary</v>
       </c>
       <c r="AJ21" t="str">
         <v>4K</v>
@@ -4155,7 +4155,7 @@
         <v>gbif | wikipedia | youtube | wikimedia</v>
       </c>
       <c r="AM21" t="str">
-        <v>2026-08-01T15:10:29.776Z</v>
+        <v>2026-08-01T16:42:00.004Z</v>
       </c>
       <c r="AN21">
         <v>0.99</v>
@@ -4203,13 +4203,13 @@
         <v/>
       </c>
       <c r="BC21">
-        <v>1600</v>
+        <v>2057</v>
       </c>
       <c r="BD21">
-        <v>1066</v>
+        <v>1855</v>
       </c>
       <c r="BE21" t="str">
-        <v>HD</v>
+        <v>Full HD</v>
       </c>
       <c r="BF21" t="str">
         <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
@@ -4310,22 +4310,22 @@
         <v/>
       </c>
       <c r="AD22" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/f/f8/Keulemans-GreatAuk.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/e/e1/341_Great_Auk.jpg</v>
       </c>
       <c r="AE22" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:The_great_auk,_or_garefowl_(alca_impennis,_Linn.)_(microform)_-_its_history,_archaeology,_and_remains_(IA_cihm_06624).pdf</v>
+        <v>https://commons.wikimedia.org/wiki/File:341_Great_Auk.jpg</v>
       </c>
       <c r="AF22" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG22" t="str">
-        <v>https://www.youtube.com/watch?v=rplG42457-I</v>
+        <v>https://www.youtube.com/watch?v=sIL357oO_l4</v>
       </c>
       <c r="AH22" t="str">
-        <v>rplG42457-I</v>
+        <v>sIL357oO_l4</v>
       </c>
       <c r="AI22" t="str">
-        <v>Antarctica Wildlife 4K: Penguins, Whales &amp; Ice Landscapes | Nature Sounds</v>
+        <v>Searching For A Great Auk On The Remote Faroe Islands | Extinct Or Alive?</v>
       </c>
       <c r="AJ22" t="str">
         <v>4K</v>
@@ -4337,7 +4337,7 @@
         <v>gbif | wikipedia | youtube | wikimedia</v>
       </c>
       <c r="AM22" t="str">
-        <v>2026-08-01T15:10:31.763Z</v>
+        <v>2026-08-01T16:42:03.781Z</v>
       </c>
       <c r="AN22">
         <v>0.99</v>
@@ -4385,13 +4385,13 @@
         <v/>
       </c>
       <c r="BC22">
-        <v>1112</v>
+        <v>15984</v>
       </c>
       <c r="BD22">
-        <v>1352</v>
+        <v>11104</v>
       </c>
       <c r="BE22" t="str">
-        <v>HD</v>
+        <v>4K</v>
       </c>
       <c r="BF22" t="str">
         <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
@@ -4492,22 +4492,22 @@
         <v/>
       </c>
       <c r="AD23" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/4/49/O._megalodon_reconstruction_2025.png</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/f/fb/Size_comparison_between_variously_sized_individuals_of_otodus_megalodon.png</v>
       </c>
       <c r="AE23" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Megalodon_skeletal_(2025).png</v>
+        <v>https://commons.wikimedia.org/wiki/File:Size_comparison_between_variously_sized_individuals_of_otodus_megalodon.png</v>
       </c>
       <c r="AF23" t="str">
         <v>CC0</v>
       </c>
       <c r="AG23" t="str">
-        <v>https://www.youtube.com/watch?v=vQEM57aw-3c</v>
+        <v>https://www.youtube.com/watch?v=2ACNN2Z6Uss</v>
       </c>
       <c r="AH23" t="str">
-        <v>vQEM57aw-3c</v>
+        <v>2ACNN2Z6Uss</v>
       </c>
       <c r="AI23" t="str">
-        <v>They Ate MEGALODONS For Breakfast: The LARGEST Monsters in History | 4K Documentary</v>
+        <v>How the Great White Shark Killed the Megalodon | 4K Nature Documentary</v>
       </c>
       <c r="AJ23" t="str">
         <v>4K</v>
@@ -4519,7 +4519,7 @@
         <v>gbif | wikipedia | youtube | wikimedia</v>
       </c>
       <c r="AM23" t="str">
-        <v>2026-08-01T15:10:33.672Z</v>
+        <v>2026-08-01T16:42:07.402Z</v>
       </c>
       <c r="AN23">
         <v>0.98</v>
@@ -4567,10 +4567,10 @@
         <v/>
       </c>
       <c r="BC23">
-        <v>10000</v>
+        <v>4983</v>
       </c>
       <c r="BD23">
-        <v>6016</v>
+        <v>4723</v>
       </c>
       <c r="BE23" t="str">
         <v>4K</v>
@@ -4677,19 +4677,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/7/7c/Anomalocaris_10.25.jpg</v>
       </c>
       <c r="AE24" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Anomalocaris_Mt._Stephen.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Anomalocaris_10.25.jpg</v>
       </c>
       <c r="AF24" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG24" t="str">
-        <v>https://www.youtube.com/watch?v=3cIcyg3jF2U</v>
+        <v>https://www.youtube.com/watch?v=IusDSvDjFUw</v>
       </c>
       <c r="AH24" t="str">
-        <v>3cIcyg3jF2U</v>
+        <v>IusDSvDjFUw</v>
       </c>
       <c r="AI24" t="str">
-        <v>DEEP OCEAN | Hidden Creatures in the Depths | 4K Animal Documentary</v>
+        <v>The First Apex Predator of the Cambrian Seas | Anomalocaris Documentary</v>
       </c>
       <c r="AJ24" t="str">
         <v>4K</v>
@@ -4701,7 +4701,7 @@
         <v>gbif | wikipedia | youtube | wikipedia-en | wikipedia-vi | wikimedia</v>
       </c>
       <c r="AM24" t="str">
-        <v>2026-08-01T15:10:36.077Z</v>
+        <v>2026-08-01T16:42:10.992Z</v>
       </c>
       <c r="AN24">
         <v>0.92</v>
@@ -4749,16 +4749,16 @@
         <v/>
       </c>
       <c r="BC24">
-        <v>3761</v>
+        <v>4297</v>
       </c>
       <c r="BD24">
-        <v>2292</v>
+        <v>2326</v>
       </c>
       <c r="BE24" t="str">
-        <v>Full HD</v>
+        <v>4K</v>
       </c>
       <c r="BF24" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG24" t="str">
         <v>rights-free</v>
@@ -4865,13 +4865,13 @@
         <v>CC0</v>
       </c>
       <c r="AG25" t="str">
-        <v>https://www.youtube.com/watch?v=kIP8r7kUc5c</v>
+        <v>https://www.youtube.com/watch?v=T8KiVIJkCUk</v>
       </c>
       <c r="AH25" t="str">
-        <v>kIP8r7kUc5c</v>
+        <v>T8KiVIJkCUk</v>
       </c>
       <c r="AI25" t="str">
-        <v>The Evolution of Life with David Attenborough (4K Documentary)</v>
+        <v>Volcanic Ash Froze Trilobites and Rewrote Science | Tribobite Documentary</v>
       </c>
       <c r="AJ25" t="str">
         <v>4K</v>
@@ -4883,7 +4883,7 @@
         <v>gbif | wikipedia | youtube | wikipedia-en | wikimedia</v>
       </c>
       <c r="AM25" t="str">
-        <v>2026-08-01T15:10:39.070Z</v>
+        <v>2026-08-01T16:42:14.601Z</v>
       </c>
       <c r="AN25">
         <v>0.99</v>
@@ -5041,19 +5041,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/7/73/Bolet%C3%ADn_del_Instituto_Geol%C3%B3gico_de_M%C3%A9xico_%28IA_boletndelinsti291912inst%29.pdf</v>
       </c>
       <c r="AE26" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Abhandlungen_der_Schweizerischen_Pal%C3%A4ontologischen_Gesellschaft_(IA_abhandlungenders4241unse).pdf</v>
+        <v>https://commons.wikimedia.org/wiki/File:Bolet%C3%ADn_del_Instituto_Geol%C3%B3gico_de_M%C3%A9xico_(IA_boletndelinsti291912inst).pdf</v>
       </c>
       <c r="AF26" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG26" t="str">
-        <v>https://www.youtube.com/watch?v=YcnmQdsCDiI</v>
+        <v>https://www.youtube.com/watch?v=rbgro6b1Kxg</v>
       </c>
       <c r="AH26" t="str">
-        <v>YcnmQdsCDiI</v>
+        <v>rbgro6b1Kxg</v>
       </c>
       <c r="AI26" t="str">
-        <v>How Britain's Wildlife Survives a Changing Landscape (4K Documentary)</v>
+        <v>The Only Time Spiral-Shelled Predators Ruled the Seas | Ammonite Documentary</v>
       </c>
       <c r="AJ26" t="str">
         <v>4K</v>
@@ -5065,7 +5065,7 @@
         <v>gbif | wikipedia | youtube | wikipedia-vi | wikimedia</v>
       </c>
       <c r="AM26" t="str">
-        <v>2026-08-01T15:10:40.343Z</v>
+        <v>2026-08-01T16:42:17.363Z</v>
       </c>
       <c r="AN26">
         <v>0.92</v>
@@ -5113,10 +5113,10 @@
         <v/>
       </c>
       <c r="BC26">
-        <v>1312</v>
+        <v>820</v>
       </c>
       <c r="BD26">
-        <v>1868</v>
+        <v>1302</v>
       </c>
       <c r="BE26" t="str">
         <v>HD</v>
@@ -5229,13 +5229,13 @@
         <v>CC0</v>
       </c>
       <c r="AG27" t="str">
-        <v>https://www.youtube.com/watch?v=YcnmQdsCDiI</v>
+        <v>https://www.youtube.com/watch?v=ahv-tZ2CriQ</v>
       </c>
       <c r="AH27" t="str">
-        <v>YcnmQdsCDiI</v>
+        <v>ahv-tZ2CriQ</v>
       </c>
       <c r="AI27" t="str">
-        <v>How Britain's Wildlife Survives a Changing Landscape (4K Documentary)</v>
+        <v>The Charisma of Cowries</v>
       </c>
       <c r="AJ27" t="str">
         <v>4K</v>
@@ -5247,7 +5247,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM27" t="str">
-        <v>2026-08-01T15:10:42.282Z</v>
+        <v>2026-08-01T16:42:21.507Z</v>
       </c>
       <c r="AN27">
         <v>0.99</v>
@@ -5405,19 +5405,19 @@
         <v>https://inaturalist-open-data.s3.amazonaws.com/photos/322883970/original.jpeg</v>
       </c>
       <c r="AE28" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Octopus_vulgaris_Merculiano.jpg</v>
+        <v>https://www.inaturalist.org/photos/322883970</v>
       </c>
       <c r="AF28" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG28" t="str">
-        <v>https://www.youtube.com/watch?v=dF1X13Oo0pg</v>
+        <v>https://www.youtube.com/watch?v=yYt_psQXvEM</v>
       </c>
       <c r="AH28" t="str">
-        <v>dF1X13Oo0pg</v>
+        <v>yYt_psQXvEM</v>
       </c>
       <c r="AI28" t="str">
-        <v>10 Hours of Epic 4K Wildlife Documentary: Crocodiles Buffaloes &amp; Nature’s Greatest Battles #wildlife</v>
+        <v>Crab vs Eel vs Octopus | 4K UHD | Blue Planet II | BBC Earth</v>
       </c>
       <c r="AJ28" t="str">
         <v>4K</v>
@@ -5429,7 +5429,7 @@
         <v>gbif | wikipedia-vi | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM28" t="str">
-        <v>2026-08-01T14:55:59.431Z</v>
+        <v>2026-08-01T16:42:27.358Z</v>
       </c>
       <c r="AN28">
         <v>0.98</v>
@@ -5477,16 +5477,16 @@
         <v/>
       </c>
       <c r="BC28">
-        <v>1800</v>
+        <v>2048</v>
       </c>
       <c r="BD28">
-        <v>2000</v>
+        <v>1358</v>
       </c>
       <c r="BE28" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF28" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG28" t="str">
         <v>rights-free</v>
@@ -5587,19 +5587,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/e/e6/Flower_clams.jpg</v>
       </c>
       <c r="AE29" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Ruditapes_philippinarum.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Flower_clams.jpg</v>
       </c>
       <c r="AF29" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG29" t="str">
-        <v>https://www.youtube.com/watch?v=ZEjnXYDKJfU</v>
+        <v>https://www.youtube.com/watch?v=FORTyKj4-P8</v>
       </c>
       <c r="AH29" t="str">
-        <v>ZEjnXYDKJfU</v>
+        <v>FORTyKj4-P8</v>
       </c>
       <c r="AI29" t="str">
-        <v>WONDERS OF NATURE | The Wildest Places in the Philippines | 4K Documentary</v>
+        <v>Clam Documentary | Ancient Bivalve Mollusk Life, Anatomy, Habitat, Survival, and Ocean Ecosystem</v>
       </c>
       <c r="AJ29" t="str">
         <v>4K</v>
@@ -5611,7 +5611,7 @@
         <v>gbif | wikipedia-vi | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM29" t="str">
-        <v>2026-08-01T15:10:46.553Z</v>
+        <v>2026-08-01T16:42:31.176Z</v>
       </c>
       <c r="AN29">
         <v>0.99</v>
@@ -5659,16 +5659,16 @@
         <v/>
       </c>
       <c r="BC29">
-        <v>1024</v>
+        <v>3000</v>
       </c>
       <c r="BD29">
-        <v>740</v>
+        <v>3000</v>
       </c>
       <c r="BE29" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF29" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG29" t="str">
         <v>rights-free</v>
@@ -5766,7 +5766,7 @@
         <v/>
       </c>
       <c r="AD30" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/0/03/Illustrations_of_new_species_of_exotic_butterflies_Diadema_I.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/0/0b/Sasakia_charonda_male_and_female.png</v>
       </c>
       <c r="AE30" t="str">
         <v>https://commons.wikimedia.org/wiki/File:Sasakia_charonda_male_and_female.png</v>
@@ -5775,16 +5775,16 @@
         <v>Public Domain</v>
       </c>
       <c r="AG30" t="str">
-        <v>https://www.youtube.com/watch?v=e_K-6i7ZYM0</v>
+        <v>https://www.youtube.com/watch?v=RPQimPt2HYc</v>
       </c>
       <c r="AH30" t="str">
-        <v>e_K-6i7ZYM0</v>
+        <v>RPQimPt2HYc</v>
       </c>
       <c r="AI30" t="str">
-        <v>100 Most Beautiful Butterflies in the World Stunning 4K Ultra HD Close Up Butterfly Documentary</v>
+        <v>Monarch Butterfly Migration: A Mystery Of The Natural World - HD Documentary</v>
       </c>
       <c r="AJ30" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK30" t="str">
         <v>https://www.gbif.org/species/5128519</v>
@@ -5793,7 +5793,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM30" t="str">
-        <v>2026-08-01T15:10:48.436Z</v>
+        <v>2026-08-01T16:42:34.526Z</v>
       </c>
       <c r="AN30">
         <v>0.99</v>
@@ -5951,19 +5951,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/2/21/Cricket_missing_a_hind_leg.webm</v>
       </c>
       <c r="AE31" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:True_crickets_-_Home_crickets.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Cricket_missing_a_hind_leg.webm</v>
       </c>
       <c r="AF31" t="str">
         <v>CC0</v>
       </c>
       <c r="AG31" t="str">
-        <v>https://www.youtube.com/watch?v=L6JG_L-PWMA</v>
+        <v>https://www.youtube.com/watch?v=gR4G1Hf8WeA</v>
       </c>
       <c r="AH31" t="str">
-        <v>L6JG_L-PWMA</v>
+        <v>gR4G1Hf8WeA</v>
       </c>
       <c r="AI31" t="str">
-        <v>4K Mountain Meadows - Cricket &amp; Grasshopper Sounds - Wild Flowers - Relaxing Nature Video - Ultra HD</v>
+        <v>What is about FIELD CRICKETS? | Micro-documentary</v>
       </c>
       <c r="AJ31" t="str">
         <v>4K</v>
@@ -5975,7 +5975,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM31" t="str">
-        <v>2026-08-01T15:10:50.480Z</v>
+        <v>2026-08-01T16:42:38.980Z</v>
       </c>
       <c r="AN31">
         <v>0.94</v>
@@ -6023,13 +6023,13 @@
         <v/>
       </c>
       <c r="BC31">
-        <v>2329</v>
+        <v>1280</v>
       </c>
       <c r="BD31">
-        <v>3096</v>
+        <v>720</v>
       </c>
       <c r="BE31" t="str">
-        <v>Full HD</v>
+        <v>HD</v>
       </c>
       <c r="BF31" t="str">
         <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
@@ -6139,13 +6139,13 @@
         <v>CC0</v>
       </c>
       <c r="AG32" t="str">
-        <v>https://www.youtube.com/watch?v=dF1X13Oo0pg</v>
+        <v>https://www.youtube.com/watch?v=j8UohToWGTs</v>
       </c>
       <c r="AH32" t="str">
-        <v>dF1X13Oo0pg</v>
+        <v>j8UohToWGTs</v>
       </c>
       <c r="AI32" t="str">
-        <v>10 Hours of Epic 4K Wildlife Documentary: Crocodiles Buffaloes &amp; Nature’s Greatest Battles #wildlife</v>
+        <v>Scorpion VS Centipede: A Deadly Fight | David Attenborough's Micro Monsters | Nature Bites</v>
       </c>
       <c r="AJ32" t="str">
         <v>4K</v>
@@ -6157,7 +6157,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM32" t="str">
-        <v>2026-08-01T13:44:21.815Z</v>
+        <v>2026-08-01T16:42:42.630Z</v>
       </c>
       <c r="AN32">
         <v>0.94</v>
@@ -6315,19 +6315,19 @@
         <v>https://inaturalist-open-data.s3.amazonaws.com/photos/521615676/original.jpg</v>
       </c>
       <c r="AE33" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Armadillidium_vulgare_138264167.jpg</v>
+        <v>https://www.inaturalist.org/photos/521615676</v>
       </c>
       <c r="AF33" t="str">
         <v>CC0</v>
       </c>
       <c r="AG33" t="str">
-        <v>https://www.youtube.com/watch?v=Y58UtzZNtyU</v>
+        <v>https://www.youtube.com/watch?v=g__ize11Y8Q</v>
       </c>
       <c r="AH33" t="str">
-        <v>Y58UtzZNtyU</v>
+        <v>g__ize11Y8Q</v>
       </c>
       <c r="AI33" t="str">
-        <v>The Hidden Mysteries Behind The Dinosaur-Like Insects Of Amazonia | [4K] Wildlife Documentary</v>
+        <v>AP Pillbug Documentary</v>
       </c>
       <c r="AJ33" t="str">
         <v>4K</v>
@@ -6339,7 +6339,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM33" t="str">
-        <v>2026-08-01T14:56:07.641Z</v>
+        <v>2026-08-01T16:42:47.409Z</v>
       </c>
       <c r="AN33">
         <v>0.99</v>
@@ -6390,13 +6390,13 @@
         <v>2048</v>
       </c>
       <c r="BD33">
-        <v>1536</v>
+        <v>2048</v>
       </c>
       <c r="BE33" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF33" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG33" t="str">
         <v>rights-free</v>
@@ -6497,19 +6497,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/3/36/Gfp-state-pencil-sea-urchin.jpg</v>
       </c>
       <c r="AE34" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Eucidaris_tribuloides_(USNM_E32990)_002.jpeg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Gfp-state-pencil-sea-urchin.jpg</v>
       </c>
       <c r="AF34" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG34" t="str">
-        <v>https://www.youtube.com/watch?v=kHsxd8C9_O8</v>
+        <v>https://www.youtube.com/watch?v=X7BUo7KkpuI</v>
       </c>
       <c r="AH34" t="str">
-        <v>kHsxd8C9_O8</v>
+        <v>X7BUo7KkpuI</v>
       </c>
       <c r="AI34" t="str">
-        <v>THE RED SEA | The Extraordinary Wildlife Hidden Beneath Ancient Waters | 4K Documentary</v>
+        <v>Sea Urchins: The Spine-Covered Architects of the Ocean | Full Nature Documentary</v>
       </c>
       <c r="AJ34" t="str">
         <v>4K</v>
@@ -6521,7 +6521,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM34" t="str">
-        <v>2026-08-01T15:10:57.919Z</v>
+        <v>2026-08-01T16:42:52.086Z</v>
       </c>
       <c r="AN34">
         <v>0.99</v>
@@ -6569,16 +6569,16 @@
         <v/>
       </c>
       <c r="BC34">
-        <v>3008</v>
+        <v>1272</v>
       </c>
       <c r="BD34">
-        <v>1960</v>
+        <v>1240</v>
       </c>
       <c r="BE34" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF34" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://web.archive.org/web/20230926203737/https://creativecommons.org/licenses/publicdomain/</v>
       </c>
       <c r="BG34" t="str">
         <v>rights-free</v>
@@ -6679,19 +6679,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/6/60/Portunus_trituberculatus.gif</v>
       </c>
       <c r="AE35" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Portunus_trituberculatus_-_National_Museum_of_Nature_and_Science,_Tokyo_-_DSC06892.JPG</v>
+        <v>https://commons.wikimedia.org/wiki/File:Portunus_trituberculatus.gif</v>
       </c>
       <c r="AF35" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG35" t="str">
-        <v>https://www.youtube.com/watch?v=R0dZ724GGh0</v>
+        <v>https://www.youtube.com/watch?v=5zwMANyTTFU</v>
       </c>
       <c r="AH35" t="str">
-        <v>R0dZ724GGh0</v>
+        <v>5zwMANyTTFU</v>
       </c>
       <c r="AI35" t="str">
-        <v>Australia’s Wild Northeast | Queensland Wildlife 4K Documentary</v>
+        <v>Gigantic Robber Crabs on Christmas Island | Full Documentary</v>
       </c>
       <c r="AJ35" t="str">
         <v>4K</v>
@@ -6703,7 +6703,7 @@
         <v>gbif | wikipedia-vi | wikimedia | youtube</v>
       </c>
       <c r="AM35" t="str">
-        <v>2026-08-01T15:10:59.764Z</v>
+        <v>2026-08-01T16:42:55.232Z</v>
       </c>
       <c r="AN35">
         <v>0.99</v>
@@ -6751,16 +6751,16 @@
         <v/>
       </c>
       <c r="BC35">
-        <v>3922</v>
+        <v>416</v>
       </c>
       <c r="BD35">
-        <v>2675</v>
+        <v>258</v>
       </c>
       <c r="BE35" t="str">
         <v>4K</v>
       </c>
       <c r="BF35" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG35" t="str">
         <v>rights-free</v>
@@ -6861,19 +6861,19 @@
         <v>https://inaturalist-open-data.s3.amazonaws.com/photos/408878457/original.jpeg</v>
       </c>
       <c r="AE36" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:California_sea_hare_(Aplysia_californica).jpg</v>
+        <v>https://www.inaturalist.org/photos/408878457</v>
       </c>
       <c r="AF36" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG36" t="str">
-        <v>https://www.youtube.com/watch?v=3cIcyg3jF2U</v>
+        <v>https://www.youtube.com/watch?v=JVSYLb8TcA0</v>
       </c>
       <c r="AH36" t="str">
-        <v>3cIcyg3jF2U</v>
+        <v>JVSYLb8TcA0</v>
       </c>
       <c r="AI36" t="str">
-        <v>DEEP OCEAN | Hidden Creatures in the Depths | 4K Animal Documentary</v>
+        <v>Episode 8 Blue Dragon Sea Slug: The Tiny Creature That Steals Venom to Survive @NatureSyndicate</v>
       </c>
       <c r="AJ36" t="str">
         <v>4K</v>
@@ -6885,7 +6885,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM36" t="str">
-        <v>2026-08-01T14:56:13.950Z</v>
+        <v>2026-08-01T16:42:59.027Z</v>
       </c>
       <c r="AN36">
         <v>0.99</v>
@@ -6933,16 +6933,16 @@
         <v/>
       </c>
       <c r="BC36">
+        <v>2048</v>
+      </c>
+      <c r="BD36">
         <v>1536</v>
-      </c>
-      <c r="BD36">
-        <v>2048</v>
       </c>
       <c r="BE36" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF36" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG36" t="str">
         <v>rights-free</v>
@@ -7049,13 +7049,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG37" t="str">
-        <v>https://www.youtube.com/watch?v=id3dWAlIAVo</v>
+        <v>https://www.youtube.com/watch?v=2kev31VMpAo</v>
       </c>
       <c r="AH37" t="str">
-        <v>id3dWAlIAVo</v>
+        <v>2kev31VMpAo</v>
       </c>
       <c r="AI37" t="str">
-        <v>Jewel of the Jungle: The Keel Billed Toucan in 4K Close-ups. #birds #4kvideo #documentary</v>
+        <v>Can These Tortoises Avoid Being Boiled In Their Shell? | A Perfect Planet | 4K UHD | BBC Earth</v>
       </c>
       <c r="AJ37" t="str">
         <v>4K</v>
@@ -7067,7 +7067,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM37" t="str">
-        <v>2026-08-01T13:44:42.043Z</v>
+        <v>2026-08-01T16:43:02.803Z</v>
       </c>
       <c r="AN37">
         <v>0.99</v>
@@ -7231,16 +7231,16 @@
         <v>Public Domain</v>
       </c>
       <c r="AG38" t="str">
-        <v>https://www.youtube.com/watch?v=wqMNRqVeEd4</v>
+        <v>https://www.youtube.com/watch?v=myJumAHift4</v>
       </c>
       <c r="AH38" t="str">
-        <v>wqMNRqVeEd4</v>
+        <v>myJumAHift4</v>
       </c>
       <c r="AI38" t="str">
-        <v>Miraculous Dancers of the Blue Sky: Dragonflies | 4K Animal Documentary</v>
+        <v>Flatworm on the move. Egypt HD</v>
       </c>
       <c r="AJ38" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK38" t="str">
         <v>https://www.gbif.org/species/5817919</v>
@@ -7249,7 +7249,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM38" t="str">
-        <v>2026-08-01T15:11:05.458Z</v>
+        <v>2026-08-01T16:43:06.133Z</v>
       </c>
       <c r="AN38">
         <v>0.99</v>
@@ -7413,13 +7413,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG39" t="str">
-        <v>https://www.youtube.com/watch?v=O-yyQ6t_B-U</v>
+        <v>https://www.youtube.com/watch?v=2nt4sOvAgkM</v>
       </c>
       <c r="AH39" t="str">
-        <v>O-yyQ6t_B-U</v>
+        <v>2nt4sOvAgkM</v>
       </c>
       <c r="AI39" t="str">
-        <v>Amazon Rainforest 4K Ultra HD 🌿 | Peaceful Jungle Sounds &amp; Exotic Wildlife Documentary</v>
+        <v>How Australia Harvests $10 Million in Abalone While Battling Sharks and Rocks | Fishing Documentary</v>
       </c>
       <c r="AJ39" t="str">
         <v>4K</v>
@@ -7431,7 +7431,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM39" t="str">
-        <v>2026-08-01T13:44:46.889Z</v>
+        <v>2026-08-01T16:43:09.849Z</v>
       </c>
       <c r="AN39">
         <v>0.99</v>
@@ -7595,13 +7595,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG40" t="str">
-        <v>https://www.youtube.com/watch?v=iRaLJ2wWy98</v>
+        <v>https://www.youtube.com/watch?v=ivZq_Bm3Fbg</v>
       </c>
       <c r="AH40" t="str">
-        <v>iRaLJ2wWy98</v>
+        <v>ivZq_Bm3Fbg</v>
       </c>
       <c r="AI40" t="str">
-        <v>Australia’s Wetland Wildlife in 4K: Birds, Frogs, Snakes &amp; Turtles Documentary</v>
+        <v>Wonders of Creation: Venus Flower Basket</v>
       </c>
       <c r="AJ40" t="str">
         <v>4K</v>
@@ -7613,7 +7613,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM40" t="str">
-        <v>2026-08-01T13:44:49.554Z</v>
+        <v>2026-08-01T16:43:13.021Z</v>
       </c>
       <c r="AN40">
         <v>0.99</v>
@@ -7777,13 +7777,13 @@
         <v>CC0</v>
       </c>
       <c r="AG41" t="str">
-        <v>https://www.youtube.com/watch?v=Ceww6yLijFc</v>
+        <v>https://www.youtube.com/watch?v=GzrfLPGd9uk</v>
       </c>
       <c r="AH41" t="str">
-        <v>Ceww6yLijFc</v>
+        <v>GzrfLPGd9uk</v>
       </c>
       <c r="AI41" t="str">
-        <v>The Depths of the North Sea: Life in the Cold Abyss | Secrets of the Seas Ep. 1 | 4K UHD Documentary</v>
+        <v>Invasive Royal Crab: How This Species is Taking Over Northern Seas | SLICE EARTH | FULL DOCUMENTARY</v>
       </c>
       <c r="AJ41" t="str">
         <v>4K</v>
@@ -7795,7 +7795,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM41" t="str">
-        <v>2026-08-01T15:11:11.751Z</v>
+        <v>2026-08-01T16:43:16.670Z</v>
       </c>
       <c r="AN41">
         <v>0.99</v>
@@ -7950,22 +7950,22 @@
         <v/>
       </c>
       <c r="AD42" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/b/b2/Scotoplanes.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/a/a3/Scotoplanes_globosa_and_crab_%28cropped%29.jpg</v>
       </c>
       <c r="AE42" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Scotoplanes_globosa_(USNM_E27694).jpeg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Scotoplanes_globosa_and_crab_(cropped).jpg</v>
       </c>
       <c r="AF42" t="str">
         <v>CC0</v>
       </c>
       <c r="AG42" t="str">
-        <v>https://www.youtube.com/watch?v=Ceww6yLijFc</v>
+        <v>https://www.youtube.com/watch?v=WhMzqiNQBio</v>
       </c>
       <c r="AH42" t="str">
-        <v>Ceww6yLijFc</v>
+        <v>WhMzqiNQBio</v>
       </c>
       <c r="AI42" t="str">
-        <v>The Depths of the North Sea: Life in the Cold Abyss | Secrets of the Seas Ep. 1 | 4K UHD Documentary</v>
+        <v>Sea Pigs (Scotoplanes): This Bizarre Deep-Sea Creature Cleans the Ocean Floor</v>
       </c>
       <c r="AJ42" t="str">
         <v>4K</v>
@@ -7977,7 +7977,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM42" t="str">
-        <v>2026-08-01T15:11:13.483Z</v>
+        <v>2026-08-01T16:43:20.103Z</v>
       </c>
       <c r="AN42">
         <v>0.99</v>
@@ -8025,10 +8025,10 @@
         <v>577</v>
       </c>
       <c r="BC42">
-        <v>4288</v>
+        <v>862</v>
       </c>
       <c r="BD42">
-        <v>2848</v>
+        <v>862</v>
       </c>
       <c r="BE42" t="str">
         <v>4K</v>
@@ -8141,13 +8141,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG43" t="str">
-        <v>https://www.youtube.com/watch?v=qSm93-hhZGg</v>
+        <v>https://www.youtube.com/watch?v=g4KQ49KrSRA</v>
       </c>
       <c r="AH43" t="str">
-        <v>qSm93-hhZGg</v>
+        <v>g4KQ49KrSRA</v>
       </c>
       <c r="AI43" t="str">
-        <v>Daintree Rainforest Documentary in 4K | Australia Nature | Queensland | Original Documentary</v>
+        <v>Pistol Shrimp: Nature's Tiny Superweapon | Full Wildlife Documentary (4K)</v>
       </c>
       <c r="AJ43" t="str">
         <v>4K</v>
@@ -8159,7 +8159,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM43" t="str">
-        <v>2026-08-01T13:45:00.157Z</v>
+        <v>2026-08-01T16:43:23.806Z</v>
       </c>
       <c r="AN43">
         <v>0.99</v>
@@ -8314,22 +8314,22 @@
         <v/>
       </c>
       <c r="AD44" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/b/b6/Les_bathynomes_%28Descr._of_Plate_2%29_BHL4307288.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/b/b8/Bathynomus_giganteus.webm</v>
       </c>
       <c r="AE44" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Bathynomus_giganteus_hi-res.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Bathynomus_giganteus.webm</v>
       </c>
       <c r="AF44" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG44" t="str">
-        <v>https://www.youtube.com/watch?v=ELHfyUIdQXw</v>
+        <v>https://www.youtube.com/watch?v=ulN47jhXQGA</v>
       </c>
       <c r="AH44" t="str">
-        <v>ELHfyUIdQXw</v>
+        <v>ulN47jhXQGA</v>
       </c>
       <c r="AI44" t="str">
-        <v>Giant Pacific Octopus: The Ultimate Deep Sea Survivor | 4K UHD Documentary</v>
+        <v>Giant Isopod - The Alien-Looking Creature | AmazingNature</v>
       </c>
       <c r="AJ44" t="str">
         <v>4K</v>
@@ -8341,7 +8341,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM44" t="str">
-        <v>2026-08-01T15:11:17.296Z</v>
+        <v>2026-08-01T16:43:27.455Z</v>
       </c>
       <c r="AN44">
         <v>0.99</v>
@@ -8389,13 +8389,13 @@
         <v>607</v>
       </c>
       <c r="BC44">
-        <v>1920</v>
+        <v>1280</v>
       </c>
       <c r="BD44">
-        <v>1080</v>
+        <v>720</v>
       </c>
       <c r="BE44" t="str">
-        <v>Full HD</v>
+        <v>HD</v>
       </c>
       <c r="BF44" t="str">
         <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
@@ -8505,13 +8505,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG45" t="str">
-        <v>https://www.youtube.com/watch?v=a7_1JRznZl8</v>
+        <v>https://www.youtube.com/watch?v=VNbWxKN0u0g</v>
       </c>
       <c r="AH45" t="str">
-        <v>a7_1JRznZl8</v>
+        <v>VNbWxKN0u0g</v>
       </c>
       <c r="AI45" t="str">
-        <v>4k Ocean Giants - The Fascinating World of Huge Clams</v>
+        <v>Gian clam (Tridacna gigas) in 4K</v>
       </c>
       <c r="AJ45" t="str">
         <v>4K</v>
@@ -8523,7 +8523,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM45" t="str">
-        <v>2026-08-01T15:11:19.472Z</v>
+        <v>2026-08-01T16:43:31.328Z</v>
       </c>
       <c r="AN45">
         <v>0.99</v>
@@ -8687,13 +8687,13 @@
         <v>CC0</v>
       </c>
       <c r="AG46" t="str">
-        <v>https://www.youtube.com/watch?v=Ceww6yLijFc</v>
+        <v>https://www.youtube.com/watch?v=uyRAHhDgSHk</v>
       </c>
       <c r="AH46" t="str">
-        <v>Ceww6yLijFc</v>
+        <v>uyRAHhDgSHk</v>
       </c>
       <c r="AI46" t="str">
-        <v>The Depths of the North Sea: Life in the Cold Abyss | Secrets of the Seas Ep. 1 | 4K UHD Documentary</v>
+        <v>A Pineapple Republic: A History of Pineapple in Hawaii (Full Documentary)</v>
       </c>
       <c r="AJ46" t="str">
         <v>4K</v>
@@ -8705,7 +8705,7 @@
         <v>gbif | wikipedia-vi | wikimedia | youtube</v>
       </c>
       <c r="AM46" t="str">
-        <v>2026-08-01T13:45:06.291Z</v>
+        <v>2026-08-01T16:43:34.273Z</v>
       </c>
       <c r="AN46">
         <v>0.99</v>
@@ -8863,19 +8863,19 @@
         <v>https://inaturalist-open-data.s3.amazonaws.com/photos/108691934/original.jpeg</v>
       </c>
       <c r="AE47" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Paracanthurus_hepatus_244215093.jpg</v>
+        <v>https://www.inaturalist.org/photos/108691934</v>
       </c>
       <c r="AF47" t="str">
         <v>CC0</v>
       </c>
       <c r="AG47" t="str">
-        <v>https://www.youtube.com/watch?v=Ceww6yLijFc</v>
+        <v>https://www.youtube.com/watch?v=T3rqE6pep1s</v>
       </c>
       <c r="AH47" t="str">
-        <v>Ceww6yLijFc</v>
+        <v>T3rqE6pep1s</v>
       </c>
       <c r="AI47" t="str">
-        <v>The Depths of the North Sea: Life in the Cold Abyss | Secrets of the Seas Ep. 1 | 4K UHD Documentary</v>
+        <v>Blue Tang – Jewel of the Coral Reefs | Relaxing 4K Ocean Documentary with Music#AnimalHQ #Wildlife</v>
       </c>
       <c r="AJ47" t="str">
         <v>4K</v>
@@ -8887,7 +8887,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM47" t="str">
-        <v>2026-08-01T14:56:33.243Z</v>
+        <v>2026-08-01T16:43:38.503Z</v>
       </c>
       <c r="AN47">
         <v>0.99</v>
@@ -8935,16 +8935,16 @@
         <v>644</v>
       </c>
       <c r="BC47">
-        <v>1292</v>
+        <v>2048</v>
       </c>
       <c r="BD47">
-        <v>1025</v>
+        <v>1536</v>
       </c>
       <c r="BE47" t="str">
-        <v>HD</v>
+        <v>Full HD</v>
       </c>
       <c r="BF47" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG47" t="str">
         <v>rights-free</v>
@@ -9051,13 +9051,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG48" t="str">
-        <v>https://www.youtube.com/watch?v=SnBWOe13QlQ</v>
+        <v>https://www.youtube.com/watch?v=Tyi5S76cZ-s</v>
       </c>
       <c r="AH48" t="str">
-        <v>SnBWOe13QlQ</v>
+        <v>Tyi5S76cZ-s</v>
       </c>
       <c r="AI48" t="str">
-        <v>Creatures Of The Deep: Coral Reefs and Marine Wildlife (4K Documentary)</v>
+        <v>Amazing Clownfish Teamwork | 4K UHD | Blue Planet II | BBC Earth</v>
       </c>
       <c r="AJ48" t="str">
         <v>4K</v>
@@ -9069,7 +9069,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube</v>
       </c>
       <c r="AM48" t="str">
-        <v>2026-08-01T13:45:13.281Z</v>
+        <v>2026-08-01T16:43:41.566Z</v>
       </c>
       <c r="AN48">
         <v>0.99</v>
@@ -9227,19 +9227,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/c/c5/AtlanticGoliathGrouper.jpg</v>
       </c>
       <c r="AE49" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Epinephelus_itajara_-_Museu_da_Ci%C3%AAncia_da_Universidade_de_Coimbra_-_University_of_Coimbra_-_Coimbra,_Portugal_-_DSC09236.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:AtlanticGoliathGrouper.jpg</v>
       </c>
       <c r="AF49" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG49" t="str">
-        <v>https://www.youtube.com/watch?v=LkZl4HcVVB8</v>
+        <v>https://www.youtube.com/watch?v=Qmzmbu9468U</v>
       </c>
       <c r="AH49" t="str">
-        <v>LkZl4HcVVB8</v>
+        <v>Qmzmbu9468U</v>
       </c>
       <c r="AI49" t="str">
-        <v>Jungle Animals in 4K UHD 🌿 | Amazing Wildlife Discovery | 60FPS Ultra HD Nature Documentary</v>
+        <v>ATLANTIC GOLIATH GROUPER &amp; the Sonic Boom (Epinephelus itajara) (#19)</v>
       </c>
       <c r="AJ49" t="str">
         <v>4K</v>
@@ -9251,7 +9251,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM49" t="str">
-        <v>2026-08-01T15:11:26.692Z</v>
+        <v>2026-08-01T16:43:44.567Z</v>
       </c>
       <c r="AN49">
         <v>0.99</v>
@@ -9299,16 +9299,16 @@
         <v>710</v>
       </c>
       <c r="BC49">
-        <v>5037</v>
+        <v>1285</v>
       </c>
       <c r="BD49">
-        <v>2937</v>
+        <v>884</v>
       </c>
       <c r="BE49" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="BF49" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG49" t="str">
         <v>rights-free</v>
@@ -9406,22 +9406,22 @@
         <v/>
       </c>
       <c r="AD50" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/e/ec/FMIB_41032_Decapterus_canonoides_Jenkins%2C_new_species_Type.jpeg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/2/28/Reef2354_-_Flickr_-_NOAA_Photo_Library.jpg</v>
       </c>
       <c r="AE50" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:FMIB_41032_Decapterus_canonoides_Jenkins,_new_species_Type.jpeg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Reef2354_-_Flickr_-_NOAA_Photo_Library.jpg</v>
       </c>
       <c r="AF50" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG50" t="str">
-        <v>https://www.youtube.com/watch?v=WI4yGLk1_F8</v>
+        <v>https://www.youtube.com/watch?v=cMcgtp8L7ys</v>
       </c>
       <c r="AH50" t="str">
-        <v>WI4yGLk1_F8</v>
+        <v>cMcgtp8L7ys</v>
       </c>
       <c r="AI50" t="str">
-        <v>Ocean Wildlife | The Hidden Kingdoms of Marine Life Revealed | 4K Documentary</v>
+        <v>Round Scad (Galunggong) Documentary | Abigail Dumanat</v>
       </c>
       <c r="AJ50" t="str">
         <v>4K</v>
@@ -9433,7 +9433,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM50" t="str">
-        <v>2026-08-01T15:11:29.008Z</v>
+        <v>2026-08-01T16:43:48.466Z</v>
       </c>
       <c r="AN50">
         <v>0.99</v>
@@ -9481,10 +9481,10 @@
         <v>728</v>
       </c>
       <c r="BC50">
-        <v>1657</v>
+        <v>3072</v>
       </c>
       <c r="BD50">
-        <v>719</v>
+        <v>2304</v>
       </c>
       <c r="BE50" t="str">
         <v>Full HD</v>
@@ -9591,19 +9591,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/4/4d/Fish4443_-_Flickr_-_NOAA_Photo_Library.jpg</v>
       </c>
       <c r="AE51" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:NOAA_diver_bigeye_scad_school_Saipan_2022.png</v>
+        <v>https://commons.wikimedia.org/wiki/File:Fish4443_-_Flickr_-_NOAA_Photo_Library.jpg</v>
       </c>
       <c r="AF51" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG51" t="str">
-        <v>https://www.youtube.com/watch?v=YcnmQdsCDiI</v>
+        <v>https://www.youtube.com/watch?v=0UW498zDm1E</v>
       </c>
       <c r="AH51" t="str">
-        <v>YcnmQdsCDiI</v>
+        <v>0UW498zDm1E</v>
       </c>
       <c r="AI51" t="str">
-        <v>How Britain's Wildlife Survives a Changing Landscape (4K Documentary)</v>
+        <v>Mesmerizing Schooling Bigeye Scad in Gorontalo | Scuba Diving Video</v>
       </c>
       <c r="AJ51" t="str">
         <v>4K</v>
@@ -9615,7 +9615,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM51" t="str">
-        <v>2026-08-01T15:11:30.900Z</v>
+        <v>2026-08-01T16:43:52.159Z</v>
       </c>
       <c r="AN51">
         <v>0.99</v>
@@ -9663,10 +9663,10 @@
         <v>746</v>
       </c>
       <c r="BC51">
-        <v>1213</v>
+        <v>2896</v>
       </c>
       <c r="BD51">
-        <v>814</v>
+        <v>1944</v>
       </c>
       <c r="BE51" t="str">
         <v>Full HD</v>
@@ -9779,13 +9779,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG52" t="str">
-        <v>https://www.youtube.com/watch?v=J3dYjV1wqV0</v>
+        <v>https://www.youtube.com/watch?v=q2EHrfU-aNU</v>
       </c>
       <c r="AH52" t="str">
-        <v>J3dYjV1wqV0</v>
+        <v>q2EHrfU-aNU</v>
       </c>
       <c r="AI52" t="str">
-        <v>Tasmania Documentary 4K | Wildlife | Australia Landscapes and Nature | Original Documentary</v>
+        <v>The Dance of the Little Trevally and the Jellyfish - Documentary 4K</v>
       </c>
       <c r="AJ52" t="str">
         <v>4K</v>
@@ -9797,7 +9797,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM52" t="str">
-        <v>2026-08-01T15:11:32.605Z</v>
+        <v>2026-08-01T16:43:56.045Z</v>
       </c>
       <c r="AN52">
         <v>0.99</v>
@@ -9961,13 +9961,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG53" t="str">
-        <v>https://www.youtube.com/watch?v=94weodD4TMo</v>
+        <v>https://www.youtube.com/watch?v=hGo1W0G3-1U</v>
       </c>
       <c r="AH53" t="str">
-        <v>94weodD4TMo</v>
+        <v>hGo1W0G3-1U</v>
       </c>
       <c r="AI53" t="str">
-        <v>Fish – The Hidden Civilization Underwater | 4K Wildlife Documentary</v>
+        <v>Northern Anchovy schooling long take Engraulis mordax 4K stock footage</v>
       </c>
       <c r="AJ53" t="str">
         <v>4K</v>
@@ -9979,7 +9979,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM53" t="str">
-        <v>2026-08-01T15:11:35.025Z</v>
+        <v>2026-08-01T16:43:59.521Z</v>
       </c>
       <c r="AN53">
         <v>0.99</v>
@@ -10143,13 +10143,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG54" t="str">
-        <v>https://www.youtube.com/watch?v=mTE1cJWOClQ</v>
+        <v>https://www.youtube.com/watch?v=qTOTkYAmgfI</v>
       </c>
       <c r="AH54" t="str">
-        <v>mTE1cJWOClQ</v>
+        <v>qTOTkYAmgfI</v>
       </c>
       <c r="AI54" t="str">
-        <v>FLYING OVER ELAFONISI (4K UHD) – Soothing Music Along With Beautiful Nature Video -4K Video ULTRA HD</v>
+        <v>10/25/18 Barred Knife Jaw (Oplegnathus Fasciatus) at Breakwater wall</v>
       </c>
       <c r="AJ54" t="str">
         <v>4K</v>
@@ -10161,7 +10161,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube</v>
       </c>
       <c r="AM54" t="str">
-        <v>2026-08-01T13:45:55.171Z</v>
+        <v>2026-08-01T16:44:02.686Z</v>
       </c>
       <c r="AN54">
         <v>0.99</v>
@@ -10316,22 +10316,22 @@
         <v/>
       </c>
       <c r="AD55" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/7/75/Blue_Marlin_Statue_Pangandaran.png</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/d/da/OJ_L_202302167_of_2023_-_ES_Spanish.pdf</v>
       </c>
       <c r="AE55" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Atlantic_blue_marlin.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:OJ_L_202302167_of_2023_-_ES_Spanish.pdf</v>
       </c>
       <c r="AF55" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG55" t="str">
-        <v>https://www.youtube.com/watch?v=dF1X13Oo0pg</v>
+        <v>https://www.youtube.com/watch?v=a7gwM3K19DA</v>
       </c>
       <c r="AH55" t="str">
-        <v>dF1X13Oo0pg</v>
+        <v>a7gwM3K19DA</v>
       </c>
       <c r="AI55" t="str">
-        <v>10 Hours of Epic 4K Wildlife Documentary: Crocodiles Buffaloes &amp; Nature’s Greatest Battles #wildlife</v>
+        <v>Marlin facts: also swordfish facts | Animal Fact Files</v>
       </c>
       <c r="AJ55" t="str">
         <v>4K</v>
@@ -10343,7 +10343,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM55" t="str">
-        <v>2026-08-01T15:11:39.168Z</v>
+        <v>2026-08-01T16:44:06.281Z</v>
       </c>
       <c r="AN55">
         <v>0.97</v>
@@ -10391,13 +10391,13 @@
         <v>794</v>
       </c>
       <c r="BC55">
-        <v>4608</v>
+        <v>1239</v>
       </c>
       <c r="BD55">
-        <v>3357</v>
+        <v>1752</v>
       </c>
       <c r="BE55" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="BF55" t="str">
         <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
@@ -10498,22 +10498,22 @@
         <v/>
       </c>
       <c r="AD56" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/7/7b/Xiphias_velifer_-_1700-1880_-_Print_-_Iconographia_Zoologica_-_Special_Collections_University_of_Amsterdam_-_UBA01_IZ13600013.tif</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/5/5b/Histiophorus_immaculatus_TZSL.jpg</v>
       </c>
       <c r="AE56" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Istiophorus_platypterus_juveniles.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Histiophorus_immaculatus_TZSL.jpg</v>
       </c>
       <c r="AF56" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG56" t="str">
-        <v>https://www.youtube.com/watch?v=GFvp4Hdalwg</v>
+        <v>https://www.youtube.com/watch?v=zB4sQgFyp4Q</v>
       </c>
       <c r="AH56" t="str">
-        <v>GFvp4Hdalwg</v>
+        <v>zB4sQgFyp4Q</v>
       </c>
       <c r="AI56" t="str">
-        <v>The Great Ocean Migration 4K | Epic Survival Journeys of Marine Animals – Documentary</v>
+        <v>How Fishermen Catch 1000 Pound Giant Sailfish – A Documentary About Deep-sea Fishing</v>
       </c>
       <c r="AJ56" t="str">
         <v>4K</v>
@@ -10525,7 +10525,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM56" t="str">
-        <v>2026-08-01T15:11:41.039Z</v>
+        <v>2026-08-01T16:44:09.689Z</v>
       </c>
       <c r="AN56">
         <v>0.99</v>
@@ -10573,10 +10573,10 @@
         <v>800</v>
       </c>
       <c r="BC56">
-        <v>3264</v>
+        <v>2927</v>
       </c>
       <c r="BD56">
-        <v>2448</v>
+        <v>2185</v>
       </c>
       <c r="BE56" t="str">
         <v>Full HD</v>
@@ -10683,19 +10683,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/7/79/Lutjanus_campechanus.jpg</v>
       </c>
       <c r="AE57" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Lutjanus_campechanus_range.png</v>
+        <v>https://commons.wikimedia.org/wiki/File:Lutjanus_campechanus.jpg</v>
       </c>
       <c r="AF57" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG57" t="str">
-        <v>https://www.youtube.com/watch?v=dF1X13Oo0pg</v>
+        <v>https://www.youtube.com/watch?v=70sUFFp0x2w</v>
       </c>
       <c r="AH57" t="str">
-        <v>dF1X13Oo0pg</v>
+        <v>70sUFFp0x2w</v>
       </c>
       <c r="AI57" t="str">
-        <v>10 Hours of Epic 4K Wildlife Documentary: Crocodiles Buffaloes &amp; Nature’s Greatest Battles #wildlife</v>
+        <v>Red Snapper and Big Eye Trevally schools, Peleliu, Palau. Underwater wildlife 4K stock footage.</v>
       </c>
       <c r="AJ57" t="str">
         <v>4K</v>
@@ -10707,7 +10707,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM57" t="str">
-        <v>2026-08-01T15:11:43.015Z</v>
+        <v>2026-08-01T16:44:13.330Z</v>
       </c>
       <c r="AN57">
         <v>0.99</v>
@@ -10755,10 +10755,10 @@
         <v>806</v>
       </c>
       <c r="BC57">
-        <v>1020</v>
+        <v>2304</v>
       </c>
       <c r="BD57">
-        <v>675</v>
+        <v>1536</v>
       </c>
       <c r="BE57" t="str">
         <v>Full HD</v>
@@ -10871,13 +10871,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG58" t="str">
-        <v>https://www.youtube.com/watch?v=UQnnd_NmuXk</v>
+        <v>https://www.youtube.com/watch?v=ANuSafFJAT4</v>
       </c>
       <c r="AH58" t="str">
-        <v>UQnnd_NmuXk</v>
+        <v>ANuSafFJAT4</v>
       </c>
       <c r="AI58" t="str">
-        <v>Underwater World 4K 60FPS | Ultra HD Documentary on Colorful Marine Life</v>
+        <v>Lyretail anthias (Pseudanthias squamipinnis) sea goldie in 4K</v>
       </c>
       <c r="AJ58" t="str">
         <v>4K</v>
@@ -10889,7 +10889,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM58" t="str">
-        <v>2026-08-01T15:11:44.788Z</v>
+        <v>2026-08-01T16:44:16.817Z</v>
       </c>
       <c r="AN58">
         <v>0.99</v>
@@ -11047,19 +11047,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/e/e6/Adriaen_Coenen%27s_Visboeck_-_KB_78_E_54_-_folio_136v.jpg</v>
       </c>
       <c r="AE59" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Limanda_limanda_(Pleuronectes_limanda)_-_Swedish_Museum_of_Natural_History_-_Stockholm,_Sweden_-_DSC00589.JPG</v>
+        <v>https://commons.wikimedia.org/wiki/File:Adriaen_Coenen%27s_Visboeck_-_KB_78_E_54_-_folio_136v.jpg</v>
       </c>
       <c r="AF59" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG59" t="str">
-        <v>https://www.youtube.com/watch?v=mMIn_b-n6OQ</v>
+        <v>https://www.youtube.com/watch?v=botARn8rWBs</v>
       </c>
       <c r="AH59" t="str">
-        <v>mMIn_b-n6OQ</v>
+        <v>botARn8rWBs</v>
       </c>
       <c r="AI59" t="str">
-        <v>From Dry Savannahs to Wide River Landscapes | 4K UHD Documentary</v>
+        <v>Fish, Dab, Limanda limanda, camouflage, disruptive pattern, sand, rock pool life, Filey Brigg</v>
       </c>
       <c r="AJ59" t="str">
         <v>4K</v>
@@ -11071,7 +11071,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM59" t="str">
-        <v>2026-08-01T15:11:47.600Z</v>
+        <v>2026-08-01T16:44:21.850Z</v>
       </c>
       <c r="AN59">
         <v>0.99</v>
@@ -11119,16 +11119,16 @@
         <v>878</v>
       </c>
       <c r="BC59">
-        <v>5472</v>
+        <v>3335</v>
       </c>
       <c r="BD59">
-        <v>3648</v>
+        <v>4911</v>
       </c>
       <c r="BE59" t="str">
         <v>4K</v>
       </c>
       <c r="BF59" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG59" t="str">
         <v>rights-free</v>
@@ -11226,25 +11226,25 @@
         <v/>
       </c>
       <c r="AD60" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/3/36/%E5%9C%9F%E9%AD%A0%E9%AD%9A2.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/b/b7/Prise_%C3%A0_la_r%C3%A9union.jpg</v>
       </c>
       <c r="AE60" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Scomberomorus_commerson_(USNM-403390).jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Prise_%C3%A0_la_r%C3%A9union.jpg</v>
       </c>
       <c r="AF60" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG60" t="str">
-        <v>https://www.youtube.com/watch?v=ZlsK9ZmaC08</v>
+        <v>https://www.youtube.com/watch?v=OwJ7bqSLsA0</v>
       </c>
       <c r="AH60" t="str">
-        <v>ZlsK9ZmaC08</v>
+        <v>OwJ7bqSLsA0</v>
       </c>
       <c r="AI60" t="str">
-        <v>Borneo's Secret Kingdom: King of the Swamp #animals #borneo #wildlife #4k</v>
+        <v>Spanish Mackerel Fish Fillet by Kinife Cutting Skills | CINEMATIC FILM LOOK FULL HD ASMR</v>
       </c>
       <c r="AJ60" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK60" t="str">
         <v>https://www.gbif.org/species/2374255</v>
@@ -11253,7 +11253,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM60" t="str">
-        <v>2026-08-01T15:11:49.478Z</v>
+        <v>2026-08-01T16:44:28.408Z</v>
       </c>
       <c r="AN60">
         <v>0.99</v>
@@ -11301,10 +11301,10 @@
         <v>890</v>
       </c>
       <c r="BC60">
-        <v>4281</v>
+        <v>1600</v>
       </c>
       <c r="BD60">
-        <v>1557</v>
+        <v>2400</v>
       </c>
       <c r="BE60" t="str">
         <v>Full HD</v>
@@ -11408,22 +11408,22 @@
         <v/>
       </c>
       <c r="AD61" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/1/12/Auxis_rochei_-_1700-1880_-_Print_-_Iconographia_Zoologica_-_Special_Collections_University_of_Amsterdam_-_UBA01_IZ13500222.tif</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/9/9b/FMIB_46151_Plain_Bonito.jpeg</v>
       </c>
       <c r="AE61" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Auxis_rochei_(USNM-424772).jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:FMIB_46151_Plain_Bonito.jpeg</v>
       </c>
       <c r="AF61" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG61" t="str">
-        <v>https://www.youtube.com/watch?v=dF1X13Oo0pg</v>
+        <v>https://www.youtube.com/watch?v=x9eReaWALCU</v>
       </c>
       <c r="AH61" t="str">
-        <v>dF1X13Oo0pg</v>
+        <v>x9eReaWALCU</v>
       </c>
       <c r="AI61" t="str">
-        <v>10 Hours of Epic 4K Wildlife Documentary: Crocodiles Buffaloes &amp; Nature’s Greatest Battles #wildlife</v>
+        <v>The fascinating migration of tuna | Full Documentary</v>
       </c>
       <c r="AJ61" t="str">
         <v>4K</v>
@@ -11435,7 +11435,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM61" t="str">
-        <v>2026-08-01T15:11:53.798Z</v>
+        <v>2026-08-01T16:44:32.051Z</v>
       </c>
       <c r="AN61">
         <v>0.99</v>
@@ -11483,10 +11483,10 @@
         <v>902</v>
       </c>
       <c r="BC61">
-        <v>4288</v>
+        <v>1422</v>
       </c>
       <c r="BD61">
-        <v>1493</v>
+        <v>685</v>
       </c>
       <c r="BE61" t="str">
         <v>Full HD</v>
@@ -11590,7 +11590,7 @@
         <v/>
       </c>
       <c r="AD62" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/c/cb/Katsuwonus_pelamis_192965870.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/3/30/Katsuwonus_pelamis_Kagoshima.jpg</v>
       </c>
       <c r="AE62" t="str">
         <v>https://commons.wikimedia.org/wiki/File:Katsuwonus_pelamis_Kagoshima.jpg</v>
@@ -11599,13 +11599,13 @@
         <v>CC0</v>
       </c>
       <c r="AG62" t="str">
-        <v>https://www.youtube.com/watch?v=Ceww6yLijFc</v>
+        <v>https://www.youtube.com/watch?v=1FglVJjL1Lk</v>
       </c>
       <c r="AH62" t="str">
-        <v>Ceww6yLijFc</v>
+        <v>1FglVJjL1Lk</v>
       </c>
       <c r="AI62" t="str">
-        <v>The Depths of the North Sea: Life in the Cold Abyss | Secrets of the Seas Ep. 1 | 4K UHD Documentary</v>
+        <v>How 72 Hours of Bluefin Tuna Fishing Can Lead to a $2 Million Payoff | Fishing Documentary</v>
       </c>
       <c r="AJ62" t="str">
         <v>4K</v>
@@ -11617,7 +11617,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM62" t="str">
-        <v>2026-08-01T15:11:55.840Z</v>
+        <v>2026-08-01T16:44:35.677Z</v>
       </c>
       <c r="AN62">
         <v>0.99</v>
@@ -11781,13 +11781,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG63" t="str">
-        <v>https://www.youtube.com/watch?v=LkZl4HcVVB8</v>
+        <v>https://www.youtube.com/watch?v=x9eReaWALCU</v>
       </c>
       <c r="AH63" t="str">
-        <v>LkZl4HcVVB8</v>
+        <v>x9eReaWALCU</v>
       </c>
       <c r="AI63" t="str">
-        <v>Jungle Animals in 4K UHD 🌿 | Amazing Wildlife Discovery | 60FPS Ultra HD Nature Documentary</v>
+        <v>The fascinating migration of tuna | Full Documentary</v>
       </c>
       <c r="AJ63" t="str">
         <v>4K</v>
@@ -11799,7 +11799,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM63" t="str">
-        <v>2026-08-01T15:11:58.062Z</v>
+        <v>2026-08-01T16:44:39.398Z</v>
       </c>
       <c r="AN63">
         <v>0.99</v>
@@ -11957,7 +11957,7 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/8/87/Der_naturen_bloeme_-_Jacob_van_Maerlant_-_KB_KA_16_-_110r.jpg</v>
       </c>
       <c r="AE64" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Bluefin-big.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Der_naturen_bloeme_-_Jacob_van_Maerlant_-_KB_KA_16_-_110r.jpg</v>
       </c>
       <c r="AF64" t="str">
         <v>Public Domain</v>
@@ -11981,7 +11981,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM64" t="str">
-        <v>2026-08-01T15:12:00.685Z</v>
+        <v>2026-08-01T16:44:43.013Z</v>
       </c>
       <c r="AN64">
         <v>0.99</v>
@@ -12029,13 +12029,13 @@
         <v>920</v>
       </c>
       <c r="BC64">
-        <v>1728</v>
+        <v>2029</v>
       </c>
       <c r="BD64">
-        <v>1140</v>
+        <v>2671</v>
       </c>
       <c r="BE64" t="str">
-        <v>HD</v>
+        <v>Full HD</v>
       </c>
       <c r="BF64" t="str">
         <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
@@ -12139,19 +12139,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/e/e1/Keputusan_Menteri_Keuangan_Nomor_26~KM.4~2022.pdf</v>
       </c>
       <c r="AE65" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Thunnus_tonggol_(USNM-445333).jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Keputusan_Menteri_Keuangan_Nomor_26~KM.4~2022.pdf</v>
       </c>
       <c r="AF65" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG65" t="str">
-        <v>https://www.youtube.com/watch?v=T3R63YQYbs0</v>
+        <v>https://www.youtube.com/watch?v=1FglVJjL1Lk</v>
       </c>
       <c r="AH65" t="str">
-        <v>T3R63YQYbs0</v>
+        <v>1FglVJjL1Lk</v>
       </c>
       <c r="AI65" t="str">
-        <v>Ocean Wildlife 4K: The Blue Kingdom of Life Underwater Cinematic Documentary, Relaxing Sounds</v>
+        <v>How 72 Hours of Bluefin Tuna Fishing Can Lead to a $2 Million Payoff | Fishing Documentary</v>
       </c>
       <c r="AJ65" t="str">
         <v>4K</v>
@@ -12163,7 +12163,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube</v>
       </c>
       <c r="AM65" t="str">
-        <v>2026-08-01T15:12:02.234Z</v>
+        <v>2026-08-01T16:44:45.879Z</v>
       </c>
       <c r="AN65">
         <v>0.99</v>
@@ -12211,13 +12211,13 @@
         <v>926</v>
       </c>
       <c r="BC65">
-        <v>5998</v>
+        <v>1275</v>
       </c>
       <c r="BD65">
-        <v>2404</v>
+        <v>1950</v>
       </c>
       <c r="BE65" t="str">
-        <v>4K</v>
+        <v>Full HD</v>
       </c>
       <c r="BF65" t="str">
         <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
@@ -12321,10 +12321,10 @@
         <v>https://inaturalist-open-data.s3.amazonaws.com/photos/113880693/original.jpg</v>
       </c>
       <c r="AE66" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Pterois_antennata-3.jpg</v>
+        <v>https://www.inaturalist.org/photos/113880693</v>
       </c>
       <c r="AF66" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG66" t="str">
         <v>https://www.youtube.com/watch?v=nRF0V1nN8jM</v>
@@ -12345,7 +12345,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM66" t="str">
-        <v>2026-08-01T14:57:12.496Z</v>
+        <v>2026-08-01T16:44:49.602Z</v>
       </c>
       <c r="AN66">
         <v>0.99</v>
@@ -12393,16 +12393,16 @@
         <v>932</v>
       </c>
       <c r="BC66">
-        <v>1536</v>
+        <v>604</v>
       </c>
       <c r="BD66">
-        <v>1024</v>
+        <v>453</v>
       </c>
       <c r="BE66" t="str">
         <v>HD</v>
       </c>
       <c r="BF66" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG66" t="str">
         <v>rights-free</v>
@@ -12500,22 +12500,22 @@
         <v/>
       </c>
       <c r="AD67" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/1/17/Scorpaenopsis_diabolus_151247709.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/f/f5/Scorpaenopsis_diabolus_460338811.jpg</v>
       </c>
       <c r="AE67" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Scorpaenopsis_diabolus_151247709.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Scorpaenopsis_diabolus_460338811.jpg</v>
       </c>
       <c r="AF67" t="str">
         <v>CC0</v>
       </c>
       <c r="AG67" t="str">
-        <v>https://www.youtube.com/watch?v=761MzAss2gQ</v>
+        <v>https://www.youtube.com/watch?v=YQM_B4icmD4</v>
       </c>
       <c r="AH67" t="str">
-        <v>761MzAss2gQ</v>
+        <v>YQM_B4icmD4</v>
       </c>
       <c r="AI67" t="str">
-        <v>UNBELIEVABLE! GIANT DEVIL RAY, WHITETIP REEF SHARK, LACY &amp; LEAF SCORPIONFISH - PAPUA NEW GUINEA</v>
+        <v>Devil Scorpionfish - venomous fish that walks on tiny legs</v>
       </c>
       <c r="AJ67" t="str">
         <v/>
@@ -12527,7 +12527,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM67" t="str">
-        <v>2026-08-01T15:12:06.249Z</v>
+        <v>2026-08-01T16:44:53.034Z</v>
       </c>
       <c r="AN67">
         <v>0.99</v>
@@ -12578,7 +12578,7 @@
         <v>2048</v>
       </c>
       <c r="BD67">
-        <v>1472</v>
+        <v>1536</v>
       </c>
       <c r="BE67" t="str">
         <v>Full HD</v>
@@ -12682,22 +12682,22 @@
         <v/>
       </c>
       <c r="AD68" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/6/67/A_happy_fisherman_with_his_fish.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/7/7c/Britannica_Sheepshead.jpg</v>
       </c>
       <c r="AE68" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Sheepshead.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Britannica_Sheepshead.jpg</v>
       </c>
       <c r="AF68" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG68" t="str">
-        <v>https://www.youtube.com/watch?v=UTuAIid6x28</v>
+        <v>https://www.youtube.com/watch?v=1Rg1AeqFMJg</v>
       </c>
       <c r="AH68" t="str">
-        <v>UTuAIid6x28</v>
+        <v>1Rg1AeqFMJg</v>
       </c>
       <c r="AI68" t="str">
-        <v>Stunning 4K Underwater Nature Footage | BBC Earth</v>
+        <v>How a Professional Fillets a Sheepshead! (Toughest Scales)</v>
       </c>
       <c r="AJ68" t="str">
         <v>4K</v>
@@ -12709,7 +12709,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM68" t="str">
-        <v>2026-08-01T15:12:08.242Z</v>
+        <v>2026-08-01T16:44:56.930Z</v>
       </c>
       <c r="AN68">
         <v>0.99</v>
@@ -12757,10 +12757,10 @@
         <v>950</v>
       </c>
       <c r="BC68">
-        <v>349</v>
+        <v>760</v>
       </c>
       <c r="BD68">
-        <v>258</v>
+        <v>660</v>
       </c>
       <c r="BE68" t="str">
         <v>HD</v>
@@ -12867,19 +12867,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/c/c3/Barracuda_with_prey.jpg</v>
       </c>
       <c r="AE69" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Barracuda_laban.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Barracuda_with_prey.jpg</v>
       </c>
       <c r="AF69" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG69" t="str">
-        <v>https://www.youtube.com/watch?v=LbXfoKQmsjw</v>
+        <v>https://www.youtube.com/watch?v=wQUe8EFod_k</v>
       </c>
       <c r="AH69" t="str">
-        <v>LbXfoKQmsjw</v>
+        <v>wQUe8EFod_k</v>
       </c>
       <c r="AI69" t="str">
-        <v>Big Fish Day Large Barracudas 4K Fishing Documentary</v>
+        <v>Barracuda Documentary</v>
       </c>
       <c r="AJ69" t="str">
         <v>4K</v>
@@ -12891,7 +12891,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM69" t="str">
-        <v>2026-08-01T15:12:10.384Z</v>
+        <v>2026-08-01T16:45:00.863Z</v>
       </c>
       <c r="AN69">
         <v>0.99</v>
@@ -12939,13 +12939,13 @@
         <v>956</v>
       </c>
       <c r="BC69">
-        <v>999</v>
+        <v>1796</v>
       </c>
       <c r="BD69">
-        <v>750</v>
+        <v>1172</v>
       </c>
       <c r="BE69" t="str">
-        <v>Full HD</v>
+        <v>HD</v>
       </c>
       <c r="BF69" t="str">
         <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
@@ -13055,13 +13055,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG70" t="str">
-        <v>https://www.youtube.com/watch?v=1myUo_-kpUY</v>
+        <v>https://www.youtube.com/watch?v=XG5d7SZ9Ns8</v>
       </c>
       <c r="AH70" t="str">
-        <v>1myUo_-kpUY</v>
+        <v>XG5d7SZ9Ns8</v>
       </c>
       <c r="AI70" t="str">
-        <v>Stunning 4K Underwater footage + Music Seahorses Nature/ocean animals/relaxing/ sleep videos/calming</v>
+        <v>DESCENDING 4K | S1 E13 | The Pygmy Seahorse</v>
       </c>
       <c r="AJ70" t="str">
         <v>4K</v>
@@ -13073,7 +13073,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM70" t="str">
-        <v>2026-08-01T15:12:12.220Z</v>
+        <v>2026-08-01T16:45:03.898Z</v>
       </c>
       <c r="AN70">
         <v>0.99</v>
@@ -13237,13 +13237,13 @@
         <v>CC0</v>
       </c>
       <c r="AG71" t="str">
-        <v>https://www.youtube.com/watch?v=Ceww6yLijFc</v>
+        <v>https://www.youtube.com/watch?v=XG5d7SZ9Ns8</v>
       </c>
       <c r="AH71" t="str">
-        <v>Ceww6yLijFc</v>
+        <v>XG5d7SZ9Ns8</v>
       </c>
       <c r="AI71" t="str">
-        <v>The Depths of the North Sea: Life in the Cold Abyss | Secrets of the Seas Ep. 1 | 4K UHD Documentary</v>
+        <v>DESCENDING 4K | S1 E13 | The Pygmy Seahorse</v>
       </c>
       <c r="AJ71" t="str">
         <v>4K</v>
@@ -13255,7 +13255,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM71" t="str">
-        <v>2026-08-01T15:12:14.823Z</v>
+        <v>2026-08-01T16:45:10.858Z</v>
       </c>
       <c r="AN71">
         <v>0.99</v>
@@ -13419,13 +13419,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG72" t="str">
-        <v>https://www.youtube.com/watch?v=1myUo_-kpUY</v>
+        <v>https://www.youtube.com/watch?v=eTqXCCp3DpI</v>
       </c>
       <c r="AH72" t="str">
-        <v>1myUo_-kpUY</v>
+        <v>eTqXCCp3DpI</v>
       </c>
       <c r="AI72" t="str">
-        <v>Stunning 4K Underwater footage + Music Seahorses Nature/ocean animals/relaxing/ sleep videos/calming</v>
+        <v>SEAHORSE Documentary National Geographic For KIDS 2016 BBC</v>
       </c>
       <c r="AJ72" t="str">
         <v>4K</v>
@@ -13437,7 +13437,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube</v>
       </c>
       <c r="AM72" t="str">
-        <v>2026-08-01T13:46:59.483Z</v>
+        <v>2026-08-01T16:45:16.094Z</v>
       </c>
       <c r="AN72">
         <v>0.99</v>
@@ -13592,25 +13592,25 @@
         <v/>
       </c>
       <c r="AD73" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/b/b8/Picasso.triggerfish.arp.jpg</v>
+        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/145072177/original.jpg</v>
       </c>
       <c r="AE73" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Picasso.triggerfish.arp.jpg</v>
+        <v>https://www.inaturalist.org/photos/145072177</v>
       </c>
       <c r="AF73" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG73" t="str">
-        <v>https://www.youtube.com/watch?v=76y8t2kYHZ0</v>
+        <v>https://www.youtube.com/watch?v=UVjjjEKXW1w</v>
       </c>
       <c r="AH73" t="str">
-        <v>76y8t2kYHZ0</v>
+        <v>UVjjjEKXW1w</v>
       </c>
       <c r="AI73" t="str">
-        <v>The Ultimate Wildlife Documentary | 150 Stunning Animals in 4K</v>
+        <v>[HD] Merry Christmas with Triggerfish / Drückerfische @ Aquazoo [23/52]</v>
       </c>
       <c r="AJ73" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK73" t="str">
         <v>https://www.gbif.org/species/2407235</v>
@@ -13619,7 +13619,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM73" t="str">
-        <v>2026-08-01T15:12:18.643Z</v>
+        <v>2026-08-01T16:45:20.161Z</v>
       </c>
       <c r="AN73">
         <v>0.99</v>
@@ -13667,16 +13667,16 @@
         <v>998</v>
       </c>
       <c r="BC73">
-        <v>1800</v>
+        <v>1592</v>
       </c>
       <c r="BD73">
-        <v>1416</v>
+        <v>744</v>
       </c>
       <c r="BE73" t="str">
         <v>HD</v>
       </c>
       <c r="BF73" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG73" t="str">
         <v>rights-free</v>
@@ -13774,22 +13774,22 @@
         <v/>
       </c>
       <c r="AD74" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/0/06/Blacktip_Reef_Shark_imported_from_iNaturalist_photo_420767872_on_22_August_2024.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/7/7c/Blacktip_Reef_Shark_imported_from_iNaturalist_photo_420767906_on_22_August_2024.jpg</v>
       </c>
       <c r="AE74" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Carcharhinus_melanopterus_mirihi.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Blacktip_Reef_Shark_imported_from_iNaturalist_photo_420767906_on_22_August_2024.jpg</v>
       </c>
       <c r="AF74" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG74" t="str">
-        <v>https://www.youtube.com/watch?v=UTuAIid6x28</v>
+        <v>https://www.youtube.com/watch?v=7iQZT5yrBSw</v>
       </c>
       <c r="AH74" t="str">
-        <v>UTuAIid6x28</v>
+        <v>7iQZT5yrBSw</v>
       </c>
       <c r="AI74" t="str">
-        <v>Stunning 4K Underwater Nature Footage | BBC Earth</v>
+        <v>Blacktip reef shark 4K (Carcharhinus melanopterus)</v>
       </c>
       <c r="AJ74" t="str">
         <v>4K</v>
@@ -13801,7 +13801,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM74" t="str">
-        <v>2026-08-01T15:12:20.866Z</v>
+        <v>2026-08-01T16:45:24.768Z</v>
       </c>
       <c r="AN74">
         <v>0.99</v>
@@ -13849,16 +13849,16 @@
         <v>1016</v>
       </c>
       <c r="BC74">
-        <v>740</v>
+        <v>2048</v>
       </c>
       <c r="BD74">
-        <v>416</v>
+        <v>1312</v>
       </c>
       <c r="BE74" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF74" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG74" t="str">
         <v>rights-free</v>
@@ -13965,13 +13965,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG75" t="str">
-        <v>https://www.youtube.com/watch?v=UTuAIid6x28</v>
+        <v>https://www.youtube.com/watch?v=tX3Z3jnHlbc</v>
       </c>
       <c r="AH75" t="str">
-        <v>UTuAIid6x28</v>
+        <v>tX3Z3jnHlbc</v>
       </c>
       <c r="AI75" t="str">
-        <v>Stunning 4K Underwater Nature Footage | BBC Earth</v>
+        <v>WILD COASTAL | Orca vs Great White Shark: The Day Ocean Kings Fell (Full 4K Nature Documentary)</v>
       </c>
       <c r="AJ75" t="str">
         <v>4K</v>
@@ -13983,7 +13983,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM75" t="str">
-        <v>2026-08-01T15:12:23.393Z</v>
+        <v>2026-08-01T16:45:28.362Z</v>
       </c>
       <c r="AN75">
         <v>0.99</v>
@@ -14138,22 +14138,22 @@
         <v/>
       </c>
       <c r="AD76" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/e/e1/Sphyrna_zygaena_by_Frank_Edward_Clarke.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/0/0b/Hammerhai.jpg</v>
       </c>
       <c r="AE76" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Sphyrna_zygaena_by_Frank_Edward_Clarke.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Hammerhai.jpg</v>
       </c>
       <c r="AF76" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG76" t="str">
-        <v>https://www.youtube.com/watch?v=h7KkQPNdm-4</v>
+        <v>https://www.youtube.com/watch?v=gd-h8iqzm5E</v>
       </c>
       <c r="AH76" t="str">
-        <v>h7KkQPNdm-4</v>
+        <v>gd-h8iqzm5E</v>
       </c>
       <c r="AI76" t="str">
-        <v>Hammerheads: Secrets of the Full Moon | 4K Documentary</v>
+        <v>Hammerhead shark Full documentary 2018</v>
       </c>
       <c r="AJ76" t="str">
         <v>4K</v>
@@ -14165,7 +14165,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM76" t="str">
-        <v>2026-08-01T15:12:25.363Z</v>
+        <v>2026-08-01T16:45:32.075Z</v>
       </c>
       <c r="AN76">
         <v>0.99</v>
@@ -14213,10 +14213,10 @@
         <v>1034</v>
       </c>
       <c r="BC76">
-        <v>14917</v>
+        <v>364</v>
       </c>
       <c r="BD76">
-        <v>4275</v>
+        <v>227</v>
       </c>
       <c r="BE76" t="str">
         <v>4K</v>
@@ -14323,19 +14323,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/9/95/Carcharhinus_albimarginatus-shark.jpg</v>
       </c>
       <c r="AE77" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Triaenodon_obesus_435408600.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Carcharhinus_albimarginatus-shark.jpg</v>
       </c>
       <c r="AF77" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG77" t="str">
-        <v>https://www.youtube.com/watch?v=UTuAIid6x28</v>
+        <v>https://www.youtube.com/watch?v=PAnYua2mYzU</v>
       </c>
       <c r="AH77" t="str">
-        <v>UTuAIid6x28</v>
+        <v>PAnYua2mYzU</v>
       </c>
       <c r="AI77" t="str">
-        <v>Stunning 4K Underwater Nature Footage | BBC Earth</v>
+        <v>Whitetip Reef Sharks: Deadly Nocturnal Predators | Free Documentary Nature</v>
       </c>
       <c r="AJ77" t="str">
         <v>4K</v>
@@ -14347,7 +14347,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM77" t="str">
-        <v>2026-08-01T15:12:27.847Z</v>
+        <v>2026-08-01T16:45:35.565Z</v>
       </c>
       <c r="AN77">
         <v>0.99</v>
@@ -14395,16 +14395,16 @@
         <v>1040</v>
       </c>
       <c r="BC77">
-        <v>2048</v>
+        <v>6331</v>
       </c>
       <c r="BD77">
-        <v>1536</v>
+        <v>4163</v>
       </c>
       <c r="BE77" t="str">
-        <v>Full HD</v>
+        <v>4K</v>
       </c>
       <c r="BF77" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG77" t="str">
         <v>rights-free</v>
@@ -14511,13 +14511,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG78" t="str">
-        <v>https://www.youtube.com/watch?v=TFfexEPj5eo</v>
+        <v>https://www.youtube.com/watch?v=dAd21_N1PGk</v>
       </c>
       <c r="AH78" t="str">
-        <v>TFfexEPj5eo</v>
+        <v>dAd21_N1PGk</v>
       </c>
       <c r="AI78" t="str">
-        <v>SHOCKING FACTS ABOUT SHARKS / 4K DOCUMENTARY FILM</v>
+        <v>The Fastest Shark Vs the Fastest Fish | Mako Shark Vs Sailfish | Wild Kratts</v>
       </c>
       <c r="AJ78" t="str">
         <v>4K</v>
@@ -14529,7 +14529,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM78" t="str">
-        <v>2026-08-01T15:12:29.753Z</v>
+        <v>2026-08-01T16:45:38.925Z</v>
       </c>
       <c r="AN78">
         <v>0.99</v>
@@ -14687,19 +14687,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/b/bb/Adriaen_Coenen%27s_Visboeck_-_KB_78_E_54_-_folio_369r.jpg</v>
       </c>
       <c r="AE79" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Alopias_vulpinus_tail_noaa.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Adriaen_Coenen%27s_Visboeck_-_KB_78_E_54_-_folio_369r.jpg</v>
       </c>
       <c r="AF79" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG79" t="str">
-        <v>https://www.youtube.com/watch?v=TFfexEPj5eo</v>
+        <v>https://www.youtube.com/watch?v=5sAapUALtKY</v>
       </c>
       <c r="AH79" t="str">
-        <v>TFfexEPj5eo</v>
+        <v>5sAapUALtKY</v>
       </c>
       <c r="AI79" t="str">
-        <v>SHOCKING FACTS ABOUT SHARKS / 4K DOCUMENTARY FILM</v>
+        <v>Malapascua: Island of the Thresher Shark // Life, Uncharted Ch. 03 [Documentary]</v>
       </c>
       <c r="AJ79" t="str">
         <v>4K</v>
@@ -14711,7 +14711,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM79" t="str">
-        <v>2026-08-01T15:12:32.288Z</v>
+        <v>2026-08-01T16:45:42.807Z</v>
       </c>
       <c r="AN79">
         <v>0.99</v>
@@ -14759,10 +14759,10 @@
         <v>1052</v>
       </c>
       <c r="BC79">
-        <v>941</v>
+        <v>3331</v>
       </c>
       <c r="BD79">
-        <v>529</v>
+        <v>4906</v>
       </c>
       <c r="BE79" t="str">
         <v>4K</v>
@@ -14869,22 +14869,22 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/3/36/Der_naturen_bloeme_-_Jacob_van_Maerlant_-_KB_KA_16_-_120v.jpg</v>
       </c>
       <c r="AE80" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Torpedo_marmorata_rangemap.png</v>
+        <v>https://commons.wikimedia.org/wiki/File:Der_naturen_bloeme_-_Jacob_van_Maerlant_-_KB_KA_16_-_120v.jpg</v>
       </c>
       <c r="AF80" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG80" t="str">
-        <v>https://www.youtube.com/watch?v=76y8t2kYHZ0</v>
+        <v>https://www.youtube.com/watch?v=lKm2WlgKauY</v>
       </c>
       <c r="AH80" t="str">
-        <v>76y8t2kYHZ0</v>
+        <v>lKm2WlgKauY</v>
       </c>
       <c r="AI80" t="str">
-        <v>The Ultimate Wildlife Documentary | 150 Stunning Animals in 4K</v>
+        <v>Marbled Electric Ray HD</v>
       </c>
       <c r="AJ80" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK80" t="str">
         <v>https://www.gbif.org/species/5215518</v>
@@ -14893,7 +14893,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM80" t="str">
-        <v>2026-08-01T15:12:35.039Z</v>
+        <v>2026-08-01T16:45:46.670Z</v>
       </c>
       <c r="AN80">
         <v>0.99</v>
@@ -14941,16 +14941,16 @@
         <v>1070</v>
       </c>
       <c r="BC80">
-        <v>1357</v>
+        <v>1956</v>
       </c>
       <c r="BD80">
-        <v>628</v>
+        <v>2703</v>
       </c>
       <c r="BE80" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF80" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG80" t="str">
         <v>rights-free</v>
@@ -15051,7 +15051,7 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/b/b3/Dolphinfish_%28Coryphaena_hippurus%29.jpg</v>
       </c>
       <c r="AE81" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Coryphaena_hippurus_Ford_53.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Dolphinfish_(Coryphaena_hippurus).jpg</v>
       </c>
       <c r="AF81" t="str">
         <v>Public Domain</v>
@@ -15075,7 +15075,7 @@
         <v>gbif | legacy-observation | wikipedia-vi | wikimedia | wikidata | youtube | inaturalist</v>
       </c>
       <c r="AM81" t="str">
-        <v>2026-08-01T15:12:36.923Z</v>
+        <v>2026-08-01T16:45:50.195Z</v>
       </c>
       <c r="AN81">
         <v>0.99</v>
@@ -15123,10 +15123,10 @@
         <v>1106</v>
       </c>
       <c r="BC81">
-        <v>1549</v>
+        <v>1017</v>
       </c>
       <c r="BD81">
-        <v>679</v>
+        <v>511</v>
       </c>
       <c r="BE81" t="str">
         <v/>
@@ -15230,22 +15230,22 @@
         <v/>
       </c>
       <c r="AD82" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/1/19/FMIB_51582_Corynolophus_reinhardti_%28L%C3%BCtken%29%2C_showing_luminous_bulb_Family_Ceratiidae_Deep_sea_off_Greenland.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/c/c5/Himantolophus_sp.jpg</v>
       </c>
       <c r="AE82" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Himantolophus_groenlandicus.png</v>
+        <v>https://commons.wikimedia.org/wiki/File:Himantolophus_sp.jpg</v>
       </c>
       <c r="AF82" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG82" t="str">
-        <v>https://www.youtube.com/watch?v=Ceww6yLijFc</v>
+        <v>https://www.youtube.com/watch?v=94weodD4TMo</v>
       </c>
       <c r="AH82" t="str">
-        <v>Ceww6yLijFc</v>
+        <v>94weodD4TMo</v>
       </c>
       <c r="AI82" t="str">
-        <v>The Depths of the North Sea: Life in the Cold Abyss | Secrets of the Seas Ep. 1 | 4K UHD Documentary</v>
+        <v>Fish – The Hidden Civilization Underwater | 4K Wildlife Documentary</v>
       </c>
       <c r="AJ82" t="str">
         <v>4K</v>
@@ -15257,7 +15257,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube</v>
       </c>
       <c r="AM82" t="str">
-        <v>2026-08-01T15:12:38.689Z</v>
+        <v>2026-08-01T16:45:52.960Z</v>
       </c>
       <c r="AN82">
         <v>0.99</v>
@@ -15305,10 +15305,10 @@
         <v>1121</v>
       </c>
       <c r="BC82">
-        <v>1056</v>
+        <v>600</v>
       </c>
       <c r="BD82">
-        <v>741</v>
+        <v>450</v>
       </c>
       <c r="BE82" t="str">
         <v/>
@@ -15421,13 +15421,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG83" t="str">
-        <v>https://www.youtube.com/watch?v=S5gNxXfPE2E</v>
+        <v>https://www.youtube.com/watch?v=y0608caVdc8</v>
       </c>
       <c r="AH83" t="str">
-        <v>S5gNxXfPE2E</v>
+        <v>y0608caVdc8</v>
       </c>
       <c r="AI83" t="str">
-        <v>Wildlife Animal Documentary | Peaceful Grassland Herds in Golden Sunrise | 4K Ultra HD</v>
+        <v>All About The Yellow Blotch Rabbitfish or Orange Spotted Foxface Rabbitfish</v>
       </c>
       <c r="AJ83" t="str">
         <v>4K</v>
@@ -15439,7 +15439,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM83" t="str">
-        <v>2026-08-01T15:12:40.528Z</v>
+        <v>2026-08-01T16:45:56.661Z</v>
       </c>
       <c r="AN83">
         <v>0.99</v>
@@ -15594,22 +15594,22 @@
         <v/>
       </c>
       <c r="AD84" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/d/da/Coat_of_Arms_of_Kuokui.png</v>
+        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/45075340/original.jpeg</v>
       </c>
       <c r="AE84" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Carassius_gibelio_male_head_2009_G1.jpg</v>
+        <v>https://www.inaturalist.org/photos/45075340</v>
       </c>
       <c r="AF84" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG84" t="str">
-        <v>https://www.youtube.com/watch?v=3eTMbBzVFfM</v>
+        <v>https://www.youtube.com/watch?v=1sQUrqhl_Lk</v>
       </c>
       <c r="AH84" t="str">
-        <v>3eTMbBzVFfM</v>
+        <v>1sQUrqhl_Lk</v>
       </c>
       <c r="AI84" t="str">
-        <v>The Magical Wildlife of Britain’s Rivers (4K Documentary)</v>
+        <v>John Wilson's GO FISHING - Foreign Fiske (Part 1_2) - Crucian Carp - National Geographic Documentary</v>
       </c>
       <c r="AJ84" t="str">
         <v>4K</v>
@@ -15621,7 +15621,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM84" t="str">
-        <v>2026-08-01T15:12:42.747Z</v>
+        <v>2026-08-01T16:46:00.594Z</v>
       </c>
       <c r="AN84">
         <v>0.99</v>
@@ -15669,16 +15669,16 @@
         <v>1148</v>
       </c>
       <c r="BC84">
-        <v>3456</v>
+        <v>802</v>
       </c>
       <c r="BD84">
-        <v>2592</v>
+        <v>534</v>
       </c>
       <c r="BE84" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF84" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG84" t="str">
         <v>rights-free</v>
@@ -15779,7 +15779,7 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/0/0b/Dori-baengbaengi.jpg</v>
       </c>
       <c r="AE85" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Zacco_platypus_-_Osaka_Museum_of_Natural_History_-_DSC07760.JPG</v>
+        <v>https://commons.wikimedia.org/wiki/File:Dori-baengbaengi.jpg</v>
       </c>
       <c r="AF85" t="str">
         <v>CC0</v>
@@ -15803,7 +15803,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM85" t="str">
-        <v>2026-08-01T15:12:44.871Z</v>
+        <v>2026-08-01T16:46:04.200Z</v>
       </c>
       <c r="AN85">
         <v>0.99</v>
@@ -15851,10 +15851,10 @@
         <v>1154</v>
       </c>
       <c r="BC85">
-        <v>4320</v>
+        <v>5184</v>
       </c>
       <c r="BD85">
-        <v>3240</v>
+        <v>3456</v>
       </c>
       <c r="BE85" t="str">
         <v>4K</v>
@@ -16149,13 +16149,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG87" t="str">
-        <v>https://www.youtube.com/watch?v=UTuAIid6x28</v>
+        <v>https://www.youtube.com/watch?v=hMBQB5sLWD8</v>
       </c>
       <c r="AH87" t="str">
-        <v>UTuAIid6x28</v>
+        <v>hMBQB5sLWD8</v>
       </c>
       <c r="AI87" t="str">
-        <v>Stunning 4K Underwater Nature Footage | BBC Earth</v>
+        <v>Largemouth Bass Growth Rate Documentary ep: 1</v>
       </c>
       <c r="AJ87" t="str">
         <v>4K</v>
@@ -16167,7 +16167,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM87" t="str">
-        <v>2026-08-01T15:12:48.635Z</v>
+        <v>2026-08-01T16:46:11.025Z</v>
       </c>
       <c r="AN87">
         <v>0.99</v>
@@ -16331,13 +16331,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG88" t="str">
-        <v>https://www.youtube.com/watch?v=LkZl4HcVVB8</v>
+        <v>https://www.youtube.com/watch?v=GnB9I07x_eo</v>
       </c>
       <c r="AH88" t="str">
-        <v>LkZl4HcVVB8</v>
+        <v>GnB9I07x_eo</v>
       </c>
       <c r="AI88" t="str">
-        <v>Jungle Animals in 4K UHD 🌿 | Amazing Wildlife Discovery | 60FPS Ultra HD Nature Documentary</v>
+        <v>Life of the Yellow Perch and How to Fish for Perch</v>
       </c>
       <c r="AJ88" t="str">
         <v>4K</v>
@@ -16349,7 +16349,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM88" t="str">
-        <v>2026-08-01T15:12:51.267Z</v>
+        <v>2026-08-01T16:46:15.257Z</v>
       </c>
       <c r="AN88">
         <v>0.99</v>
@@ -16507,19 +16507,19 @@
         <v>https://inaturalist-open-data.s3.amazonaws.com/photos/337659289/original.jpeg</v>
       </c>
       <c r="AE89" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:ChromisNiloticus.jpg</v>
+        <v>https://www.inaturalist.org/photos/337659289</v>
       </c>
       <c r="AF89" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG89" t="str">
-        <v>https://www.youtube.com/watch?v=pt7glMuzJkI</v>
+        <v>https://www.youtube.com/watch?v=OqjfRqj0ilQ</v>
       </c>
       <c r="AH89" t="str">
-        <v>pt7glMuzJkI</v>
+        <v>OqjfRqj0ilQ</v>
       </c>
       <c r="AI89" t="str">
-        <v>Life at the Limits: Water, Wildlife &amp; Extreme Survival | 4K Nature Documentary</v>
+        <v>Why Tilapia Became a $5 Billion Industry Feeding the World | Fishing Documentary</v>
       </c>
       <c r="AJ89" t="str">
         <v>4K</v>
@@ -16531,7 +16531,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM89" t="str">
-        <v>2026-08-01T14:57:55.644Z</v>
+        <v>2026-08-01T16:46:18.818Z</v>
       </c>
       <c r="AN89">
         <v>0.97</v>
@@ -16579,16 +16579,16 @@
         <v>1178</v>
       </c>
       <c r="BC89">
-        <v>890</v>
+        <v>2048</v>
       </c>
       <c r="BD89">
-        <v>594</v>
+        <v>1536</v>
       </c>
       <c r="BE89" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF89" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG89" t="str">
         <v>rights-free</v>
@@ -16695,13 +16695,13 @@
         <v>CC0</v>
       </c>
       <c r="AG90" t="str">
-        <v>https://www.youtube.com/watch?v=LkZl4HcVVB8</v>
+        <v>https://www.youtube.com/watch?v=yPfJtvwuoWU</v>
       </c>
       <c r="AH90" t="str">
-        <v>LkZl4HcVVB8</v>
+        <v>yPfJtvwuoWU</v>
       </c>
       <c r="AI90" t="str">
-        <v>Jungle Animals in 4K UHD 🌿 | Amazing Wildlife Discovery | 60FPS Ultra HD Nature Documentary</v>
+        <v>The Miracle of Gastronomy - Ayu (Sweetfish) is in season from June to October.</v>
       </c>
       <c r="AJ90" t="str">
         <v>4K</v>
@@ -16713,7 +16713,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM90" t="str">
-        <v>2026-08-01T15:12:56.225Z</v>
+        <v>2026-08-01T16:46:22.303Z</v>
       </c>
       <c r="AN90">
         <v>0.99</v>
@@ -16877,13 +16877,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG91" t="str">
-        <v>https://www.youtube.com/watch?v=7ZhdXgRfxHI</v>
+        <v>https://www.youtube.com/watch?v=iVOXMoJUBag</v>
       </c>
       <c r="AH91" t="str">
-        <v>7ZhdXgRfxHI</v>
+        <v>iVOXMoJUBag</v>
       </c>
       <c r="AI91" t="str">
-        <v>Incredible 4K Nature Scenes Narrated By David Attenborough | BBC Earth</v>
+        <v>Can Norway’s wild salmon be saved? | DW Documentary</v>
       </c>
       <c r="AJ91" t="str">
         <v>4K</v>
@@ -16895,7 +16895,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM91" t="str">
-        <v>2026-08-01T15:12:58.364Z</v>
+        <v>2026-08-01T16:46:26.303Z</v>
       </c>
       <c r="AN91">
         <v>0.99</v>
@@ -17053,22 +17053,22 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/0/01/Juvenile_Chinook_Salmon.jpg</v>
       </c>
       <c r="AE92" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:K%C3%B6nigslachs_(Oncorhynchus_tshawytscha),_R%C3%BCckkehr_aus_dem_Pazifischen_Ozean.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Juvenile_Chinook_Salmon.jpg</v>
       </c>
       <c r="AF92" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG92" t="str">
-        <v>https://www.youtube.com/watch?v=dF1X13Oo0pg</v>
+        <v>https://www.youtube.com/watch?v=S0StOLPSMoA</v>
       </c>
       <c r="AH92" t="str">
-        <v>dF1X13Oo0pg</v>
+        <v>S0StOLPSMoA</v>
       </c>
       <c r="AI92" t="str">
-        <v>10 Hours of Epic 4K Wildlife Documentary: Crocodiles Buffaloes &amp; Nature’s Greatest Battles #wildlife</v>
+        <v>HD Documentary Salmon Confidential HD Nature Documentary</v>
       </c>
       <c r="AJ92" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK92" t="str">
         <v>https://www.gbif.org/species/5204024</v>
@@ -17077,7 +17077,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM92" t="str">
-        <v>2026-08-01T15:13:01.488Z</v>
+        <v>2026-08-01T16:46:30.141Z</v>
       </c>
       <c r="AN92">
         <v>0.99</v>
@@ -17125,13 +17125,13 @@
         <v>1202</v>
       </c>
       <c r="BC92">
-        <v>3684</v>
+        <v>5651</v>
       </c>
       <c r="BD92">
-        <v>2828</v>
+        <v>2921</v>
       </c>
       <c r="BE92" t="str">
-        <v>Full HD</v>
+        <v>4K</v>
       </c>
       <c r="BF92" t="str">
         <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
@@ -17232,22 +17232,22 @@
         <v/>
       </c>
       <c r="AD93" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/a/ad/Chrysochloris_asiatica_-_1731-1795_-_Print_-_Iconographia_Zoologica_-_Special_Collections_University_of_Amsterdam.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/3/32/FMIB_46808_Taupe_doree.jpeg</v>
       </c>
       <c r="AE93" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Chrysochloris_asiatica.png</v>
+        <v>https://commons.wikimedia.org/wiki/File:FMIB_46808_Taupe_doree.jpeg</v>
       </c>
       <c r="AF93" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG93" t="str">
-        <v>https://www.youtube.com/watch?v=W-O5KfQLgO8</v>
+        <v>https://www.youtube.com/watch?v=u74iVC_wVek</v>
       </c>
       <c r="AH93" t="str">
-        <v>W-O5KfQLgO8</v>
+        <v>u74iVC_wVek</v>
       </c>
       <c r="AI93" t="str">
-        <v>The Incredible Wildlife of Europe's Most Unique Valley | 4K</v>
+        <v>The Weird and Wonderful Star-Nosed Mole | 4K UHD | Mammals | BBC Earth</v>
       </c>
       <c r="AJ93" t="str">
         <v>4K</v>
@@ -17259,7 +17259,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM93" t="str">
-        <v>2026-08-01T15:13:04.423Z</v>
+        <v>2026-08-01T16:40:06.044Z</v>
       </c>
       <c r="AN93">
         <v>0.99</v>
@@ -17307,10 +17307,10 @@
         <v>1215</v>
       </c>
       <c r="BC93">
-        <v>500</v>
+        <v>884</v>
       </c>
       <c r="BD93">
-        <v>333</v>
+        <v>553</v>
       </c>
       <c r="BE93" t="str">
         <v>Full HD</v>
@@ -17417,19 +17417,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/0/06/Blue_Whale_001_body_bw.jpg</v>
       </c>
       <c r="AE94" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Balaenoptera_musculus_size_comparison_for_Wikipedia.png</v>
+        <v>https://commons.wikimedia.org/wiki/File:Blue_Whale_001_body_bw.jpg</v>
       </c>
       <c r="AF94" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG94" t="str">
-        <v>https://www.youtube.com/watch?v=9_1pBQI75b4</v>
+        <v>https://www.youtube.com/watch?v=V79bJVX3xQM</v>
       </c>
       <c r="AH94" t="str">
-        <v>9_1pBQI75b4</v>
+        <v>V79bJVX3xQM</v>
       </c>
       <c r="AI94" t="str">
-        <v>Whale Kingdom: Uncovering the Mysteries of the Deep - Full 4K UHD Documentary</v>
+        <v>Blue Whale: The Largest Animal In Existence! | 4K Animal Documentary</v>
       </c>
       <c r="AJ94" t="str">
         <v>4K</v>
@@ -17441,7 +17441,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM94" t="str">
-        <v>2026-08-01T15:13:06.499Z</v>
+        <v>2026-08-01T16:46:39.070Z</v>
       </c>
       <c r="AN94">
         <v>0.99</v>
@@ -17489,16 +17489,16 @@
         <v>1239</v>
       </c>
       <c r="BC94">
-        <v>4696</v>
+        <v>3983</v>
       </c>
       <c r="BD94">
-        <v>2400</v>
+        <v>5087</v>
       </c>
       <c r="BE94" t="str">
         <v>4K</v>
       </c>
       <c r="BF94" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG94" t="str">
         <v>rights-free</v>
@@ -17599,19 +17599,19 @@
         <v>https://inaturalist-open-data.s3.amazonaws.com/photos/392120354/original.jpeg</v>
       </c>
       <c r="AE95" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Capra_aegagrus_hircus_in_isla_Margarita.jpg</v>
+        <v>https://www.inaturalist.org/photos/392120354</v>
       </c>
       <c r="AF95" t="str">
         <v>CC0</v>
       </c>
       <c r="AG95" t="str">
-        <v>https://www.youtube.com/watch?v=TvIasT0vNQg</v>
+        <v>https://www.youtube.com/watch?v=jHXK9ohcYug</v>
       </c>
       <c r="AH95" t="str">
-        <v>TvIasT0vNQg</v>
+        <v>jHXK9ohcYug</v>
       </c>
       <c r="AI95" t="str">
-        <v>Markhor: The Mountain Goat That Defies Death | 4K Documentary</v>
+        <v>Goats: Social, Smart, and Surprisingly Sensitive | FULL DOCUMENTARY</v>
       </c>
       <c r="AJ95" t="str">
         <v>4K</v>
@@ -17623,7 +17623,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM95" t="str">
-        <v>2026-08-01T14:58:08.443Z</v>
+        <v>2026-08-01T16:46:42.894Z</v>
       </c>
       <c r="AN95">
         <v>0.99</v>
@@ -17671,16 +17671,16 @@
         <v>1251</v>
       </c>
       <c r="BC95">
-        <v>4133</v>
+        <v>2048</v>
       </c>
       <c r="BD95">
-        <v>2573</v>
+        <v>1537</v>
       </c>
       <c r="BE95" t="str">
-        <v>4K</v>
+        <v>Full HD</v>
       </c>
       <c r="BF95" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG95" t="str">
         <v>rights-free</v>
@@ -17781,19 +17781,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/2/24/6%2818%29_Sperm_whale.JPG</v>
       </c>
       <c r="AE96" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:6(3)_Sperm_whale_(Physeter_macrocephalus).JPG</v>
+        <v>https://commons.wikimedia.org/wiki/File:6(18)_Sperm_whale.JPG</v>
       </c>
       <c r="AF96" t="str">
         <v>CC0</v>
       </c>
       <c r="AG96" t="str">
-        <v>https://www.youtube.com/watch?v=9_1pBQI75b4</v>
+        <v>https://www.youtube.com/watch?v=GWR7PQokeMc</v>
       </c>
       <c r="AH96" t="str">
-        <v>9_1pBQI75b4</v>
+        <v>GWR7PQokeMc</v>
       </c>
       <c r="AI96" t="str">
-        <v>Whale Kingdom: Uncovering the Mysteries of the Deep - Full 4K UHD Documentary</v>
+        <v>Sperm Whale: The Ultimate Deep Sea Predator | Ocean Documentary 4K</v>
       </c>
       <c r="AJ96" t="str">
         <v>4K</v>
@@ -17805,7 +17805,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM96" t="str">
-        <v>2026-08-01T15:13:11.160Z</v>
+        <v>2026-08-01T16:46:46.876Z</v>
       </c>
       <c r="AN96">
         <v>0.99</v>
@@ -17853,13 +17853,13 @@
         <v>1269</v>
       </c>
       <c r="BC96">
-        <v>3648</v>
+        <v>4320</v>
       </c>
       <c r="BD96">
-        <v>2736</v>
+        <v>2880</v>
       </c>
       <c r="BE96" t="str">
-        <v>Full HD</v>
+        <v>4K</v>
       </c>
       <c r="BF96" t="str">
         <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
@@ -17963,19 +17963,19 @@
         <v>https://inaturalist-open-data.s3.amazonaws.com/photos/570226854/original.jpg</v>
       </c>
       <c r="AE97" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Priodontes_maximus,_museum_02.JPG</v>
+        <v>https://www.inaturalist.org/photos/570226854</v>
       </c>
       <c r="AF97" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG97" t="str">
-        <v>https://www.youtube.com/watch?v=m_JgG7qbEB0</v>
+        <v>https://www.youtube.com/watch?v=1rTmjsjPiRA</v>
       </c>
       <c r="AH97" t="str">
-        <v>m_JgG7qbEB0</v>
+        <v>1rTmjsjPiRA</v>
       </c>
       <c r="AI97" t="str">
-        <v>Armadillo Life Story 4K #wildlife</v>
+        <v>Amazing Armadillo Looks for Love | 4K UHD | Mammals | BBC Earth</v>
       </c>
       <c r="AJ97" t="str">
         <v>4K</v>
@@ -17987,7 +17987,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM97" t="str">
-        <v>2026-08-01T14:58:11.984Z</v>
+        <v>2026-08-01T16:46:50.130Z</v>
       </c>
       <c r="AN97">
         <v>0.99</v>
@@ -18035,16 +18035,16 @@
         <v>1281</v>
       </c>
       <c r="BC97">
-        <v>2642</v>
+        <v>2048</v>
       </c>
       <c r="BD97">
-        <v>2112</v>
+        <v>1536</v>
       </c>
       <c r="BE97" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF97" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG97" t="str">
         <v>rights-free</v>
@@ -18142,7 +18142,7 @@
         <v/>
       </c>
       <c r="AD98" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/5/5e/Pteropus_edulis_-_1700-1880_-_Print_-_Iconographia_Zoologica_-_Special_Collections_University_of_Amsterdam_-_UBA01_IZ20700008.tif</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/0/09/Pteropus_vampyrus_435399917.jpg</v>
       </c>
       <c r="AE98" t="str">
         <v>https://commons.wikimedia.org/wiki/File:Pteropus_vampyrus_435399917.jpg</v>
@@ -18151,13 +18151,13 @@
         <v>CC0</v>
       </c>
       <c r="AG98" t="str">
-        <v>https://www.youtube.com/watch?v=Wg3ua_bprTo</v>
+        <v>https://www.youtube.com/watch?v=f6dOBB9SXbA</v>
       </c>
       <c r="AH98" t="str">
-        <v>Wg3ua_bprTo</v>
+        <v>f6dOBB9SXbA</v>
       </c>
       <c r="AI98" t="str">
-        <v>Devoted Flying Fox Protects Pup With Her Wings (4K)</v>
+        <v>Flying Fox Fairy Tale 🦇| Bat Documentary | Natural History Channel</v>
       </c>
       <c r="AJ98" t="str">
         <v>4K</v>
@@ -18169,7 +18169,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM98" t="str">
-        <v>2026-08-01T15:13:15.471Z</v>
+        <v>2026-08-01T16:46:55.783Z</v>
       </c>
       <c r="AN98">
         <v>0.99</v>
@@ -18327,19 +18327,19 @@
         <v>https://inaturalist-open-data.s3.amazonaws.com/photos/56995639/original.jpeg</v>
       </c>
       <c r="AE99" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Zwergfledermaus_(Pipistrellus_pipistrellus).png</v>
+        <v>https://www.inaturalist.org/photos/56995639</v>
       </c>
       <c r="AF99" t="str">
         <v>CC0</v>
       </c>
       <c r="AG99" t="str">
-        <v>https://www.youtube.com/watch?v=8_lLAEEvty4</v>
+        <v>https://www.youtube.com/watch?v=uAlzEc2F80k</v>
       </c>
       <c r="AH99" t="str">
-        <v>8_lLAEEvty4</v>
+        <v>uAlzEc2F80k</v>
       </c>
       <c r="AI99" t="str">
-        <v>The Most Extraordinary Birds on Earth | 4K Wildlife Documentary</v>
+        <v>Tiny Bat Facts | Common Pipistrelle Bat Documentary |Mysterious Creatures of the Night</v>
       </c>
       <c r="AJ99" t="str">
         <v>4K</v>
@@ -18351,7 +18351,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM99" t="str">
-        <v>2026-08-01T14:58:16.227Z</v>
+        <v>2026-08-01T16:47:01.113Z</v>
       </c>
       <c r="AN99">
         <v>0.99</v>
@@ -18399,16 +18399,16 @@
         <v>1305</v>
       </c>
       <c r="BC99">
-        <v>1080</v>
+        <v>2048</v>
       </c>
       <c r="BD99">
-        <v>1920</v>
+        <v>1536</v>
       </c>
       <c r="BE99" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF99" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG99" t="str">
         <v>rights-free</v>
@@ -18509,7 +18509,7 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/c/c6/Angry_domestic_cat_versus_hungry_Virginia_opossum.jpg</v>
       </c>
       <c r="AE100" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:8_month_old_Virginia_Opossum_(Didelphis_virginiana).jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Angry_domestic_cat_versus_hungry_Virginia_opossum.jpg</v>
       </c>
       <c r="AF100" t="str">
         <v>CC0</v>
@@ -18533,7 +18533,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM100" t="str">
-        <v>2026-08-01T15:13:20.030Z</v>
+        <v>2026-08-01T16:47:05.914Z</v>
       </c>
       <c r="AN100">
         <v>0.99</v>
@@ -18581,13 +18581,13 @@
         <v>1323</v>
       </c>
       <c r="BC100">
-        <v>798</v>
+        <v>1536</v>
       </c>
       <c r="BD100">
-        <v>1325</v>
+        <v>2048</v>
       </c>
       <c r="BE100" t="str">
-        <v>HD</v>
+        <v>Full HD</v>
       </c>
       <c r="BF100" t="str">
         <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
@@ -18691,22 +18691,22 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/f/fa/Didelphis_marsupialis_Schreber.jpg</v>
       </c>
       <c r="AE101" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Common_opossum_(Didelphis_marsupialis)_-_skeleton_(AMNH_M-204031).jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Didelphis_marsupialis_Schreber.jpg</v>
       </c>
       <c r="AF101" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG101" t="str">
-        <v>https://www.youtube.com/watch?v=CRQ5T3z2YOY</v>
+        <v>https://www.youtube.com/watch?v=mNtlMfrhbE4</v>
       </c>
       <c r="AH101" t="str">
-        <v>CRQ5T3z2YOY</v>
+        <v>mNtlMfrhbE4</v>
       </c>
       <c r="AI101" t="str">
-        <v>Opossum beautiful animals family, animal sounds, amazon, 4k Ultra HD, opossum, jancy family opossum,</v>
+        <v>Virginia Opossum - HD Mini-Documentary</v>
       </c>
       <c r="AJ101" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK101" t="str">
         <v>https://www.gbif.org/species/2439920</v>
@@ -18715,7 +18715,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM101" t="str">
-        <v>2026-08-01T15:13:22.482Z</v>
+        <v>2026-08-01T16:47:10.924Z</v>
       </c>
       <c r="AN101">
         <v>0.99</v>
@@ -18763,16 +18763,16 @@
         <v>1329</v>
       </c>
       <c r="BC101">
-        <v>4728</v>
+        <v>611</v>
       </c>
       <c r="BD101">
-        <v>3138</v>
+        <v>600</v>
       </c>
       <c r="BE101" t="str">
         <v>4K</v>
       </c>
       <c r="BF101" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG101" t="str">
         <v>rights-free</v>
@@ -18879,13 +18879,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG102" t="str">
-        <v>https://www.youtube.com/watch?v=-0F7iua-37Y</v>
+        <v>https://www.youtube.com/watch?v=VrThTQBhKcU</v>
       </c>
       <c r="AH102" t="str">
-        <v>-0F7iua-37Y</v>
+        <v>VrThTQBhKcU</v>
       </c>
       <c r="AI102" t="str">
-        <v>Animals of Europe 4K - Scenic Wildlife Film With Calming Music</v>
+        <v>Hedgehogs: Secrets Beneath the Spines | 4K Wildlife Documentary</v>
       </c>
       <c r="AJ102" t="str">
         <v>4K</v>
@@ -18897,7 +18897,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM102" t="str">
-        <v>2026-08-01T15:13:24.770Z</v>
+        <v>2026-08-01T16:47:15.553Z</v>
       </c>
       <c r="AN102">
         <v>0.99</v>
@@ -19061,13 +19061,13 @@
         <v>CC0</v>
       </c>
       <c r="AG103" t="str">
-        <v>https://www.youtube.com/watch?v=r_8qzrZY9io</v>
+        <v>https://www.youtube.com/watch?v=i2Ehch3ibkI</v>
       </c>
       <c r="AH103" t="str">
-        <v>r_8qzrZY9io</v>
+        <v>i2Ehch3ibkI</v>
       </c>
       <c r="AI103" t="str">
-        <v>The Tiny Endangered Elephant Shrews of Africa [4K Animal Documentary] | Elephant Shrew | Real Wild</v>
+        <v>Why are ASIAN HOUSE SHREW all lined up? | Leo the Wildlife Ranger Spinoff S3E12 | @mediacorpokto</v>
       </c>
       <c r="AJ103" t="str">
         <v>4K</v>
@@ -19079,7 +19079,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM103" t="str">
-        <v>2026-08-01T15:13:26.648Z</v>
+        <v>2026-08-01T16:40:24.596Z</v>
       </c>
       <c r="AN103">
         <v>0.99</v>
@@ -19237,19 +19237,19 @@
         <v>https://inaturalist-open-data.s3.amazonaws.com/photos/42869530/original.jpeg</v>
       </c>
       <c r="AE104" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:EB1911_Insectivora_%E2%80%94_Fig._3.%E2%80%94Skeleton_of_Mole_(Talpa_europaea).jpg</v>
+        <v>https://www.inaturalist.org/photos/42869530</v>
       </c>
       <c r="AF104" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG104" t="str">
-        <v>https://www.youtube.com/watch?v=-0F7iua-37Y</v>
+        <v>https://www.youtube.com/watch?v=u74iVC_wVek</v>
       </c>
       <c r="AH104" t="str">
-        <v>-0F7iua-37Y</v>
+        <v>u74iVC_wVek</v>
       </c>
       <c r="AI104" t="str">
-        <v>Animals of Europe 4K - Scenic Wildlife Film With Calming Music</v>
+        <v>The Weird and Wonderful Star-Nosed Mole | 4K UHD | Mammals | BBC Earth</v>
       </c>
       <c r="AJ104" t="str">
         <v>4K</v>
@@ -19261,7 +19261,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM104" t="str">
-        <v>2026-08-01T14:58:27.615Z</v>
+        <v>2026-08-01T16:47:24.228Z</v>
       </c>
       <c r="AN104">
         <v>0.99</v>
@@ -19309,16 +19309,16 @@
         <v>1371</v>
       </c>
       <c r="BC104">
-        <v>307</v>
+        <v>1024</v>
       </c>
       <c r="BD104">
-        <v>672</v>
+        <v>768</v>
       </c>
       <c r="BE104" t="str">
         <v/>
       </c>
       <c r="BF104" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG104" t="str">
         <v>rights-free</v>
@@ -19425,13 +19425,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG105" t="str">
-        <v>https://www.youtube.com/watch?v=3dgT8a9f78Q</v>
+        <v>https://www.youtube.com/watch?v=JxFBA267y7A</v>
       </c>
       <c r="AH105" t="str">
-        <v>3dgT8a9f78Q</v>
+        <v>JxFBA267y7A</v>
       </c>
       <c r="AI105" t="str">
-        <v>This African Mammal Always Has Time For a Quick Nap (4K)</v>
+        <v>Rock Hyrax Documentary Shocking Secrets of the Small Animal Related to Elephants Part 2</v>
       </c>
       <c r="AJ105" t="str">
         <v>4K</v>
@@ -19443,7 +19443,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM105" t="str">
-        <v>2026-08-01T13:48:40.736Z</v>
+        <v>2026-08-01T16:47:27.855Z</v>
       </c>
       <c r="AN105">
         <v>0.99</v>
@@ -19607,13 +19607,13 @@
         <v>CC0</v>
       </c>
       <c r="AG106" t="str">
-        <v>https://www.youtube.com/watch?v=uOs5DEB1l1o</v>
+        <v>https://www.youtube.com/watch?v=6JKCbdHVWDs</v>
       </c>
       <c r="AH106" t="str">
-        <v>uOs5DEB1l1o</v>
+        <v>6JKCbdHVWDs</v>
       </c>
       <c r="AI106" t="str">
-        <v>Saving Earth’s Rarest Animals (4K Documentary)</v>
+        <v>The WILDlife of Filmmaking: Hyrax</v>
       </c>
       <c r="AJ106" t="str">
         <v>4K</v>
@@ -19625,7 +19625,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM106" t="str">
-        <v>2026-08-01T15:13:32.868Z</v>
+        <v>2026-08-01T16:47:31.295Z</v>
       </c>
       <c r="AN106">
         <v>0.99</v>
@@ -19783,19 +19783,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/a/a0/Iepure_de_c%C3%A2mp_alerg%C3%A2nd.jpg</v>
       </c>
       <c r="AE107" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Feldhase_(Mai_2024).jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Iepure_de_c%C3%A2mp_alerg%C3%A2nd.jpg</v>
       </c>
       <c r="AF107" t="str">
         <v>CC0</v>
       </c>
       <c r="AG107" t="str">
-        <v>https://www.youtube.com/watch?v=KFCn7QPMZSc</v>
+        <v>https://www.youtube.com/watch?v=396mHypuyaA</v>
       </c>
       <c r="AH107" t="str">
-        <v>KFCn7QPMZSc</v>
+        <v>396mHypuyaA</v>
       </c>
       <c r="AI107" t="str">
-        <v>Hare / Lepus (Haas), filmed in 4K.</v>
+        <v>Secrets of the European Hare: Nature's Swift Survivor</v>
       </c>
       <c r="AJ107" t="str">
         <v>4K</v>
@@ -19807,7 +19807,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM107" t="str">
-        <v>2026-08-01T15:13:35.665Z</v>
+        <v>2026-08-01T16:47:35.272Z</v>
       </c>
       <c r="AN107">
         <v>0.99</v>
@@ -19855,13 +19855,13 @@
         <v>1401</v>
       </c>
       <c r="BC107">
-        <v>3807</v>
+        <v>5184</v>
       </c>
       <c r="BD107">
-        <v>2538</v>
+        <v>3888</v>
       </c>
       <c r="BE107" t="str">
-        <v>Full HD</v>
+        <v>4K</v>
       </c>
       <c r="BF107" t="str">
         <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
@@ -19965,22 +19965,22 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/8/8f/American_pika_Banff_National_Park.jpg</v>
       </c>
       <c r="AE108" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Ochotona_princeps_rockies.JPG</v>
+        <v>https://commons.wikimedia.org/wiki/File:American_pika_Banff_National_Park.jpg</v>
       </c>
       <c r="AF108" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG108" t="str">
-        <v>https://www.youtube.com/watch?v=uOs5DEB1l1o</v>
+        <v>https://www.youtube.com/watch?v=XLUGzXAgiqI</v>
       </c>
       <c r="AH108" t="str">
-        <v>uOs5DEB1l1o</v>
+        <v>XLUGzXAgiqI</v>
       </c>
       <c r="AI108" t="str">
-        <v>Saving Earth’s Rarest Animals (4K Documentary)</v>
+        <v>The Rare and Elusive Pika(full documentary)HD</v>
       </c>
       <c r="AJ108" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK108" t="str">
         <v>https://www.gbif.org/species/2436982</v>
@@ -19989,7 +19989,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM108" t="str">
-        <v>2026-08-01T15:13:37.798Z</v>
+        <v>2026-08-01T16:47:39.515Z</v>
       </c>
       <c r="AN108">
         <v>0.99</v>
@@ -20037,16 +20037,16 @@
         <v>1407</v>
       </c>
       <c r="BC108">
-        <v>1313</v>
+        <v>3504</v>
       </c>
       <c r="BD108">
-        <v>1072</v>
+        <v>2336</v>
       </c>
       <c r="BE108" t="str">
-        <v>HD</v>
+        <v>Full HD</v>
       </c>
       <c r="BF108" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG108" t="str">
         <v>rights-free</v>
@@ -20144,13 +20144,13 @@
         <v/>
       </c>
       <c r="AD109" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/1/15/Macroscelides_brachyrhynchus_-_1700-1880_-_Print_-_Iconographia_Zoologica_-_Special_Collections_University_of_Amsterdam_-_UBA01_IZ20900075.tif</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/d/d8/Elephantulus_brachyrhynchus.jpg</v>
       </c>
       <c r="AE109" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Macroscelides_brachyrhynchus_-_1700-1880_-_Print_-_Iconographia_Zoologica_-_Special_Collections_University_of_Amsterdam_-_UBA01_IZ20900075.tif</v>
+        <v>https://commons.wikimedia.org/wiki/File:Elephantulus_brachyrhynchus.jpg</v>
       </c>
       <c r="AF109" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG109" t="str">
         <v>https://www.youtube.com/watch?v=r_8qzrZY9io</v>
@@ -20171,7 +20171,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM109" t="str">
-        <v>2026-08-01T15:13:39.608Z</v>
+        <v>2026-08-01T16:47:42.182Z</v>
       </c>
       <c r="AN109">
         <v>0.99</v>
@@ -20219,16 +20219,16 @@
         <v>1413</v>
       </c>
       <c r="BC109">
-        <v>3504</v>
+        <v>1536</v>
       </c>
       <c r="BD109">
-        <v>4465</v>
+        <v>2048</v>
       </c>
       <c r="BE109" t="str">
-        <v>4K</v>
+        <v>Full HD</v>
       </c>
       <c r="BF109" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG109" t="str">
         <v>rights-free</v>
@@ -20329,7 +20329,7 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/7/7b/THE_ELEPHANT-_SHREW_OF_ZANZIBAR.png</v>
       </c>
       <c r="AE110" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Rhynchocyon_petersi_one.JPG</v>
+        <v>https://commons.wikimedia.org/wiki/File:THE_ELEPHANT-_SHREW_OF_ZANZIBAR.png</v>
       </c>
       <c r="AF110" t="str">
         <v>Public Domain</v>
@@ -20350,10 +20350,10 @@
         <v>https://www.gbif.org/species/5220100</v>
       </c>
       <c r="AL110" t="str">
-        <v>gbif | wikimedia | youtube</v>
+        <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM110" t="str">
-        <v>2026-08-01T15:13:42.926Z</v>
+        <v>2026-08-01T16:40:30.297Z</v>
       </c>
       <c r="AN110">
         <v>0.99</v>
@@ -20401,10 +20401,10 @@
         <v>1425</v>
       </c>
       <c r="BC110">
-        <v>1095</v>
+        <v>1677</v>
       </c>
       <c r="BD110">
-        <v>822</v>
+        <v>703</v>
       </c>
       <c r="BE110" t="str">
         <v/>
@@ -20517,13 +20517,13 @@
         <v>CC0</v>
       </c>
       <c r="AG111" t="str">
-        <v>https://www.youtube.com/watch?v=MpiHQUCT1Cc</v>
+        <v>https://www.youtube.com/watch?v=gVCCMK-mbEg</v>
       </c>
       <c r="AH111" t="str">
-        <v>MpiHQUCT1Cc</v>
+        <v>gVCCMK-mbEg</v>
       </c>
       <c r="AI111" t="str">
-        <v>Monkeys &amp; Primates 4K - Scenic Wildlife Film With Calming Music</v>
+        <v>🎥 👉Nature Wednesday: Monito del Monte</v>
       </c>
       <c r="AJ111" t="str">
         <v>4K</v>
@@ -20535,7 +20535,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM111" t="str">
-        <v>2026-08-01T15:13:44.868Z</v>
+        <v>2026-08-01T16:47:48.544Z</v>
       </c>
       <c r="AN111">
         <v>0.99</v>
@@ -20693,19 +20693,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/1/1b/Ornithorhynchus_anatinus_254191145.jpg</v>
       </c>
       <c r="AE112" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Platypus_(Ornithorhynchus_anatinus)._First_Description_1799.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Ornithorhynchus_anatinus_254191145.jpg</v>
       </c>
       <c r="AF112" t="str">
         <v>CC0</v>
       </c>
       <c r="AG112" t="str">
-        <v>https://www.youtube.com/watch?v=_ViYFwnX2vM</v>
+        <v>https://www.youtube.com/watch?v=hDVp6o4Z9xM</v>
       </c>
       <c r="AH112" t="str">
-        <v>_ViYFwnX2vM</v>
+        <v>hDVp6o4Z9xM</v>
       </c>
       <c r="AI112" t="str">
-        <v>Hidden Worlds and Wildlife of Australia | Documentary 4K</v>
+        <v>Platypus: The MOST Unique Animal On Earth | 4K Animal Documentary</v>
       </c>
       <c r="AJ112" t="str">
         <v>4K</v>
@@ -20717,7 +20717,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM112" t="str">
-        <v>2026-08-01T15:13:47.995Z</v>
+        <v>2026-08-01T16:47:52.394Z</v>
       </c>
       <c r="AN112">
         <v>0.99</v>
@@ -20765,10 +20765,10 @@
         <v>1437</v>
       </c>
       <c r="BC112">
-        <v>2256</v>
+        <v>2048</v>
       </c>
       <c r="BD112">
-        <v>1135</v>
+        <v>1536</v>
       </c>
       <c r="BE112" t="str">
         <v>Full HD</v>
@@ -20875,19 +20875,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/7/70/Echidna_burningwell.jpg</v>
       </c>
       <c r="AE113" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Tachyglossus_aculeatus_aculeatus_358475387.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Echidna_burningwell.jpg</v>
       </c>
       <c r="AF113" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG113" t="str">
-        <v>https://www.youtube.com/watch?v=3e70z8lrRFU</v>
+        <v>https://www.youtube.com/watch?v=An-z8Q3gMzo</v>
       </c>
       <c r="AH113" t="str">
-        <v>3e70z8lrRFU</v>
+        <v>An-z8Q3gMzo</v>
       </c>
       <c r="AI113" t="str">
-        <v>Short-beaked Echidna on a beach cliff | 4K Nature Relaxation | Unique Australian Mammals</v>
+        <v>Meet the Echidna, an Incredible, Fire-Proof Spiny Anteater</v>
       </c>
       <c r="AJ113" t="str">
         <v>4K</v>
@@ -20899,7 +20899,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM113" t="str">
-        <v>2026-08-01T15:13:49.777Z</v>
+        <v>2026-08-01T16:47:56.123Z</v>
       </c>
       <c r="AN113">
         <v>0.99</v>
@@ -20947,16 +20947,16 @@
         <v>1443</v>
       </c>
       <c r="BC113">
-        <v>2048</v>
+        <v>1808</v>
       </c>
       <c r="BD113">
-        <v>1536</v>
+        <v>1356</v>
       </c>
       <c r="BE113" t="str">
-        <v>Full HD</v>
+        <v>HD</v>
       </c>
       <c r="BF113" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG113" t="str">
         <v>rights-free</v>
@@ -21057,19 +21057,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/8/8f/PSM_V40_D672_The_new_mammal_notoryctes_typhlops.jpg</v>
       </c>
       <c r="AE114" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Notoryctes_typhlops.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:PSM_V40_D672_The_new_mammal_notoryctes_typhlops.jpg</v>
       </c>
       <c r="AF114" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG114" t="str">
-        <v>https://www.youtube.com/watch?v=KPZon5Uokeo</v>
+        <v>https://www.youtube.com/watch?v=u74iVC_wVek</v>
       </c>
       <c r="AH114" t="str">
-        <v>KPZon5Uokeo</v>
+        <v>u74iVC_wVek</v>
       </c>
       <c r="AI114" t="str">
-        <v>The Beautiful Killers of the Tropics | 4k 60p Documentary</v>
+        <v>The Weird and Wonderful Star-Nosed Mole | 4K UHD | Mammals | BBC Earth</v>
       </c>
       <c r="AJ114" t="str">
         <v>4K</v>
@@ -21081,7 +21081,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM114" t="str">
-        <v>2026-08-01T15:13:52.448Z</v>
+        <v>2026-08-01T16:47:59.276Z</v>
       </c>
       <c r="AN114">
         <v>0.99</v>
@@ -21129,13 +21129,13 @@
         <v>1449</v>
       </c>
       <c r="BC114">
-        <v>3835</v>
+        <v>1678</v>
       </c>
       <c r="BD114">
-        <v>2263</v>
+        <v>1845</v>
       </c>
       <c r="BE114" t="str">
-        <v>Full HD</v>
+        <v>HD</v>
       </c>
       <c r="BF114" t="str">
         <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
@@ -21239,19 +21239,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/5/5c/NotoryctesMAD.png</v>
       </c>
       <c r="AE115" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Memoir_(IA_Memoir6Aust).pdf</v>
+        <v>https://commons.wikimedia.org/wiki/File:NotoryctesMAD.png</v>
       </c>
       <c r="AF115" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG115" t="str">
-        <v>https://www.youtube.com/watch?v=uOs5DEB1l1o</v>
+        <v>https://www.youtube.com/watch?v=u74iVC_wVek</v>
       </c>
       <c r="AH115" t="str">
-        <v>uOs5DEB1l1o</v>
+        <v>u74iVC_wVek</v>
       </c>
       <c r="AI115" t="str">
-        <v>Saving Earth’s Rarest Animals (4K Documentary)</v>
+        <v>The Weird and Wonderful Star-Nosed Mole | 4K UHD | Mammals | BBC Earth</v>
       </c>
       <c r="AJ115" t="str">
         <v>4K</v>
@@ -21263,7 +21263,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM115" t="str">
-        <v>2026-08-01T15:13:53.717Z</v>
+        <v>2026-08-01T16:48:02.414Z</v>
       </c>
       <c r="AN115">
         <v>0.99</v>
@@ -21311,10 +21311,10 @@
         <v>1455</v>
       </c>
       <c r="BC115">
-        <v>1108</v>
+        <v>890</v>
       </c>
       <c r="BD115">
-        <v>1475</v>
+        <v>668</v>
       </c>
       <c r="BE115" t="str">
         <v>HD</v>
@@ -21418,13 +21418,13 @@
         <v/>
       </c>
       <c r="AD116" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/5/5d/Perameles_nasuta_-_1700-1880_-_Print_-_Iconographia_Zoologica_-_Special_Collections_University_of_Amsterdam_-_UBA01_IZ20300072.tif</v>
+        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/644502802/original.jpg</v>
       </c>
       <c r="AE116" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Perameles_nasuta_(Harvard_University).JPG</v>
+        <v>https://www.inaturalist.org/photos/644502802</v>
       </c>
       <c r="AF116" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG116" t="str">
         <v>https://www.youtube.com/watch?v=zmf7Bi8Dn0M</v>
@@ -21445,7 +21445,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM116" t="str">
-        <v>2026-08-01T15:13:56.383Z</v>
+        <v>2026-08-01T16:48:06.923Z</v>
       </c>
       <c r="AN116">
         <v>0.99</v>
@@ -21493,16 +21493,16 @@
         <v>1461</v>
       </c>
       <c r="BC116">
-        <v>2222</v>
+        <v>2048</v>
       </c>
       <c r="BD116">
-        <v>1840</v>
+        <v>1152</v>
       </c>
       <c r="BE116" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF116" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG116" t="str">
         <v>rights-free</v>
@@ -21609,13 +21609,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG117" t="str">
-        <v>https://www.youtube.com/watch?v=76y8t2kYHZ0</v>
+        <v>https://www.youtube.com/watch?v=j6xUSWABzUg</v>
       </c>
       <c r="AH117" t="str">
-        <v>76y8t2kYHZ0</v>
+        <v>j6xUSWABzUg</v>
       </c>
       <c r="AI117" t="str">
-        <v>The Ultimate Wildlife Documentary | 150 Stunning Animals in 4K</v>
+        <v>Bilby: Guardian of Australia's Drylands – Animal Documentary</v>
       </c>
       <c r="AJ117" t="str">
         <v>4K</v>
@@ -21627,7 +21627,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM117" t="str">
-        <v>2026-08-01T13:49:07.269Z</v>
+        <v>2026-08-01T16:48:10.821Z</v>
       </c>
       <c r="AN117">
         <v>0.99</v>
@@ -21782,22 +21782,22 @@
         <v/>
       </c>
       <c r="AD118" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/a/a8/Evolucion_del_caballo.png</v>
+        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/12222219/original.jpg</v>
       </c>
       <c r="AE118" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Horse-drawn_sleighs_2012_G1.jpg</v>
+        <v>https://www.inaturalist.org/photos/12222219</v>
       </c>
       <c r="AF118" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG118" t="str">
-        <v>https://www.youtube.com/watch?v=ZDvjrcNjInI</v>
+        <v>https://www.youtube.com/watch?v=KliFN5I_ims</v>
       </c>
       <c r="AH118" t="str">
-        <v>ZDvjrcNjInI</v>
+        <v>KliFN5I_ims</v>
       </c>
       <c r="AI118" t="str">
-        <v>Horses in 4K Ultra HD | Nature | Cinematic Wildlife Documentary</v>
+        <v>Grace &amp; Power: Wild Horses in 4K – Scenic Animal Film with Relaxing Music</v>
       </c>
       <c r="AJ118" t="str">
         <v>4K</v>
@@ -21809,7 +21809,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM118" t="str">
-        <v>2026-08-01T15:14:02.316Z</v>
+        <v>2026-08-01T16:48:16.298Z</v>
       </c>
       <c r="AN118">
         <v>0.99</v>
@@ -21857,16 +21857,16 @@
         <v>1473</v>
       </c>
       <c r="BC118">
-        <v>5184</v>
+        <v>1799</v>
       </c>
       <c r="BD118">
-        <v>3456</v>
+        <v>1166</v>
       </c>
       <c r="BE118" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="BF118" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG118" t="str">
         <v>rights-free</v>
@@ -21967,19 +21967,19 @@
         <v>https://inaturalist-open-data.s3.amazonaws.com/photos/30025794/original.jpeg</v>
       </c>
       <c r="AE119" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Ceratotherium_simum_white_Rhinoceros_blanc_female_MNHN.jpg</v>
+        <v>https://www.inaturalist.org/photos/30025794</v>
       </c>
       <c r="AF119" t="str">
         <v>CC0</v>
       </c>
       <c r="AG119" t="str">
-        <v>https://www.youtube.com/watch?v=NOgl1nW0NtA</v>
+        <v>https://www.youtube.com/watch?v=6x4NjMxbtes</v>
       </c>
       <c r="AH119" t="str">
-        <v>NOgl1nW0NtA</v>
+        <v>6x4NjMxbtes</v>
       </c>
       <c r="AI119" t="str">
-        <v>A Rhino's Life: Survival in the Jaws of Danger | 4K UHD Documentary</v>
+        <v>White Rhinoceros: The Brutal Fight for Survival | 4K Documentary</v>
       </c>
       <c r="AJ119" t="str">
         <v>4K</v>
@@ -21991,7 +21991,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM119" t="str">
-        <v>2026-08-01T14:58:56.858Z</v>
+        <v>2026-08-01T16:48:20.927Z</v>
       </c>
       <c r="AN119">
         <v>0.99</v>
@@ -22039,16 +22039,16 @@
         <v>1479</v>
       </c>
       <c r="BC119">
-        <v>2700</v>
+        <v>800</v>
       </c>
       <c r="BD119">
-        <v>2580</v>
+        <v>600</v>
       </c>
       <c r="BE119" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF119" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG119" t="str">
         <v>rights-free</v>
@@ -22146,10 +22146,10 @@
         <v/>
       </c>
       <c r="AD120" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/1/13/Stamp_of_Indonesia_-_1958_-_Colnect_231775_-_Sunda_Pangolin_Manis_javanica.jpeg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/7/7a/Stamp_of_Indonesia_-_1958_-_Colnect_231774_-_Sunda_Pangolin_Manis_javanica.jpeg</v>
       </c>
       <c r="AE120" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Stamp_of_Indonesia_-_1956_-_Colnect_231773_-_Sunda_Pangolin_Manis_javanica.jpeg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Stamp_of_Indonesia_-_1958_-_Colnect_231774_-_Sunda_Pangolin_Manis_javanica.jpeg</v>
       </c>
       <c r="AF120" t="str">
         <v>Public Domain</v>
@@ -22173,7 +22173,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM120" t="str">
-        <v>2026-08-01T15:14:06.471Z</v>
+        <v>2026-08-01T16:48:24.661Z</v>
       </c>
       <c r="AN120">
         <v>0.99</v>
@@ -22337,13 +22337,13 @@
         <v>CC0</v>
       </c>
       <c r="AG121" t="str">
-        <v>https://www.youtube.com/watch?v=FZ7Tf87QpIM</v>
+        <v>https://www.youtube.com/watch?v=y2VgZyNfcFo</v>
       </c>
       <c r="AH121" t="str">
-        <v>FZ7Tf87QpIM</v>
+        <v>y2VgZyNfcFo</v>
       </c>
       <c r="AI121" t="str">
-        <v>Relaxing Walk in the Amazon: Golden Hour Jungle Floor | Giant Anteater 4K Nature ASMR</v>
+        <v>Giant Anteater Documentary</v>
       </c>
       <c r="AJ121" t="str">
         <v>4K</v>
@@ -22355,7 +22355,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM121" t="str">
-        <v>2026-08-01T15:14:10.434Z</v>
+        <v>2026-08-01T16:48:29.031Z</v>
       </c>
       <c r="AN121">
         <v>0.99</v>
@@ -22510,22 +22510,22 @@
         <v/>
       </c>
       <c r="AD122" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/8/8a/Linne%27s_two-toed_sloth_in_Drusillas_Park_2024-12-18.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/7/7b/Faultier.jpg</v>
       </c>
       <c r="AE122" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Choloepus_didactylus_2_-_Buffalo_Zoo.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Faultier.jpg</v>
       </c>
       <c r="AF122" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG122" t="str">
-        <v>https://www.youtube.com/watch?v=vit8V2lWFek</v>
+        <v>https://www.youtube.com/watch?v=84z5hAT8OBQ</v>
       </c>
       <c r="AH122" t="str">
-        <v>vit8V2lWFek</v>
+        <v>84z5hAT8OBQ</v>
       </c>
       <c r="AI122" t="str">
-        <v>Nature documentary A tiny orphaned Sloth Named Velcro full HD english subtitles 2</v>
+        <v>Two-Toed Sloths Unveiled: The Ultimate Guide to Nature's Delightful Dose of Slow Motion!</v>
       </c>
       <c r="AJ122" t="str">
         <v>HD</v>
@@ -22537,7 +22537,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM122" t="str">
-        <v>2026-08-01T15:14:12.928Z</v>
+        <v>2026-08-01T16:48:34.001Z</v>
       </c>
       <c r="AN122">
         <v>0.99</v>
@@ -22585,10 +22585,10 @@
         <v>1509</v>
       </c>
       <c r="BC122">
-        <v>2679</v>
+        <v>1984</v>
       </c>
       <c r="BD122">
-        <v>2304</v>
+        <v>1488</v>
       </c>
       <c r="BE122" t="str">
         <v>Full HD</v>
@@ -22695,19 +22695,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/3/33/Mus_musculus_57127864.jpg</v>
       </c>
       <c r="AE123" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:House_mouse_(Mus_musculus)_2766.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Mus_musculus_57127864.jpg</v>
       </c>
       <c r="AF123" t="str">
         <v>CC0</v>
       </c>
       <c r="AG123" t="str">
-        <v>https://www.youtube.com/watch?v=dF1X13Oo0pg</v>
+        <v>https://www.youtube.com/watch?v=X1Z70-M2rSk</v>
       </c>
       <c r="AH123" t="str">
-        <v>dF1X13Oo0pg</v>
+        <v>X1Z70-M2rSk</v>
       </c>
       <c r="AI123" t="str">
-        <v>10 Hours of Epic 4K Wildlife Documentary: Crocodiles Buffaloes &amp; Nature’s Greatest Battles #wildlife</v>
+        <v>Wildlife Chronicles: Killer Mouse (Grasshopper Mouse full documentary)</v>
       </c>
       <c r="AJ123" t="str">
         <v>4K</v>
@@ -22719,7 +22719,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM123" t="str">
-        <v>2026-08-01T15:14:16.317Z</v>
+        <v>2026-08-01T16:48:37.935Z</v>
       </c>
       <c r="AN123">
         <v>0.99</v>
@@ -22767,10 +22767,10 @@
         <v>1563</v>
       </c>
       <c r="BC123">
-        <v>2592</v>
+        <v>1536</v>
       </c>
       <c r="BD123">
-        <v>1944</v>
+        <v>2048</v>
       </c>
       <c r="BE123" t="str">
         <v>Full HD</v>
@@ -22877,19 +22877,19 @@
         <v>https://inaturalist-open-data.s3.amazonaws.com/photos/462748811/original.jpeg</v>
       </c>
       <c r="AE124" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Rattus_norvegicus_74_Sunbury_Street_Geebung_P1012741.jpg</v>
+        <v>https://www.inaturalist.org/photos/462748811</v>
       </c>
       <c r="AF124" t="str">
         <v>CC0</v>
       </c>
       <c r="AG124" t="str">
-        <v>https://www.youtube.com/watch?v=7VJMYoUvKyY</v>
+        <v>https://www.youtube.com/watch?v=vPEXGr47o8c</v>
       </c>
       <c r="AH124" t="str">
-        <v>7VJMYoUvKyY</v>
+        <v>vPEXGr47o8c</v>
       </c>
       <c r="AI124" t="str">
-        <v>Survival of the Smallest 🐁 | The Untold Life Story of a Mouse | 4K Wildlife Documentary</v>
+        <v>A Tale Of Brown Rats</v>
       </c>
       <c r="AJ124" t="str">
         <v>4K</v>
@@ -22901,7 +22901,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM124" t="str">
-        <v>2026-08-01T14:59:06.946Z</v>
+        <v>2026-08-01T16:48:42.988Z</v>
       </c>
       <c r="AN124">
         <v>0.99</v>
@@ -22949,16 +22949,16 @@
         <v>1569</v>
       </c>
       <c r="BC124">
-        <v>2756</v>
+        <v>2048</v>
       </c>
       <c r="BD124">
-        <v>1837</v>
+        <v>2048</v>
       </c>
       <c r="BE124" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF124" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG124" t="str">
         <v>rights-free</v>
@@ -23059,19 +23059,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/4/41/Manatee_with_calf.PD.jpg</v>
       </c>
       <c r="AE125" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Manatee_trichechus_manatus_latirostris_close_up_underwater_photo.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Manatee_with_calf.PD.jpg</v>
       </c>
       <c r="AF125" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG125" t="str">
-        <v>https://www.youtube.com/watch?v=7ZhdXgRfxHI</v>
+        <v>https://www.youtube.com/watch?v=09zVrUc4pec</v>
       </c>
       <c r="AH125" t="str">
-        <v>7ZhdXgRfxHI</v>
+        <v>09zVrUc4pec</v>
       </c>
       <c r="AI125" t="str">
-        <v>Incredible 4K Nature Scenes Narrated By David Attenborough | BBC Earth</v>
+        <v>Manatees and Dugongs in Danger | Blue Realm | Free Documentary Nature</v>
       </c>
       <c r="AJ125" t="str">
         <v>4K</v>
@@ -23083,7 +23083,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM125" t="str">
-        <v>2026-08-01T15:14:20.871Z</v>
+        <v>2026-08-01T16:48:47.041Z</v>
       </c>
       <c r="AN125">
         <v>0.99</v>
@@ -23131,10 +23131,10 @@
         <v>1587</v>
       </c>
       <c r="BC125">
-        <v>2008</v>
+        <v>3658</v>
       </c>
       <c r="BD125">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="BE125" t="str">
         <v>Full HD</v>
@@ -23241,19 +23241,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/1/1b/Artis_heeft_weer_aardvarkens_na_27_jaar%2C_Bestanddeelnr_915-3764.jpg</v>
       </c>
       <c r="AE126" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Orycteropus_afer_ssp._afer.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Artis_heeft_weer_aardvarkens_na_27_jaar,_Bestanddeelnr_915-3764.jpg</v>
       </c>
       <c r="AF126" t="str">
         <v>CC0</v>
       </c>
       <c r="AG126" t="str">
-        <v>https://www.youtube.com/watch?v=2OitEHoPpTE</v>
+        <v>https://www.youtube.com/watch?v=7bf-AIhVk3A</v>
       </c>
       <c r="AH126" t="str">
-        <v>2OitEHoPpTE</v>
+        <v>7bf-AIhVk3A</v>
       </c>
       <c r="AI126" t="str">
-        <v>Pangolins and Aardvarks Search for Termites | 4K UHD | Seven Worlds One Planet | BBC Earth</v>
+        <v>Secret Creatures: Africa's earth pig, the Aardvark. #wildlife</v>
       </c>
       <c r="AJ126" t="str">
         <v>4K</v>
@@ -23265,7 +23265,7 @@
         <v>gbif | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM126" t="str">
-        <v>2026-08-01T15:14:23.281Z</v>
+        <v>2026-08-01T16:48:50.860Z</v>
       </c>
       <c r="AN126">
         <v>0.99</v>
@@ -23313,10 +23313,10 @@
         <v>1599</v>
       </c>
       <c r="BC126">
-        <v>2048</v>
+        <v>2619</v>
       </c>
       <c r="BD126">
-        <v>1536</v>
+        <v>2620</v>
       </c>
       <c r="BE126" t="str">
         <v>Full HD</v>
@@ -23423,7 +23423,7 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/7/77/Big-eared-townsend-fledermaus.jpg</v>
       </c>
       <c r="AE127" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Haeckel_Chiroptera.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Big-eared-townsend-fledermaus.jpg</v>
       </c>
       <c r="AF127" t="str">
         <v>Public Domain</v>
@@ -23447,7 +23447,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM127" t="str">
-        <v>2026-08-01T15:14:25.918Z</v>
+        <v>2026-08-01T16:48:55.074Z</v>
       </c>
       <c r="AN127">
         <v>0.94</v>
@@ -23495,10 +23495,10 @@
         <v>1631</v>
       </c>
       <c r="BC127">
-        <v>2314</v>
+        <v>617</v>
       </c>
       <c r="BD127">
-        <v>3220</v>
+        <v>375</v>
       </c>
       <c r="BE127" t="str">
         <v>Full HD</v>
@@ -23611,13 +23611,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG128" t="str">
-        <v>https://www.youtube.com/watch?v=J3dYjV1wqV0</v>
+        <v>https://www.youtube.com/watch?v=s-U2nvZb_Rs</v>
       </c>
       <c r="AH128" t="str">
-        <v>J3dYjV1wqV0</v>
+        <v>s-U2nvZb_Rs</v>
       </c>
       <c r="AI128" t="str">
-        <v>Tasmania Documentary 4K | Wildlife | Australia Landscapes and Nature | Original Documentary</v>
+        <v>Dasyuromorphia</v>
       </c>
       <c r="AJ128" t="str">
         <v>4K</v>
@@ -23629,7 +23629,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM128" t="str">
-        <v>2026-08-01T13:49:49.919Z</v>
+        <v>2026-08-01T16:48:58.589Z</v>
       </c>
       <c r="AN128">
         <v>0.94</v>
@@ -23793,13 +23793,13 @@
         <v>CC0</v>
       </c>
       <c r="AG129" t="str">
-        <v>https://www.youtube.com/watch?v=JoDXDbRR2U4</v>
+        <v>https://www.youtube.com/watch?v=lsUwdsYu_7I</v>
       </c>
       <c r="AH129" t="str">
-        <v>JoDXDbRR2U4</v>
+        <v>lsUwdsYu_7I</v>
       </c>
       <c r="AI129" t="str">
-        <v>DOCUMENTARY OF BEAUTIFUL WILDLIFE 4K ULTRA HD</v>
+        <v>Order Didelphimorphia</v>
       </c>
       <c r="AJ129" t="str">
         <v>4K</v>
@@ -23811,7 +23811,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM129" t="str">
-        <v>2026-08-01T13:49:57.508Z</v>
+        <v>2026-08-01T16:49:03.779Z</v>
       </c>
       <c r="AN129">
         <v>0.94</v>
@@ -23969,19 +23969,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/9/9a/Don%27t_feed_bread_to_bandicoots%2C_Armadale%2C_WA%2C_Australia.jpg</v>
       </c>
       <c r="AE130" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Bandicoot.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Don%27t_feed_bread_to_bandicoots,_Armadale,_WA,_Australia.jpg</v>
       </c>
       <c r="AF130" t="str">
-        <v>Public Domain</v>
+        <v>CC0</v>
       </c>
       <c r="AG130" t="str">
-        <v>https://www.youtube.com/watch?v=hicGF5s51k8</v>
+        <v>https://www.youtube.com/watch?v=0-chLC9ERi4</v>
       </c>
       <c r="AH130" t="str">
-        <v>hicGF5s51k8</v>
+        <v>0-chLC9ERi4</v>
       </c>
       <c r="AI130" t="str">
-        <v>Amazon's Hidden Predators Wildlife Documentary in 4K Ultra HD</v>
+        <v>Zool 4640 Monotremes &amp; Marsupials Lab - Video 4, Peramelemorphia</v>
       </c>
       <c r="AJ130" t="str">
         <v>4K</v>
@@ -23993,7 +23993,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM130" t="str">
-        <v>2026-08-01T15:14:32.974Z</v>
+        <v>2026-08-01T16:49:07.299Z</v>
       </c>
       <c r="AN130">
         <v>0.94</v>
@@ -24041,16 +24041,16 @@
         <v>1667</v>
       </c>
       <c r="BC130">
-        <v>3039</v>
+        <v>3456</v>
       </c>
       <c r="BD130">
-        <v>2014</v>
+        <v>3456</v>
       </c>
       <c r="BE130" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF130" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG130" t="str">
         <v>rights-free</v>
@@ -24151,19 +24151,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/3/38/Meyers_b9_s0850a.jpg</v>
       </c>
       <c r="AE131" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:A_hand-book_to_the_marsupialia_and_monotremata_(Plate_XVI)_(6008352459).jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Meyers_b9_s0850a.jpg</v>
       </c>
       <c r="AF131" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG131" t="str">
-        <v>https://www.youtube.com/watch?v=pJxeyK7it0o</v>
+        <v>https://www.youtube.com/watch?v=elWxvTt684o</v>
       </c>
       <c r="AH131" t="str">
-        <v>pJxeyK7it0o</v>
+        <v>elWxvTt684o</v>
       </c>
       <c r="AI131" t="str">
-        <v>Breathtaking Nature in 4K | BBC Earth</v>
+        <v>MONOTREMES: The Mammalian Enigmas | Mammalia Ep1 - Monotremata | The Platypus &amp; Echidnas</v>
       </c>
       <c r="AJ131" t="str">
         <v>4K</v>
@@ -24175,7 +24175,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM131" t="str">
-        <v>2026-08-01T15:14:35.352Z</v>
+        <v>2026-08-01T16:49:10.954Z</v>
       </c>
       <c r="AN131">
         <v>0.94</v>
@@ -24223,10 +24223,10 @@
         <v>1673</v>
       </c>
       <c r="BC131">
-        <v>3426</v>
+        <v>2309</v>
       </c>
       <c r="BD131">
-        <v>2136</v>
+        <v>3569</v>
       </c>
       <c r="BE131" t="str">
         <v>Full HD</v>
@@ -24330,22 +24330,22 @@
         <v/>
       </c>
       <c r="AD132" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/4/4c/Eusthenopteron_Foordi_Fossile.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/c/c7/NIE_1905_Rhizopoda_-_Eusthenopteron_Foordi.jpg</v>
       </c>
       <c r="AE132" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Eusthenopteron_Foordi_Fossile.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:NIE_1905_Rhizopoda_-_Eusthenopteron_Foordi.jpg</v>
       </c>
       <c r="AF132" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG132" t="str">
-        <v>https://www.youtube.com/watch?v=GK1ll8e017k</v>
+        <v>https://www.youtube.com/watch?v=Xze0T6j1Trc</v>
       </c>
       <c r="AH132" t="str">
-        <v>GK1ll8e017k</v>
+        <v>Xze0T6j1Trc</v>
       </c>
       <c r="AI132" t="str">
-        <v>4K Ostrich the Flightless Bird - African Wildlife Documentary Film with Narration</v>
+        <v>Hyneria and Eusthenopteron</v>
       </c>
       <c r="AJ132" t="str">
         <v>4K</v>
@@ -24357,7 +24357,7 @@
         <v>gbif | legacy-observation | wikipedia-vi | wikimedia | youtube</v>
       </c>
       <c r="AM132" t="str">
-        <v>2026-08-01T13:50:05.262Z</v>
+        <v>2026-08-01T16:49:13.979Z</v>
       </c>
       <c r="AN132">
         <v>0.99</v>
@@ -24405,10 +24405,10 @@
         <v>1715</v>
       </c>
       <c r="BC132">
-        <v>713</v>
+        <v>593</v>
       </c>
       <c r="BD132">
-        <v>468</v>
+        <v>415</v>
       </c>
       <c r="BE132" t="str">
         <v/>
@@ -24515,19 +24515,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/0/01/Ophthalmosaurus_icenius_coracoid_and_scapular_fossils_NHMUK_R2133.png</v>
       </c>
       <c r="AE133" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Ophthalmosaurus_Scale.svg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Ophthalmosaurus_icenius_coracoid_and_scapular_fossils_NHMUK_R2133.png</v>
       </c>
       <c r="AF133" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG133" t="str">
-        <v>https://www.youtube.com/watch?v=WI4yGLk1_F8</v>
+        <v>https://www.youtube.com/watch?v=_XF3e5KPOMg</v>
       </c>
       <c r="AH133" t="str">
-        <v>WI4yGLk1_F8</v>
+        <v>_XF3e5KPOMg</v>
       </c>
       <c r="AI133" t="str">
-        <v>Ocean Wildlife | The Hidden Kingdoms of Marine Life Revealed | 4K Documentary</v>
+        <v>Walking With Dinosaurs [1999] - Ophthalmosaurus Screen Time</v>
       </c>
       <c r="AJ133" t="str">
         <v>4K</v>
@@ -24539,7 +24539,7 @@
         <v>gbif | legacy-observation | wikipedia-vi | wikimedia | wikidata | youtube</v>
       </c>
       <c r="AM133" t="str">
-        <v>2026-08-01T15:14:39.221Z</v>
+        <v>2026-08-01T16:49:16.845Z</v>
       </c>
       <c r="AN133">
         <v>0.99</v>
@@ -24587,10 +24587,10 @@
         <v>1751</v>
       </c>
       <c r="BC133">
-        <v>2002</v>
+        <v>1456</v>
       </c>
       <c r="BD133">
-        <v>1283</v>
+        <v>2378</v>
       </c>
       <c r="BE133" t="str">
         <v>Full HD</v>
@@ -24697,19 +24697,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/c/cd/Plesiosaur_on_land.jpg</v>
       </c>
       <c r="AE134" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Plesiosaurus_dolichodeirus.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Plesiosaur_on_land.jpg</v>
       </c>
       <c r="AF134" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG134" t="str">
-        <v>https://www.youtube.com/watch?v=6L_860nWMwA</v>
+        <v>https://www.youtube.com/watch?v=ynSFzhD5CRw</v>
       </c>
       <c r="AH134" t="str">
-        <v>6L_860nWMwA</v>
+        <v>ynSFzhD5CRw</v>
       </c>
       <c r="AI134" t="str">
-        <v>Planet Dinosaur - A Dinosaur Documentary [4k]</v>
+        <v>A 100 Million-Year-Old Ocean Battle | Kronosaurus vs Plesiosaurus</v>
       </c>
       <c r="AJ134" t="str">
         <v>4K</v>
@@ -24721,7 +24721,7 @@
         <v>gbif | legacy-observation | wikipedia-vi | wikimedia | wikidata | youtube</v>
       </c>
       <c r="AM134" t="str">
-        <v>2026-08-01T15:14:41.215Z</v>
+        <v>2026-08-01T16:49:20.003Z</v>
       </c>
       <c r="AN134">
         <v>0.99</v>
@@ -24769,10 +24769,10 @@
         <v>1757</v>
       </c>
       <c r="BC134">
-        <v>3505</v>
+        <v>826</v>
       </c>
       <c r="BD134">
-        <v>1475</v>
+        <v>476</v>
       </c>
       <c r="BE134" t="str">
         <v>Full HD</v>
@@ -24879,19 +24879,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/d/d9/Brachiosaurus_DB.jpg</v>
       </c>
       <c r="AE135" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Brachiosaurus_vertebra_anatomy_annotated-ru.png</v>
+        <v>https://commons.wikimedia.org/wiki/File:Brachiosaurus_DB.jpg</v>
       </c>
       <c r="AF135" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG135" t="str">
-        <v>https://www.youtube.com/watch?v=P-5b8-ozvLM</v>
+        <v>https://www.youtube.com/watch?v=cu3l8V_qx98</v>
       </c>
       <c r="AH135" t="str">
-        <v>P-5b8-ozvLM</v>
+        <v>cu3l8V_qx98</v>
       </c>
       <c r="AI135" t="str">
-        <v>What Earth Actually Looked Like When Dinosaurs Ruled It | 4k Documentary</v>
+        <v>Brachiosaurus: One Of The LARGEST Animals to Ever Exist | Dinosaur Documentary</v>
       </c>
       <c r="AJ135" t="str">
         <v>4K</v>
@@ -24903,7 +24903,7 @@
         <v>gbif | legacy-observation | wikipedia-vi | wikimedia | wikidata | youtube</v>
       </c>
       <c r="AM135" t="str">
-        <v>2026-08-01T15:14:43.341Z</v>
+        <v>2026-08-01T16:49:23.243Z</v>
       </c>
       <c r="AN135">
         <v>0.99</v>
@@ -24951,13 +24951,13 @@
         <v>1769</v>
       </c>
       <c r="BC135">
-        <v>2143</v>
+        <v>1959</v>
       </c>
       <c r="BD135">
-        <v>2865</v>
+        <v>1024</v>
       </c>
       <c r="BE135" t="str">
-        <v>Full HD</v>
+        <v>HD</v>
       </c>
       <c r="BF135" t="str">
         <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
@@ -25067,13 +25067,13 @@
         <v>Public Domain</v>
       </c>
       <c r="AG136" t="str">
-        <v>https://www.youtube.com/watch?v=-Mjl8gDev9I</v>
+        <v>https://www.youtube.com/watch?v=8DY7xTrrMTQ</v>
       </c>
       <c r="AH136" t="str">
-        <v>-Mjl8gDev9I</v>
+        <v>8DY7xTrrMTQ</v>
       </c>
       <c r="AI136" t="str">
-        <v>Planet Dinosaur - A Dinosaur Documentary [4K]</v>
+        <v>Diplodocus: The Dinosaur with a Super Sonic Whip for a Tail | Dinosaur Documentary</v>
       </c>
       <c r="AJ136" t="str">
         <v>4K</v>
@@ -25085,7 +25085,7 @@
         <v>gbif | legacy-observation | wikimedia | youtube</v>
       </c>
       <c r="AM136" t="str">
-        <v>2026-08-01T13:50:27.850Z</v>
+        <v>2026-08-01T16:49:26.629Z</v>
       </c>
       <c r="AN136">
         <v>0.99</v>
@@ -25243,19 +25243,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/8/8e/Archaeopteryx_skeleton%2C_from_Abel%2C_O._%281919%29._Die_St%C3%A4mme_der_Wirbeltiere.jpg</v>
       </c>
       <c r="AE137" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Archaeopteryx_lithographica_paris.JPG</v>
+        <v>https://commons.wikimedia.org/wiki/File:Archaeopteryx_skeleton,_from_Abel,_O._(1919)._Die_St%C3%A4mme_der_Wirbeltiere.jpg</v>
       </c>
       <c r="AF137" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG137" t="str">
-        <v>https://www.youtube.com/watch?v=P-5b8-ozvLM</v>
+        <v>https://www.youtube.com/watch?v=FKoXlvnl_TA</v>
       </c>
       <c r="AH137" t="str">
-        <v>P-5b8-ozvLM</v>
+        <v>FKoXlvnl_TA</v>
       </c>
       <c r="AI137" t="str">
-        <v>What Earth Actually Looked Like When Dinosaurs Ruled It | 4k Documentary</v>
+        <v>ARCHAEOPTERYX - The Dinosaur-Toothed Bird That Rewrote Evolutionary History | Science Documentary</v>
       </c>
       <c r="AJ137" t="str">
         <v>4K</v>
@@ -25267,7 +25267,7 @@
         <v>gbif | wikipedia-vi | wikimedia | youtube</v>
       </c>
       <c r="AM137" t="str">
-        <v>2026-08-01T15:14:47.182Z</v>
+        <v>2026-08-01T16:49:30.294Z</v>
       </c>
       <c r="AN137">
         <v>0.99</v>
@@ -25315,10 +25315,10 @@
         <v>1787</v>
       </c>
       <c r="BC137">
-        <v>1430</v>
+        <v>796</v>
       </c>
       <c r="BD137">
-        <v>1900</v>
+        <v>582</v>
       </c>
       <c r="BE137" t="str">
         <v>HD</v>
@@ -25422,22 +25422,22 @@
         <v/>
       </c>
       <c r="AD138" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/9/9c/Schilderij_van_L%C3%A9on_Becker.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/b/be/Iguanodon_skeletal_mounts%2C_from_Abel%2C_O._%281919%29._Die_St%C3%A4mme_der_Wirbeltiere.jpg</v>
       </c>
       <c r="AE138" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Iguanodon_bernissartensis_skull.JPG</v>
+        <v>https://commons.wikimedia.org/wiki/File:Iguanodon_skeletal_mounts,_from_Abel,_O._(1919)._Die_St%C3%A4mme_der_Wirbeltiere.jpg</v>
       </c>
       <c r="AF138" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG138" t="str">
-        <v>https://www.youtube.com/watch?v=NB22eLacQMM</v>
+        <v>https://www.youtube.com/watch?v=6VUUGydxTvI</v>
       </c>
       <c r="AH138" t="str">
-        <v>NB22eLacQMM</v>
+        <v>6VUUGydxTvI</v>
       </c>
       <c r="AI138" t="str">
-        <v>🦖 Realistic Dinosaur World in 4K | Relaxing Nature and Wildlife Documentary</v>
+        <v>Dead-End Canyon: An Iguanodon Father's 1v15 Battle for Survival – 4K Ultra HD</v>
       </c>
       <c r="AJ138" t="str">
         <v>4K</v>
@@ -25449,7 +25449,7 @@
         <v>gbif | legacy-observation | wikipedia-vi | wikimedia | wikidata | youtube</v>
       </c>
       <c r="AM138" t="str">
-        <v>2026-08-01T15:14:49.076Z</v>
+        <v>2026-08-01T16:49:33.769Z</v>
       </c>
       <c r="AN138">
         <v>0.99</v>
@@ -25497,10 +25497,10 @@
         <v>1793</v>
       </c>
       <c r="BC138">
-        <v>2048</v>
+        <v>843</v>
       </c>
       <c r="BD138">
-        <v>1536</v>
+        <v>1029</v>
       </c>
       <c r="BE138" t="str">
         <v>Full HD</v>
@@ -25604,25 +25604,25 @@
         <v/>
       </c>
       <c r="AD139" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/b/b1/Spinosaurus_jaw%2C_from_Abel%2C_O._%281919%29._Die_St%C3%A4mme_der_Wirbeltiere.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/3/3b/Spinosaurus_dorsal_vertebra%2C_from_Abel%2C_O._%281919%29._Die_St%C3%A4mme_der_Wirbeltiere.jpg</v>
       </c>
       <c r="AE139" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Spinosaurus_Aegyptiacus_%E2%99%82.png</v>
+        <v>https://commons.wikimedia.org/wiki/File:Spinosaurus_dorsal_vertebra,_from_Abel,_O._(1919)._Die_St%C3%A4mme_der_Wirbeltiere.jpg</v>
       </c>
       <c r="AF139" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG139" t="str">
-        <v>https://www.youtube.com/watch?v=-Mjl8gDev9I</v>
+        <v>https://www.youtube.com/watch?v=-6mNebnOMdM</v>
       </c>
       <c r="AH139" t="str">
-        <v>-Mjl8gDev9I</v>
+        <v>-6mNebnOMdM</v>
       </c>
       <c r="AI139" t="str">
-        <v>Planet Dinosaur - A Dinosaur Documentary [4K]</v>
+        <v>National Geographic - Spinosaurus Dinosaur Bigger Than T. Rex - New Documentary HD 2018</v>
       </c>
       <c r="AJ139" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK139" t="str">
         <v>https://www.gbif.org/species/4967112</v>
@@ -25631,7 +25631,7 @@
         <v>gbif | legacy-observation | wikipedia-vi | wikimedia | wikidata | youtube</v>
       </c>
       <c r="AM139" t="str">
-        <v>2026-08-01T15:14:50.951Z</v>
+        <v>2026-08-01T16:49:37.174Z</v>
       </c>
       <c r="AN139">
         <v>0.99</v>
@@ -25679,16 +25679,16 @@
         <v>1805</v>
       </c>
       <c r="BC139">
-        <v>883</v>
+        <v>401</v>
       </c>
       <c r="BD139">
-        <v>548</v>
+        <v>1060</v>
       </c>
       <c r="BE139" t="str">
         <v/>
       </c>
       <c r="BF139" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG139" t="str">
         <v>rights-free</v>
@@ -25786,22 +25786,22 @@
         <v/>
       </c>
       <c r="AD140" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/9/9b/Phdinoleatherpic.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/2/23/Pteranodon_pair%2C_from_Osborn%2C_H._F._%281917%29._The_origin_and_evolution_of_life%2C_on_the_theory_of_action%2C_reaction_and_interaction_of_energy.jpg</v>
       </c>
       <c r="AE140" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Pteranodon_longiceps_skulls.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Pteranodon_pair,_from_Osborn,_H._F._(1917)._The_origin_and_evolution_of_life,_on_the_theory_of_action,_reaction_and_interaction_of_energy.jpg</v>
       </c>
       <c r="AF140" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG140" t="str">
-        <v>https://www.youtube.com/watch?v=-Mjl8gDev9I</v>
+        <v>https://www.youtube.com/watch?v=Us50o5ftgR8</v>
       </c>
       <c r="AH140" t="str">
-        <v>-Mjl8gDev9I</v>
+        <v>Us50o5ftgR8</v>
       </c>
       <c r="AI140" t="str">
-        <v>Planet Dinosaur - A Dinosaur Documentary [4K]</v>
+        <v>🦅 Reign of Pteranodon – Lords of the Ancient Skies | Full Documentary 4K</v>
       </c>
       <c r="AJ140" t="str">
         <v>4K</v>
@@ -25813,7 +25813,7 @@
         <v>gbif | legacy-observation | wikipedia-vi | wikimedia | wikidata | youtube</v>
       </c>
       <c r="AM140" t="str">
-        <v>2026-08-01T15:14:52.896Z</v>
+        <v>2026-08-01T16:49:41.128Z</v>
       </c>
       <c r="AN140">
         <v>0.99</v>
@@ -25861,10 +25861,10 @@
         <v>1811</v>
       </c>
       <c r="BC140">
-        <v>1253</v>
+        <v>502</v>
       </c>
       <c r="BD140">
-        <v>827</v>
+        <v>325</v>
       </c>
       <c r="BE140" t="str">
         <v/>
@@ -25971,7 +25971,7 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/e/e7/Gfp-quetzalcaotlus_white_background.jpg</v>
       </c>
       <c r="AE141" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Quetzalcoatlus07.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Gfp-quetzalcaotlus_white_background.jpg</v>
       </c>
       <c r="AF141" t="str">
         <v>Public Domain</v>
@@ -25995,7 +25995,7 @@
         <v>gbif | legacy-observation | wikipedia-vi | wikimedia | wikidata | youtube</v>
       </c>
       <c r="AM141" t="str">
-        <v>2026-08-01T15:14:54.649Z</v>
+        <v>2026-08-01T16:49:44.499Z</v>
       </c>
       <c r="AN141">
         <v>0.99</v>
@@ -26043,16 +26043,16 @@
         <v>1817</v>
       </c>
       <c r="BC141">
-        <v>947</v>
+        <v>2232</v>
       </c>
       <c r="BD141">
-        <v>579</v>
+        <v>2700</v>
       </c>
       <c r="BE141" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF141" t="str">
-        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
+        <v>https://web.archive.org/web/20230926203737/https://creativecommons.org/licenses/publicdomain/</v>
       </c>
       <c r="BG141" t="str">
         <v>rights-free</v>
@@ -26153,19 +26153,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/2/2f/Parasaurolophus_Scale.svg</v>
       </c>
       <c r="AE142" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Parasaurolophus_walkeri_-_University_of_California_Museum_of_Paleontology_-_Berkeley,_CA_-_DSC04691.JPG</v>
+        <v>https://commons.wikimedia.org/wiki/File:Parasaurolophus_Scale.svg</v>
       </c>
       <c r="AF142" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG142" t="str">
-        <v>https://www.youtube.com/watch?v=-Mjl8gDev9I</v>
+        <v>https://www.youtube.com/watch?v=JERAE-68gcQ</v>
       </c>
       <c r="AH142" t="str">
-        <v>-Mjl8gDev9I</v>
+        <v>JERAE-68gcQ</v>
       </c>
       <c r="AI142" t="str">
-        <v>Planet Dinosaur - A Dinosaur Documentary [4K]</v>
+        <v>Parasaurolophus: Hunted Giants of the Cretaceous | 4K Documentary</v>
       </c>
       <c r="AJ142" t="str">
         <v>4K</v>
@@ -26177,7 +26177,7 @@
         <v>gbif | legacy-observation | wikipedia-vi | wikimedia | wikidata | youtube</v>
       </c>
       <c r="AM142" t="str">
-        <v>2026-08-01T15:14:57.153Z</v>
+        <v>2026-08-01T16:49:49.161Z</v>
       </c>
       <c r="AN142">
         <v>0.99</v>
@@ -26225,16 +26225,16 @@
         <v>1823</v>
       </c>
       <c r="BC142">
-        <v>5472</v>
+        <v>6027</v>
       </c>
       <c r="BD142">
-        <v>3648</v>
+        <v>1497</v>
       </c>
       <c r="BE142" t="str">
-        <v>4K</v>
+        <v>Full HD</v>
       </c>
       <c r="BF142" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG142" t="str">
         <v>rights-free</v>
@@ -26335,19 +26335,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/9/9b/Titanotherium.jpg</v>
       </c>
       <c r="AE143" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Megacerops_coloradensis,_type.png</v>
+        <v>https://commons.wikimedia.org/wiki/File:Titanotherium.jpg</v>
       </c>
       <c r="AF143" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG143" t="str">
-        <v>https://www.youtube.com/watch?v=7ZhdXgRfxHI</v>
+        <v>https://www.youtube.com/watch?v=UWgrHiH-XAU</v>
       </c>
       <c r="AH143" t="str">
-        <v>7ZhdXgRfxHI</v>
+        <v>UWgrHiH-XAU</v>
       </c>
       <c r="AI143" t="str">
-        <v>Incredible 4K Nature Scenes Narrated By David Attenborough | BBC Earth</v>
+        <v>Life On Our Planet [2023] - 1st Juvenile Male Megacerops Screen Time</v>
       </c>
       <c r="AJ143" t="str">
         <v>4K</v>
@@ -26359,7 +26359,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM143" t="str">
-        <v>2026-08-01T15:14:58.969Z</v>
+        <v>2026-08-01T16:49:53.273Z</v>
       </c>
       <c r="AN143">
         <v>0.99</v>
@@ -26407,10 +26407,10 @@
         <v>1859</v>
       </c>
       <c r="BC143">
-        <v>631</v>
+        <v>2212</v>
       </c>
       <c r="BD143">
-        <v>936</v>
+        <v>1644</v>
       </c>
       <c r="BE143" t="str">
         <v>Full HD</v>
@@ -26514,22 +26514,22 @@
         <v/>
       </c>
       <c r="AD144" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/a/a1/Cervus_megaceros_-_skelet_-_1826_-_Print_-_Iconographia_Zoologica_-_Special_Collections_University_of_Amsterdam_-_UBA01_IZ21500122.tif</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/c/cd/Detail%2C_Senckenberg%2C_2017-10-12.jpg</v>
       </c>
       <c r="AE144" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Megaloceros_giganteus,_Munich,_2017-09-11.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Detail,_Senckenberg,_2017-10-12.jpg</v>
       </c>
       <c r="AF144" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG144" t="str">
-        <v>https://www.youtube.com/watch?v=6FjwDjKScyo</v>
+        <v>https://www.youtube.com/watch?v=i1SOtDFpx4U</v>
       </c>
       <c r="AH144" t="str">
-        <v>6FjwDjKScyo</v>
+        <v>i1SOtDFpx4U</v>
       </c>
       <c r="AI144" t="str">
-        <v>Ice Age Bison Hunt in 4K: Life of Prehistoric Hunters</v>
+        <v>Evolution’s Mistake – The Giant Deer With Car-Sized Antlers | Megaloceros Documentary</v>
       </c>
       <c r="AJ144" t="str">
         <v>4K</v>
@@ -26541,7 +26541,7 @@
         <v>gbif | wikimedia | youtube</v>
       </c>
       <c r="AM144" t="str">
-        <v>2026-08-01T15:15:01.304Z</v>
+        <v>2026-08-01T16:49:57.906Z</v>
       </c>
       <c r="AN144">
         <v>0.99</v>
@@ -26589,13 +26589,13 @@
         <v>1865</v>
       </c>
       <c r="BC144">
-        <v>2981</v>
+        <v>3328</v>
       </c>
       <c r="BD144">
-        <v>4059</v>
+        <v>2367</v>
       </c>
       <c r="BE144" t="str">
-        <v>4K</v>
+        <v>Full HD</v>
       </c>
       <c r="BF144" t="str">
         <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
@@ -26699,7 +26699,7 @@
         <v>https://inaturalist-open-data.s3.amazonaws.com/photos/524994158/original.jpg</v>
       </c>
       <c r="AE145" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Naturalis_Biodiversity_Center_-_RMNH.MOL.277989_-_Novisuccinea_ovalis_(Say,_1817)_-_Succineidae_-_Mollusc_shell.jpeg</v>
+        <v>https://www.inaturalist.org/photos/524994158</v>
       </c>
       <c r="AF145" t="str">
         <v>CC0</v>
@@ -26723,7 +26723,7 @@
         <v>gbif | wikipedia-en | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM145" t="str">
-        <v>2026-08-01T15:15:03.051Z</v>
+        <v>2026-08-01T16:50:00.896Z</v>
       </c>
       <c r="AN145">
         <v>0.99</v>
@@ -26771,16 +26771,16 @@
         <v/>
       </c>
       <c r="BC145">
-        <v>1920</v>
+        <v>1536</v>
       </c>
       <c r="BD145">
-        <v>1277</v>
+        <v>2048</v>
       </c>
       <c r="BE145" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF145" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
       </c>
       <c r="BG145" t="str">
         <v>rights-free</v>
@@ -26878,22 +26878,22 @@
         <v/>
       </c>
       <c r="AD146" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/a/ad/Nautilus-JB-01.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/4/47/N_de_Nautilus.jpg</v>
       </c>
       <c r="AE146" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Nautilus-JB-01.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:N_de_Nautilus.jpg</v>
       </c>
       <c r="AF146" t="str">
         <v>Public Domain</v>
       </c>
       <c r="AG146" t="str">
-        <v>https://www.youtube.com/watch?v=94weodD4TMo</v>
+        <v>https://www.youtube.com/watch?v=ple5F52x1LU</v>
       </c>
       <c r="AH146" t="str">
-        <v>94weodD4TMo</v>
+        <v>ple5F52x1LU</v>
       </c>
       <c r="AI146" t="str">
-        <v>Fish – The Hidden Civilization Underwater | 4K Wildlife Documentary</v>
+        <v>Nautilus | Animated | Wildlife Documentary | Informative #biography#wildbird#seaanimals# Documentary</v>
       </c>
       <c r="AJ146" t="str">
         <v>4K</v>
@@ -26905,7 +26905,7 @@
         <v>gbif | wikipedia-en | wikipedia-vi | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM146" t="str">
-        <v>2026-08-01T15:15:04.985Z</v>
+        <v>2026-08-01T16:50:05.017Z</v>
       </c>
       <c r="AN146">
         <v>0.99</v>
@@ -26953,10 +26953,10 @@
         <v/>
       </c>
       <c r="BC146">
-        <v>4272</v>
+        <v>1920</v>
       </c>
       <c r="BD146">
-        <v>2848</v>
+        <v>1440</v>
       </c>
       <c r="BE146" t="str">
         <v>Full HD</v>
@@ -27063,7 +27063,7 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/d/d6/Reef0764_-_Flickr_-_NOAA_Photo_Library.jpg</v>
       </c>
       <c r="AE147" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Heterocentrotus_mamillatus_1.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Reef0764_-_Flickr_-_NOAA_Photo_Library.jpg</v>
       </c>
       <c r="AF147" t="str">
         <v>Public Domain</v>
@@ -27087,7 +27087,7 @@
         <v>gbif | wikimedia | youtube | wikipedia-vi | inaturalist</v>
       </c>
       <c r="AM147" t="str">
-        <v>2026-08-01T15:15:06.849Z</v>
+        <v>2026-08-01T16:50:11.479Z</v>
       </c>
       <c r="AN147">
         <v>0.99</v>
@@ -27135,10 +27135,10 @@
         <v/>
       </c>
       <c r="BC147">
-        <v>6836</v>
+        <v>2048</v>
       </c>
       <c r="BD147">
-        <v>5204</v>
+        <v>1536</v>
       </c>
       <c r="BE147" t="str">
         <v>Full HD</v>
@@ -27245,19 +27245,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/c/cf/Paralithodes_camtschaticus_black-and-white.jpg</v>
       </c>
       <c r="AE148" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Paralithodes_camtschaticus_(YPM_IZ_107084).jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Paralithodes_camtschaticus_black-and-white.jpg</v>
       </c>
       <c r="AF148" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG148" t="str">
-        <v>https://www.youtube.com/watch?v=JAvcjk0SeKw</v>
+        <v>https://www.youtube.com/watch?v=GzrfLPGd9uk</v>
       </c>
       <c r="AH148" t="str">
-        <v>JAvcjk0SeKw</v>
+        <v>GzrfLPGd9uk</v>
       </c>
       <c r="AI148" t="str">
-        <v>Extraordinary Creatures of the Caribbean | 4K Nature Documentary | Nature Quest Relax</v>
+        <v>Invasive Royal Crab: How This Species is Taking Over Northern Seas | SLICE EARTH | FULL DOCUMENTARY</v>
       </c>
       <c r="AJ148" t="str">
         <v>4K</v>
@@ -27269,7 +27269,7 @@
         <v>gbif | wikipedia-en | wikipedia-vi | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM148" t="str">
-        <v>2026-08-01T15:15:08.750Z</v>
+        <v>2026-08-01T16:50:15.447Z</v>
       </c>
       <c r="AN148">
         <v>0.99</v>
@@ -27317,16 +27317,16 @@
         <v/>
       </c>
       <c r="BC148">
-        <v>5688</v>
+        <v>2500</v>
       </c>
       <c r="BD148">
-        <v>4640</v>
+        <v>1987</v>
       </c>
       <c r="BE148" t="str">
-        <v>4K</v>
+        <v>Full HD</v>
       </c>
       <c r="BF148" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG148" t="str">
         <v>rights-free</v>
@@ -27427,19 +27427,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/4/40/Hotaruika_002_for_sale_in_Tokyo.jpg</v>
       </c>
       <c r="AE149" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Watasenia_scintillans_002.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Hotaruika_002_for_sale_in_Tokyo.jpg</v>
       </c>
       <c r="AF149" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG149" t="str">
-        <v>https://www.youtube.com/watch?v=2tyLK9OB7Jc</v>
+        <v>https://www.youtube.com/watch?v=MClLB9_0hOg</v>
       </c>
       <c r="AH149" t="str">
-        <v>2tyLK9OB7Jc</v>
+        <v>MClLB9_0hOg</v>
       </c>
       <c r="AI149" t="str">
-        <v>Breathtaking Ocean Wildlife In 4K | BBC Earth</v>
+        <v>Firefly Squid: A Light in the Deep | Forces of Nature | BBC Earth Science</v>
       </c>
       <c r="AJ149" t="str">
         <v>4K</v>
@@ -27451,7 +27451,7 @@
         <v>gbif | wikipedia-en | wikipedia-vi | wikimedia | youtube | inaturalist</v>
       </c>
       <c r="AM149" t="str">
-        <v>2026-08-01T15:15:10.545Z</v>
+        <v>2026-08-01T16:50:19.163Z</v>
       </c>
       <c r="AN149">
         <v>0.99</v>
@@ -27499,16 +27499,16 @@
         <v/>
       </c>
       <c r="BC149">
-        <v>3264</v>
+        <v>1861</v>
       </c>
       <c r="BD149">
-        <v>2448</v>
+        <v>1282</v>
       </c>
       <c r="BE149" t="str">
-        <v>Full HD</v>
+        <v>HD</v>
       </c>
       <c r="BF149" t="str">
-        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG149" t="str">
         <v>rights-free</v>
@@ -27606,22 +27606,22 @@
         <v/>
       </c>
       <c r="AD150" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/0/01/Epinephelus_fuscoguttatus_435631884.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/3/32/Epinephelus_fuscoguttatus_304852602.jpg</v>
       </c>
       <c r="AE150" t="str">
-        <v>https://commons.wikimedia.org/wiki/File:Epinephelus_fuscoguttatus_435631884.jpg</v>
+        <v>https://commons.wikimedia.org/wiki/File:Epinephelus_fuscoguttatus_304852602.jpg</v>
       </c>
       <c r="AF150" t="str">
         <v>CC0</v>
       </c>
       <c r="AG150" t="str">
-        <v>https://www.youtube.com/watch?v=7ZhdXgRfxHI</v>
+        <v>https://www.youtube.com/watch?v=9B8-rvyeF4c</v>
       </c>
       <c r="AH150" t="str">
-        <v>7ZhdXgRfxHI</v>
+        <v>9B8-rvyeF4c</v>
       </c>
       <c r="AI150" t="str">
-        <v>Incredible 4K Nature Scenes Narrated By David Attenborough | BBC Earth</v>
+        <v>Camouflage grouper (Epinephelus polyphekadion) Marbled Grouper (4K)</v>
       </c>
       <c r="AJ150" t="str">
         <v>4K</v>
@@ -27633,7 +27633,7 @@
         <v>gbif | wikipedia-en | wikipedia-vi | wikimedia | wikidata | youtube | inaturalist</v>
       </c>
       <c r="AM150" t="str">
-        <v>2026-08-01T15:15:12.507Z</v>
+        <v>2026-08-01T16:50:22.592Z</v>
       </c>
       <c r="AN150">
         <v>0.99</v>
@@ -27684,7 +27684,7 @@
         <v>2048</v>
       </c>
       <c r="BD150">
-        <v>1952</v>
+        <v>1478</v>
       </c>
       <c r="BE150" t="str">
         <v>Full HD</v>
@@ -27791,19 +27791,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/f/f8/Lion_in_masai_mara.jpg</v>
       </c>
       <c r="AE151" t="str">
-        <v>https://www.inaturalist.org/photos/452124133</v>
+        <v>https://commons.wikimedia.org/wiki/File:Lion_in_masai_mara.jpg</v>
       </c>
       <c r="AF151" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG151" t="str">
-        <v>https://www.youtube.com/watch?v=Osl8arc8iZg</v>
+        <v>https://www.youtube.com/watch?v=8-6YqxYAkd0</v>
       </c>
       <c r="AH151" t="str">
-        <v>Osl8arc8iZg</v>
+        <v>8-6YqxYAkd0</v>
       </c>
       <c r="AI151" t="str">
-        <v>Wildlife Unleashed 4K Ultra HD Animal Documentary Lions, Tigers, Jaguars &amp; Jungle Wildlife</v>
+        <v>Lions: Kings of the Savannah | Roar of the Wild Ep. 1 | 4K UHD Documentary</v>
       </c>
       <c r="AJ151" t="str">
         <v>4K</v>
@@ -27815,7 +27815,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM151" t="str">
-        <v>2026-08-01T15:15:14.671Z</v>
+        <v>2026-08-01T16:50:27.201Z</v>
       </c>
       <c r="AN151">
         <v>0.99</v>
@@ -27863,16 +27863,16 @@
         <v/>
       </c>
       <c r="BC151">
-        <v>2048</v>
+        <v>3264</v>
       </c>
       <c r="BD151">
-        <v>1536</v>
+        <v>2448</v>
       </c>
       <c r="BE151" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF151" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG151" t="str">
         <v>rights-free</v>
@@ -27970,22 +27970,22 @@
         <v/>
       </c>
       <c r="AD152" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/3/3c/Memory_%28Unsplash%29.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/6/64/African_bush_elephant_%28Loxodonta_africana%29%2C_Masai_Mara.jpg</v>
       </c>
       <c r="AE152" t="str">
-        <v>https://www.inaturalist.org/photos/110278644</v>
+        <v>https://commons.wikimedia.org/wiki/File:African_bush_elephant_(Loxodonta_africana),_Masai_Mara.jpg</v>
       </c>
       <c r="AF152" t="str">
         <v>CC0</v>
       </c>
       <c r="AG152" t="str">
-        <v>https://www.youtube.com/watch?v=P8frC_cLLD4</v>
+        <v>https://www.youtube.com/watch?v=qOXeIip16No</v>
       </c>
       <c r="AH152" t="str">
-        <v>P8frC_cLLD4</v>
+        <v>qOXeIip16No</v>
       </c>
       <c r="AI152" t="str">
-        <v>African Safari 4K - Scenic Wildlife Film With African Music</v>
+        <v>Life of African Elephants - Largest Terrestrial Mammals of the Earth - 4K Nature Documentary Film</v>
       </c>
       <c r="AJ152" t="str">
         <v>4K</v>
@@ -27997,7 +27997,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM152" t="str">
-        <v>2026-08-01T15:15:18.138Z</v>
+        <v>2026-08-01T16:50:32.946Z</v>
       </c>
       <c r="AN152">
         <v>0.99</v>
@@ -28045,16 +28045,16 @@
         <v/>
       </c>
       <c r="BC152">
-        <v>2048</v>
+        <v>5068</v>
       </c>
       <c r="BD152">
-        <v>1536</v>
+        <v>3379</v>
       </c>
       <c r="BE152" t="str">
-        <v>Full HD</v>
+        <v>4K</v>
       </c>
       <c r="BF152" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG152" t="str">
         <v>rights-free</v>
@@ -28161,13 +28161,13 @@
         <v>CC0</v>
       </c>
       <c r="AG153" t="str">
-        <v>https://www.youtube.com/watch?v=hm2msf_MRTM</v>
+        <v>https://www.youtube.com/watch?v=MeBt3Cilv3I</v>
       </c>
       <c r="AH153" t="str">
-        <v>hm2msf_MRTM</v>
+        <v>MeBt3Cilv3I</v>
       </c>
       <c r="AI153" t="str">
-        <v>The Secret Life of a Fox Family - 4K HDR Scenic Wildlife Film With Calming Music, Animal Screensaver</v>
+        <v>"Red Fox (Vulpes vulpes)" (2020)</v>
       </c>
       <c r="AJ153" t="str">
         <v>4K</v>
@@ -28179,7 +28179,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
       </c>
       <c r="AM153" t="str">
-        <v>2026-08-01T14:45:12.424Z</v>
+        <v>2026-08-01T16:50:38.386Z</v>
       </c>
       <c r="AN153">
         <v>0.99</v>
@@ -28337,10 +28337,10 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/b/bd/A_Panda_eating.jpg</v>
       </c>
       <c r="AE154" t="str">
-        <v>https://www.inaturalist.org/photos/351209004</v>
+        <v>https://commons.wikimedia.org/wiki/File:A_Panda_eating.jpg</v>
       </c>
       <c r="AF154" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG154" t="str">
         <v>https://www.youtube.com/watch?v=YdP2fFyjBWQ</v>
@@ -28361,7 +28361,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM154" t="str">
-        <v>2026-08-01T15:15:23.679Z</v>
+        <v>2026-08-01T16:50:42.802Z</v>
       </c>
       <c r="AN154">
         <v>0.99</v>
@@ -28409,16 +28409,16 @@
         <v/>
       </c>
       <c r="BC154">
-        <v>2048</v>
+        <v>3648</v>
       </c>
       <c r="BD154">
-        <v>1365</v>
+        <v>4864</v>
       </c>
       <c r="BE154" t="str">
-        <v>Full HD</v>
+        <v>4K</v>
       </c>
       <c r="BF154" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG154" t="str">
         <v>rights-free</v>
@@ -28525,13 +28525,13 @@
         <v>CC0</v>
       </c>
       <c r="AG155" t="str">
-        <v>https://www.youtube.com/watch?v=iRaLJ2wWy98</v>
+        <v>https://www.youtube.com/watch?v=vyuehTxTdNY</v>
       </c>
       <c r="AH155" t="str">
-        <v>iRaLJ2wWy98</v>
+        <v>vyuehTxTdNY</v>
       </c>
       <c r="AI155" t="str">
-        <v>Australia’s Wetland Wildlife in 4K: Birds, Frogs, Snakes &amp; Turtles Documentary</v>
+        <v>Living Treasures of the Seas: Green Sea Turtles 🐢 | 4K Animal Documentary</v>
       </c>
       <c r="AJ155" t="str">
         <v>4K</v>
@@ -28543,7 +28543,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
       </c>
       <c r="AM155" t="str">
-        <v>2026-08-01T14:45:25.599Z</v>
+        <v>2026-08-01T16:50:46.497Z</v>
       </c>
       <c r="AN155">
         <v>0.97</v>
@@ -28701,22 +28701,22 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/5/51/Monarch-Butterfly-Pair-On-Nectar-Feeding-Tube-9.JPG</v>
       </c>
       <c r="AE156" t="str">
-        <v>https://www.inaturalist.org/photos/169360078</v>
+        <v>https://commons.wikimedia.org/wiki/File:Monarch-Butterfly-Pair-On-Nectar-Feeding-Tube-9.JPG</v>
       </c>
       <c r="AF156" t="str">
         <v>CC0</v>
       </c>
       <c r="AG156" t="str">
-        <v>https://www.youtube.com/watch?v=ES0DXcIv_Ec</v>
+        <v>https://www.youtube.com/watch?v=RPQimPt2HYc</v>
       </c>
       <c r="AH156" t="str">
-        <v>ES0DXcIv_Ec</v>
+        <v>RPQimPt2HYc</v>
       </c>
       <c r="AI156" t="str">
-        <v>Rare Tropical Butterflies in Stunning 4K HDR | Relaxing Nature Film</v>
+        <v>Monarch Butterfly Migration: A Mystery Of The Natural World - HD Documentary</v>
       </c>
       <c r="AJ156" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK156" t="str">
         <v>https://www.gbif.org/species/5133088 | https://en.wikipedia.org/wiki/Monarch_butterfly | https://vi.wikipedia.org/wiki/B%C6%B0%E1%BB%9Bm_vua | https://www.inaturalist.org/photos/169360078 | https://www.youtube.com/watch?v=ES0DXcIv_Ec</v>
@@ -28725,7 +28725,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM156" t="str">
-        <v>2026-08-01T15:15:29.697Z</v>
+        <v>2026-08-01T16:50:50.998Z</v>
       </c>
       <c r="AN156">
         <v>0.99</v>
@@ -28773,16 +28773,16 @@
         <v/>
       </c>
       <c r="BC156">
-        <v>2048</v>
+        <v>3968</v>
       </c>
       <c r="BD156">
-        <v>2048</v>
+        <v>2976</v>
       </c>
       <c r="BE156" t="str">
-        <v>Full HD</v>
+        <v>4K</v>
       </c>
       <c r="BF156" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG156" t="str">
         <v>rights-free</v>
@@ -28880,7 +28880,7 @@
         <v/>
       </c>
       <c r="AD157" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/d/d3/OrangutanP1.jpg</v>
+        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/109597147/original.jpg</v>
       </c>
       <c r="AE157" t="str">
         <v>https://www.inaturalist.org/photos/109597147</v>
@@ -28889,13 +28889,13 @@
         <v>CC0</v>
       </c>
       <c r="AG157" t="str">
-        <v>https://www.youtube.com/watch?v=KfjIaEP0EtY</v>
+        <v>https://www.youtube.com/watch?v=GPcEaa0SjQ0</v>
       </c>
       <c r="AH157" t="str">
-        <v>KfjIaEP0EtY</v>
+        <v>GPcEaa0SjQ0</v>
       </c>
       <c r="AI157" t="str">
-        <v>Animals of Asia 4K - Scenic Wildlife Film With Calming Music</v>
+        <v>Orangutan | 4K Wildlife Mini-Documentary</v>
       </c>
       <c r="AJ157" t="str">
         <v>4K</v>
@@ -28907,7 +28907,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM157" t="str">
-        <v>2026-08-01T15:15:32.559Z</v>
+        <v>2026-08-01T16:50:54.687Z</v>
       </c>
       <c r="AN157">
         <v>0.99</v>
@@ -29065,19 +29065,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/d/de/Dendrobates_azureus_at_Baltimore_Aquarium.JPG</v>
       </c>
       <c r="AE158" t="str">
-        <v>https://www.inaturalist.org/photos/170423605</v>
+        <v>https://commons.wikimedia.org/wiki/File:Dendrobates_azureus_at_Baltimore_Aquarium.JPG</v>
       </c>
       <c r="AF158" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG158" t="str">
-        <v>https://www.youtube.com/watch?v=7w0QFthGh5c</v>
+        <v>https://www.youtube.com/watch?v=GmqCkTNZkPI</v>
       </c>
       <c r="AH158" t="str">
-        <v>7w0QFthGh5c</v>
+        <v>GmqCkTNZkPI</v>
       </c>
       <c r="AI158" t="str">
-        <v>The Incredible Parenting of Poison Dart Frogs | Rainforest Documentary 4K</v>
+        <v>Poison Dart Frogs: Deadly Beauty of the Rainforest | Amazing Wildlife Documentary in 4K</v>
       </c>
       <c r="AJ158" t="str">
         <v>4K</v>
@@ -29089,7 +29089,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM158" t="str">
-        <v>2026-08-01T15:15:35.522Z</v>
+        <v>2026-08-01T16:40:36.250Z</v>
       </c>
       <c r="AN158">
         <v>0.98</v>
@@ -29146,7 +29146,7 @@
         <v>Full HD</v>
       </c>
       <c r="BF158" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG158" t="str">
         <v>rights-free</v>
@@ -29247,19 +29247,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/4/41/Pinctada_margaritifera.jpg</v>
       </c>
       <c r="AE159" t="str">
-        <v>https://www.inaturalist.org/photos/446483442</v>
+        <v>https://commons.wikimedia.org/wiki/File:Pinctada_margaritifera.jpg</v>
       </c>
       <c r="AF159" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG159" t="str">
-        <v>https://www.youtube.com/watch?v=LkZl4HcVVB8</v>
+        <v>https://www.youtube.com/watch?v=-xZvYktEb4I</v>
       </c>
       <c r="AH159" t="str">
-        <v>LkZl4HcVVB8</v>
+        <v>-xZvYktEb4I</v>
       </c>
       <c r="AI159" t="str">
-        <v>Jungle Animals in 4K UHD 🌿 | Amazing Wildlife Discovery | 60FPS Ultra HD Nature Documentary</v>
+        <v>Morphometric Study of the Black Lip Pearl Oyster, Pinctada margaritifera from North Sulawesi Waters,</v>
       </c>
       <c r="AJ159" t="str">
         <v>4K</v>
@@ -29271,7 +29271,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM159" t="str">
-        <v>2026-08-01T15:15:38.928Z</v>
+        <v>2026-08-01T16:51:02.016Z</v>
       </c>
       <c r="AN159">
         <v>0.99</v>
@@ -29319,16 +29319,16 @@
         <v/>
       </c>
       <c r="BC159">
-        <v>2048</v>
+        <v>1472</v>
       </c>
       <c r="BD159">
-        <v>1464</v>
+        <v>1040</v>
       </c>
       <c r="BE159" t="str">
-        <v>Full HD</v>
+        <v>HD</v>
       </c>
       <c r="BF159" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG159" t="str">
         <v>rights-free</v>
@@ -29426,22 +29426,22 @@
         <v/>
       </c>
       <c r="AD160" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/7/77/Buccinum_undatum_197060750.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/4/4f/Buccinum_undatum_from_England.jpg</v>
       </c>
       <c r="AE160" t="str">
-        <v>https://www.inaturalist.org/photos/252006506</v>
+        <v>https://commons.wikimedia.org/wiki/File:Buccinum_undatum_from_England.jpg</v>
       </c>
       <c r="AF160" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG160" t="str">
-        <v>https://www.youtube.com/watch?v=LkZl4HcVVB8</v>
+        <v>https://www.youtube.com/watch?v=7_tKd2IyewY</v>
       </c>
       <c r="AH160" t="str">
-        <v>LkZl4HcVVB8</v>
+        <v>7_tKd2IyewY</v>
       </c>
       <c r="AI160" t="str">
-        <v>Jungle Animals in 4K UHD 🌿 | Amazing Wildlife Discovery | 60FPS Ultra HD Nature Documentary</v>
+        <v>Common Whelk (Buccinum undatum) laying eggs.</v>
       </c>
       <c r="AJ160" t="str">
         <v>4K</v>
@@ -29453,7 +29453,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM160" t="str">
-        <v>2026-08-01T15:15:41.278Z</v>
+        <v>2026-08-01T16:51:05.719Z</v>
       </c>
       <c r="AN160">
         <v>0.99</v>
@@ -29501,16 +29501,16 @@
         <v/>
       </c>
       <c r="BC160">
-        <v>2048</v>
+        <v>710</v>
       </c>
       <c r="BD160">
-        <v>1365</v>
+        <v>722</v>
       </c>
       <c r="BE160" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF160" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG160" t="str">
         <v>rights-free</v>
@@ -29611,19 +29611,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/9/9a/Colias_croceus_1a.jpg</v>
       </c>
       <c r="AE161" t="str">
-        <v>https://www.inaturalist.org/photos/587388547</v>
+        <v>https://commons.wikimedia.org/wiki/File:Colias_croceus_1a.jpg</v>
       </c>
       <c r="AF161" t="str">
         <v>CC0</v>
       </c>
       <c r="AG161" t="str">
-        <v>https://www.youtube.com/watch?v=lyGsahJC19A</v>
+        <v>https://www.youtube.com/watch?v=6vRnFD08egI</v>
       </c>
       <c r="AH161" t="str">
-        <v>lyGsahJC19A</v>
+        <v>6vRnFD08egI</v>
       </c>
       <c r="AI161" t="str">
-        <v>Wild Colombia | Secrets of the Endemic Paradise | Wildlife Documentary 4K</v>
+        <v>The Clouded Yellow (Colias crocea)</v>
       </c>
       <c r="AJ161" t="str">
         <v>4K</v>
@@ -29635,7 +29635,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM161" t="str">
-        <v>2026-08-01T15:15:43.455Z</v>
+        <v>2026-08-01T16:51:09.564Z</v>
       </c>
       <c r="AN161">
         <v>0.98</v>
@@ -29683,16 +29683,16 @@
         <v/>
       </c>
       <c r="BC161">
-        <v>1927</v>
+        <v>1000</v>
       </c>
       <c r="BD161">
-        <v>1445</v>
+        <v>865</v>
       </c>
       <c r="BE161" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF161" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG161" t="str">
         <v>rights-free</v>
@@ -29793,19 +29793,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/c/cc/Idea_leuconoe_on_Ishigakijima.jpg</v>
       </c>
       <c r="AE162" t="str">
-        <v>https://www.inaturalist.org/photos/338942447</v>
+        <v>https://commons.wikimedia.org/wiki/File:Idea_leuconoe_on_Ishigakijima.jpg</v>
       </c>
       <c r="AF162" t="str">
         <v>CC0</v>
       </c>
       <c r="AG162" t="str">
-        <v>https://www.youtube.com/watch?v=e_K-6i7ZYM0</v>
+        <v>https://www.youtube.com/watch?v=9sU20Ka4rIw</v>
       </c>
       <c r="AH162" t="str">
-        <v>e_K-6i7ZYM0</v>
+        <v>9sU20Ka4rIw</v>
       </c>
       <c r="AI162" t="str">
-        <v>100 Most Beautiful Butterflies in the World Stunning 4K Ultra HD Close Up Butterfly Documentary</v>
+        <v>Idea Leuconoe life cycle (Paper kite butterfly)</v>
       </c>
       <c r="AJ162" t="str">
         <v>4K</v>
@@ -29817,7 +29817,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM162" t="str">
-        <v>2026-08-01T15:15:45.884Z</v>
+        <v>2026-08-01T16:51:14.549Z</v>
       </c>
       <c r="AN162">
         <v>0.99</v>
@@ -29865,16 +29865,16 @@
         <v/>
       </c>
       <c r="BC162">
+        <v>1536</v>
+      </c>
+      <c r="BD162">
         <v>2048</v>
-      </c>
-      <c r="BD162">
-        <v>1365</v>
       </c>
       <c r="BE162" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF162" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG162" t="str">
         <v>rights-free</v>
@@ -29981,13 +29981,13 @@
         <v>CC0</v>
       </c>
       <c r="AG163" t="str">
-        <v>https://www.youtube.com/watch?v=6hJVIxX5KJA</v>
+        <v>https://www.youtube.com/watch?v=ghjqnTCZArU</v>
       </c>
       <c r="AH163" t="str">
-        <v>6hJVIxX5KJA</v>
+        <v>ghjqnTCZArU</v>
       </c>
       <c r="AI163" t="str">
-        <v>MADAGASCAR: The Last Untouched Wilderness | 4K Travel Documentary</v>
+        <v>[手書き]外国のニシキツバメガを描いてみたよ Chrysiridia rhipheus #手書き #虫 #蛾 #アフリカ</v>
       </c>
       <c r="AJ163" t="str">
         <v>4K</v>
@@ -29999,7 +29999,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
       </c>
       <c r="AM163" t="str">
-        <v>2026-08-01T14:46:43.486Z</v>
+        <v>2026-08-01T16:51:18.421Z</v>
       </c>
       <c r="AN163">
         <v>0.97</v>
@@ -30163,13 +30163,13 @@
         <v>CC0</v>
       </c>
       <c r="AG164" t="str">
-        <v>https://www.youtube.com/watch?v=F9n18YP7F14</v>
+        <v>https://www.youtube.com/watch?v=iFJ6EVG_P2k</v>
       </c>
       <c r="AH164" t="str">
-        <v>F9n18YP7F14</v>
+        <v>iFJ6EVG_P2k</v>
       </c>
       <c r="AI164" t="str">
-        <v>Breathtaking Wildlife of Japan in 4K UHD | BBC Earth</v>
+        <v>Singing Bell Cricket (meloimorpha japonica) Natural Awesome Sounds</v>
       </c>
       <c r="AJ164" t="str">
         <v>4K</v>
@@ -30181,7 +30181,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
       </c>
       <c r="AM164" t="str">
-        <v>2026-08-01T14:46:52.674Z</v>
+        <v>2026-08-01T16:51:21.950Z</v>
       </c>
       <c r="AN164">
         <v>0.99</v>
@@ -30345,13 +30345,13 @@
         <v>CC0</v>
       </c>
       <c r="AG165" t="str">
-        <v>https://www.youtube.com/watch?v=VJxre0Zc96o</v>
+        <v>https://www.youtube.com/watch?v=AOMId3AvXG0</v>
       </c>
       <c r="AH165" t="str">
-        <v>VJxre0Zc96o</v>
+        <v>AOMId3AvXG0</v>
       </c>
       <c r="AI165" t="str">
-        <v>4K Ultra HD Rare Praying Mantis Close Up Stunning Wildlife Documentary</v>
+        <v>MIGRATORY LOCUST INSECT 4k</v>
       </c>
       <c r="AJ165" t="str">
         <v>4K</v>
@@ -30363,7 +30363,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
       </c>
       <c r="AM165" t="str">
-        <v>2026-08-01T14:46:55.964Z</v>
+        <v>2026-08-01T16:51:25.769Z</v>
       </c>
       <c r="AN165">
         <v>0.99</v>
@@ -30518,22 +30518,22 @@
         <v/>
       </c>
       <c r="AD166" t="str">
-        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/288082845/original.jpg</v>
+        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/328522677/original.jpg</v>
       </c>
       <c r="AE166" t="str">
-        <v>https://www.inaturalist.org/photos/288082845</v>
+        <v>https://www.inaturalist.org/photos/328522677</v>
       </c>
       <c r="AF166" t="str">
         <v>CC0</v>
       </c>
       <c r="AG166" t="str">
-        <v>https://www.youtube.com/watch?v=dF1X13Oo0pg</v>
+        <v>https://www.youtube.com/watch?v=DYOI1rL8Rd0</v>
       </c>
       <c r="AH166" t="str">
-        <v>dF1X13Oo0pg</v>
+        <v>DYOI1rL8Rd0</v>
       </c>
       <c r="AI166" t="str">
-        <v>10 Hours of Epic 4K Wildlife Documentary: Crocodiles Buffaloes &amp; Nature’s Greatest Battles #wildlife</v>
+        <v>Coccinella septempunctata:ladybug:: NATURE &amp; WILD JOURNEY</v>
       </c>
       <c r="AJ166" t="str">
         <v>4K</v>
@@ -30545,7 +30545,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
       </c>
       <c r="AM166" t="str">
-        <v>2026-08-01T14:47:05.122Z</v>
+        <v>2026-08-01T16:51:29.717Z</v>
       </c>
       <c r="AN166">
         <v>0.99</v>
@@ -30593,10 +30593,10 @@
         <v/>
       </c>
       <c r="BC166">
-        <v>1536</v>
+        <v>457</v>
       </c>
       <c r="BD166">
-        <v>2048</v>
+        <v>548</v>
       </c>
       <c r="BE166" t="str">
         <v>Full HD</v>
@@ -30709,16 +30709,16 @@
         <v>CC0</v>
       </c>
       <c r="AG167" t="str">
-        <v>https://www.youtube.com/watch?v=7ZhdXgRfxHI</v>
+        <v>https://www.youtube.com/watch?v=qyTgt6NysKE</v>
       </c>
       <c r="AH167" t="str">
-        <v>7ZhdXgRfxHI</v>
+        <v>qyTgt6NysKE</v>
       </c>
       <c r="AI167" t="str">
-        <v>Incredible 4K Nature Scenes Narrated By David Attenborough | BBC Earth</v>
+        <v>Incredible Spiders Full Documentary [HD] ~ National Geographic 2016</v>
       </c>
       <c r="AJ167" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK167" t="str">
         <v>https://www.gbif.org/species/1496 | https://en.wikipedia.org/wiki/Spider | https://vi.wikipedia.org/wiki/Nh%E1%BB%87n | https://www.inaturalist.org/photos/168205493 | https://www.youtube.com/watch?v=7ZhdXgRfxHI</v>
@@ -30727,7 +30727,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
       </c>
       <c r="AM167" t="str">
-        <v>2026-08-01T14:47:08.280Z</v>
+        <v>2026-08-01T16:51:33.790Z</v>
       </c>
       <c r="AN167">
         <v>0.94</v>
@@ -30891,13 +30891,13 @@
         <v>CC0</v>
       </c>
       <c r="AG168" t="str">
-        <v>https://www.youtube.com/watch?v=RCm0D0z7rMk</v>
+        <v>https://www.youtube.com/watch?v=vFxr4_a6ld0</v>
       </c>
       <c r="AH168" t="str">
-        <v>RCm0D0z7rMk</v>
+        <v>vFxr4_a6ld0</v>
       </c>
       <c r="AI168" t="str">
-        <v>Antarctica Wildlife | Apex Predators &amp; Majestic Giants | Full Documentary 4K</v>
+        <v>Amazing Beadlet - 4K Nature Relaxation - 4K View - 4K Walking Beadlet - Beadlet Travel Vidio</v>
       </c>
       <c r="AJ168" t="str">
         <v>4K</v>
@@ -30909,7 +30909,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
       </c>
       <c r="AM168" t="str">
-        <v>2026-08-01T14:47:10.565Z</v>
+        <v>2026-08-01T16:51:37.577Z</v>
       </c>
       <c r="AN168">
         <v>0.99</v>
@@ -31064,22 +31064,22 @@
         <v/>
       </c>
       <c r="AD169" t="str">
-        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/313134117/original.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/c/c0/Asterias_rubens_307854603.jpg</v>
       </c>
       <c r="AE169" t="str">
-        <v>https://www.inaturalist.org/photos/313134117</v>
+        <v>https://commons.wikimedia.org/wiki/File:Asterias_rubens_307854603.jpg</v>
       </c>
       <c r="AF169" t="str">
         <v>CC0</v>
       </c>
       <c r="AG169" t="str">
-        <v>https://www.youtube.com/watch?v=R0opYlkxRuQ</v>
+        <v>https://www.youtube.com/watch?v=qcJibCyjKTA</v>
       </c>
       <c r="AH169" t="str">
-        <v>R0opYlkxRuQ</v>
+        <v>qcJibCyjKTA</v>
       </c>
       <c r="AI169" t="str">
-        <v>Discover Australia's Wildest Wonders - Epic Landscapes and Unique Animals | Wildlife Documentary 4K</v>
+        <v>The Fascinating World of Starfish | Wildlife Documentary | Fusion Documentary</v>
       </c>
       <c r="AJ169" t="str">
         <v>4K</v>
@@ -31088,10 +31088,10 @@
         <v>https://www.gbif.org/species/7765831 | https://en.wikipedia.org/wiki/Common_starfish | https://vi.wikipedia.org/wiki/Asterias_rubens | https://www.inaturalist.org/photos/313134117 | https://www.youtube.com/watch?v=R0opYlkxRuQ</v>
       </c>
       <c r="AL169" t="str">
-        <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
+        <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM169" t="str">
-        <v>2026-08-01T14:47:13.501Z</v>
+        <v>2026-08-01T16:51:41.850Z</v>
       </c>
       <c r="AN169">
         <v>0.97</v>
@@ -31139,16 +31139,16 @@
         <v/>
       </c>
       <c r="BC169">
-        <v>1536</v>
+        <v>2048</v>
       </c>
       <c r="BD169">
-        <v>2048</v>
+        <v>1365</v>
       </c>
       <c r="BE169" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF169" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG169" t="str">
         <v>rights-free</v>
@@ -31255,13 +31255,13 @@
         <v>CC0</v>
       </c>
       <c r="AG170" t="str">
-        <v>https://www.youtube.com/watch?v=R5E7DXXWw_Q</v>
+        <v>https://www.youtube.com/watch?v=x_u08rwdw7k</v>
       </c>
       <c r="AH170" t="str">
-        <v>R5E7DXXWw_Q</v>
+        <v>x_u08rwdw7k</v>
       </c>
       <c r="AI170" t="str">
-        <v>Ocean Wildlife | Exploring the Hidden Kingdom Beneath Endless Blue | 4K Documentary</v>
+        <v>Species Spotlight - Common Rock Barnacle (Semibalanus balanoides)</v>
       </c>
       <c r="AJ170" t="str">
         <v>4K</v>
@@ -31273,7 +31273,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
       </c>
       <c r="AM170" t="str">
-        <v>2026-08-01T14:47:16.295Z</v>
+        <v>2026-08-01T16:51:45.341Z</v>
       </c>
       <c r="AN170">
         <v>0.99</v>
@@ -31437,13 +31437,13 @@
         <v>CC0</v>
       </c>
       <c r="AG171" t="str">
-        <v>https://www.youtube.com/watch?v=MQePHGMZ5iM</v>
+        <v>https://www.youtube.com/watch?v=ziybVQBSpsI</v>
       </c>
       <c r="AH171" t="str">
-        <v>MQePHGMZ5iM</v>
+        <v>ziybVQBSpsI</v>
       </c>
       <c r="AI171" t="str">
-        <v>AFRICAN SAFARIA 4K Discover Amazing Wildlife in Ultra HD 60FPS Nature Documentary #ANIMALS</v>
+        <v>Yellow Tang Surgeonfish (Zebrasoma Flavescens)【4K】</v>
       </c>
       <c r="AJ171" t="str">
         <v>4K</v>
@@ -31455,7 +31455,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube</v>
       </c>
       <c r="AM171" t="str">
-        <v>2026-08-01T14:47:23.248Z</v>
+        <v>2026-08-01T16:51:49.026Z</v>
       </c>
       <c r="AN171">
         <v>0.99</v>
@@ -31619,13 +31619,13 @@
         <v>CC0</v>
       </c>
       <c r="AG172" t="str">
-        <v>https://www.youtube.com/watch?v=WI4yGLk1_F8</v>
+        <v>https://www.youtube.com/watch?v=0Dmf_r2mD34</v>
       </c>
       <c r="AH172" t="str">
-        <v>WI4yGLk1_F8</v>
+        <v>0Dmf_r2mD34</v>
       </c>
       <c r="AI172" t="str">
-        <v>Ocean Wildlife | The Hidden Kingdoms of Marine Life Revealed | 4K Documentary</v>
+        <v>Super Grouper - Full Episode</v>
       </c>
       <c r="AJ172" t="str">
         <v>4K</v>
@@ -31637,7 +31637,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube</v>
       </c>
       <c r="AM172" t="str">
-        <v>2026-08-01T14:47:27.545Z</v>
+        <v>2026-08-01T16:51:53.008Z</v>
       </c>
       <c r="AN172">
         <v>0.99</v>
@@ -31792,25 +31792,25 @@
         <v/>
       </c>
       <c r="AD173" t="str">
-        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/554851711/original.jpg</v>
+        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/89061908/original.jpeg</v>
       </c>
       <c r="AE173" t="str">
-        <v>https://www.inaturalist.org/photos/502811263</v>
+        <v>https://www.inaturalist.org/photos/89061908</v>
       </c>
       <c r="AF173" t="str">
         <v>CC0</v>
       </c>
       <c r="AG173" t="str">
-        <v>https://www.youtube.com/watch?v=-0F7iua-37Y</v>
+        <v>https://www.youtube.com/watch?v=R9IHTZAM7KU</v>
       </c>
       <c r="AH173" t="str">
-        <v>-0F7iua-37Y</v>
+        <v>R9IHTZAM7KU</v>
       </c>
       <c r="AI173" t="str">
-        <v>Animals of Europe 4K - Scenic Wildlife Film With Calming Music</v>
+        <v>Epinephelus marginatus (Dusky grouper) and Palinurus elephas (European spiny lobster) [HD]</v>
       </c>
       <c r="AJ173" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK173" t="str">
         <v>https://www.gbif.org/species/2388507 | https://en.wikipedia.org/wiki/Epinephelus_marginatus | https://www.wikidata.org/entity/Q204861 | https://www.inaturalist.org/photos/502811263 | https://www.youtube.com/watch?v=-0F7iua-37Y</v>
@@ -31819,7 +31819,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikidata | youtube</v>
       </c>
       <c r="AM173" t="str">
-        <v>2026-08-01T15:16:10.494Z</v>
+        <v>2026-08-01T16:51:56.693Z</v>
       </c>
       <c r="AN173">
         <v>0.99</v>
@@ -31867,10 +31867,10 @@
         <v/>
       </c>
       <c r="BC173">
-        <v>2048</v>
+        <v>1180</v>
       </c>
       <c r="BD173">
-        <v>1536</v>
+        <v>665</v>
       </c>
       <c r="BE173" t="str">
         <v>Full HD</v>
@@ -31977,19 +31977,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/8/80/FMIB_36055_Plectropoma_Leopardinus_%28Leopard-Spotted_Plectropoma%29.jpeg</v>
       </c>
       <c r="AE174" t="str">
-        <v>https://www.inaturalist.org/photos/435424887</v>
+        <v>https://commons.wikimedia.org/wiki/File:FMIB_36055_Plectropoma_Leopardinus_(Leopard-Spotted_Plectropoma).jpeg</v>
       </c>
       <c r="AF174" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG174" t="str">
-        <v>https://www.youtube.com/watch?v=dF1X13Oo0pg</v>
+        <v>https://www.youtube.com/watch?v=-phatxYU9RA</v>
       </c>
       <c r="AH174" t="str">
-        <v>dF1X13Oo0pg</v>
+        <v>-phatxYU9RA</v>
       </c>
       <c r="AI174" t="str">
-        <v>10 Hours of Epic 4K Wildlife Documentary: Crocodiles Buffaloes &amp; Nature’s Greatest Battles #wildlife</v>
+        <v>Coral Trout (Plectropomus leopardus) – The Silent Predator of Coral Reefs | Deep Sea Documentary 4K</v>
       </c>
       <c r="AJ174" t="str">
         <v>4K</v>
@@ -32001,7 +32001,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube | wikimedia</v>
       </c>
       <c r="AM174" t="str">
-        <v>2026-08-01T15:16:12.721Z</v>
+        <v>2026-08-01T16:52:00.302Z</v>
       </c>
       <c r="AN174">
         <v>0.99</v>
@@ -32049,16 +32049,16 @@
         <v/>
       </c>
       <c r="BC174">
-        <v>2048</v>
+        <v>885</v>
       </c>
       <c r="BD174">
-        <v>1536</v>
+        <v>473</v>
       </c>
       <c r="BE174" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF174" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG174" t="str">
         <v>rights-free</v>
@@ -32156,22 +32156,22 @@
         <v/>
       </c>
       <c r="AD175" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/7/71/Serranus_cabrilla_-_1774-1804_-_Print_-_Iconographia_Zoologica_-_Special_Collections_University_of_Amsterdam_-_UBA01_IZ12900164.tif</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/5/52/Leptogorgia_sarmentosa_%28Esper%2C_1791%29_4.jpg</v>
       </c>
       <c r="AE175" t="str">
-        <v>https://www.inaturalist.org/photos/403784538</v>
+        <v>https://commons.wikimedia.org/wiki/File:Leptogorgia_sarmentosa_(Esper,_1791)_4.jpg</v>
       </c>
       <c r="AF175" t="str">
         <v>CC0</v>
       </c>
       <c r="AG175" t="str">
-        <v>https://www.youtube.com/watch?v=MQePHGMZ5iM</v>
+        <v>https://www.youtube.com/watch?v=jI8q0Ksl70A</v>
       </c>
       <c r="AH175" t="str">
-        <v>MQePHGMZ5iM</v>
+        <v>jI8q0Ksl70A</v>
       </c>
       <c r="AI175" t="str">
-        <v>AFRICAN SAFARIA 4K Discover Amazing Wildlife in Ultra HD 60FPS Nature Documentary #ANIMALS</v>
+        <v>Through the eyes of a PAINTED COMBER (Serranus scriba) | Sea Report ep. 6</v>
       </c>
       <c r="AJ175" t="str">
         <v>4K</v>
@@ -32183,7 +32183,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube | wikimedia</v>
       </c>
       <c r="AM175" t="str">
-        <v>2026-08-01T15:16:15.569Z</v>
+        <v>2026-08-01T16:52:04.291Z</v>
       </c>
       <c r="AN175">
         <v>0.99</v>
@@ -32231,16 +32231,16 @@
         <v/>
       </c>
       <c r="BC175">
-        <v>2048</v>
+        <v>3200</v>
       </c>
       <c r="BD175">
-        <v>1155</v>
+        <v>2080</v>
       </c>
       <c r="BE175" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF175" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG175" t="str">
         <v>rights-free</v>
@@ -32338,22 +32338,22 @@
         <v/>
       </c>
       <c r="AD176" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/4/48/Serranus_scriba_-_-_Print_-_Iconographia_Zoologica_-_Special_Collections_University_of_Amsterdam_-_UBA01_IZ12900153.tif</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/c/c6/Serranus_scriba33.jpg</v>
       </c>
       <c r="AE176" t="str">
-        <v>https://www.inaturalist.org/photos/403785218</v>
+        <v>https://commons.wikimedia.org/wiki/File:Serranus_scriba33.jpg</v>
       </c>
       <c r="AF176" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG176" t="str">
-        <v>https://www.youtube.com/watch?v=LkZl4HcVVB8</v>
+        <v>https://www.youtube.com/watch?v=jI8q0Ksl70A</v>
       </c>
       <c r="AH176" t="str">
-        <v>LkZl4HcVVB8</v>
+        <v>jI8q0Ksl70A</v>
       </c>
       <c r="AI176" t="str">
-        <v>Jungle Animals in 4K UHD 🌿 | Amazing Wildlife Discovery | 60FPS Ultra HD Nature Documentary</v>
+        <v>Through the eyes of a PAINTED COMBER (Serranus scriba) | Sea Report ep. 6</v>
       </c>
       <c r="AJ176" t="str">
         <v>4K</v>
@@ -32365,7 +32365,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube | wikimedia</v>
       </c>
       <c r="AM176" t="str">
-        <v>2026-08-01T15:16:17.830Z</v>
+        <v>2026-08-01T16:52:08.859Z</v>
       </c>
       <c r="AN176">
         <v>0.99</v>
@@ -32413,16 +32413,16 @@
         <v/>
       </c>
       <c r="BC176">
-        <v>2048</v>
+        <v>1000</v>
       </c>
       <c r="BD176">
-        <v>1155</v>
+        <v>750</v>
       </c>
       <c r="BE176" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF176" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG176" t="str">
         <v>rights-free</v>
@@ -32529,13 +32529,13 @@
         <v>CC0</v>
       </c>
       <c r="AG177" t="str">
-        <v>https://www.youtube.com/watch?v=Ceww6yLijFc</v>
+        <v>https://www.youtube.com/watch?v=jEutv8CqA7k</v>
       </c>
       <c r="AH177" t="str">
-        <v>Ceww6yLijFc</v>
+        <v>jEutv8CqA7k</v>
       </c>
       <c r="AI177" t="str">
-        <v>The Depths of the North Sea: Life in the Cold Abyss | Secrets of the Seas Ep. 1 | 4K UHD Documentary</v>
+        <v>Fimbriated Moray Eel Hunting</v>
       </c>
       <c r="AJ177" t="str">
         <v>4K</v>
@@ -32547,7 +32547,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube</v>
       </c>
       <c r="AM177" t="str">
-        <v>2026-08-01T14:48:01.046Z</v>
+        <v>2026-08-01T16:52:12.344Z</v>
       </c>
       <c r="AN177">
         <v>0.99</v>
@@ -32711,13 +32711,13 @@
         <v>CC0</v>
       </c>
       <c r="AG178" t="str">
-        <v>https://www.youtube.com/watch?v=GK1ll8e017k</v>
+        <v>https://www.youtube.com/watch?v=iVLesAn4a2w</v>
       </c>
       <c r="AH178" t="str">
-        <v>GK1ll8e017k</v>
+        <v>iVLesAn4a2w</v>
       </c>
       <c r="AI178" t="str">
-        <v>4K Ostrich the Flightless Bird - African Wildlife Documentary Film with Narration</v>
+        <v>SKAGERRAK | Survival In Atlantic’s Hidden Underwater #wildanimals | Wild Nature</v>
       </c>
       <c r="AJ178" t="str">
         <v>4K</v>
@@ -32729,7 +32729,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube</v>
       </c>
       <c r="AM178" t="str">
-        <v>2026-08-01T14:48:04.677Z</v>
+        <v>2026-08-01T16:52:16.221Z</v>
       </c>
       <c r="AN178">
         <v>0.99</v>
@@ -32884,22 +32884,22 @@
         <v/>
       </c>
       <c r="AD179" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/9/9a/Genyoroge_macolor_-_1825-1839_-_Print_-_Iconographia_Zoologica_-_Special_Collections_University_of_Amsterdam_-_UBA01_IZ12900273.tif</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/b/bb/Reef2158_-_Flickr_-_NOAA_Photo_Library.jpg</v>
       </c>
       <c r="AE179" t="str">
-        <v>https://www.inaturalist.org/photos/435717192</v>
+        <v>https://commons.wikimedia.org/wiki/File:Reef2158_-_Flickr_-_NOAA_Photo_Library.jpg</v>
       </c>
       <c r="AF179" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG179" t="str">
-        <v>https://www.youtube.com/watch?v=wQsKfXydUmI</v>
+        <v>https://www.youtube.com/watch?v=sJ0j_aMoWTY</v>
       </c>
       <c r="AH179" t="str">
-        <v>wQsKfXydUmI</v>
+        <v>sJ0j_aMoWTY</v>
       </c>
       <c r="AI179" t="str">
-        <v>WEST AFRICA: The Edge of the Wild World | 4K Travel Documentary</v>
+        <v>How Catching 100,000 lbs of Red Snapper Nets $1.5 Million in Just 5 Days | Fishing Documentary</v>
       </c>
       <c r="AJ179" t="str">
         <v>4K</v>
@@ -32911,7 +32911,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube | wikimedia</v>
       </c>
       <c r="AM179" t="str">
-        <v>2026-08-01T15:16:23.829Z</v>
+        <v>2026-08-01T16:52:19.689Z</v>
       </c>
       <c r="AN179">
         <v>0.99</v>
@@ -32959,16 +32959,16 @@
         <v/>
       </c>
       <c r="BC179">
-        <v>2048</v>
+        <v>3072</v>
       </c>
       <c r="BD179">
-        <v>1536</v>
+        <v>2304</v>
       </c>
       <c r="BE179" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF179" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG179" t="str">
         <v>rights-free</v>
@@ -33069,19 +33069,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/0/01/Rhodes_Aquarium_-_Sparisoma_cretense.jpg</v>
       </c>
       <c r="AE180" t="str">
-        <v>https://www.inaturalist.org/photos/256394294</v>
+        <v>https://commons.wikimedia.org/wiki/File:Rhodes_Aquarium_-_Sparisoma_cretense.jpg</v>
       </c>
       <c r="AF180" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG180" t="str">
-        <v>https://www.youtube.com/watch?v=kHsxd8C9_O8</v>
+        <v>https://www.youtube.com/watch?v=VfgEMQeGPKM</v>
       </c>
       <c r="AH180" t="str">
-        <v>kHsxd8C9_O8</v>
+        <v>VfgEMQeGPKM</v>
       </c>
       <c r="AI180" t="str">
-        <v>THE RED SEA | The Extraordinary Wildlife Hidden Beneath Ancient Waters | 4K Documentary</v>
+        <v>Sparisoma cretense 1 - The Parrot of the Mediterranean #PezDocSerie #GScUbALO</v>
       </c>
       <c r="AJ180" t="str">
         <v>4K</v>
@@ -33093,7 +33093,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube | wikimedia</v>
       </c>
       <c r="AM180" t="str">
-        <v>2026-08-01T15:16:26.089Z</v>
+        <v>2026-08-01T16:52:23.131Z</v>
       </c>
       <c r="AN180">
         <v>0.99</v>
@@ -33141,16 +33141,16 @@
         <v/>
       </c>
       <c r="BC180">
-        <v>2048</v>
+        <v>3004</v>
       </c>
       <c r="BD180">
-        <v>1514</v>
+        <v>1562</v>
       </c>
       <c r="BE180" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF180" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG180" t="str">
         <v>rights-free</v>
@@ -33257,13 +33257,13 @@
         <v>CC0</v>
       </c>
       <c r="AG181" t="str">
-        <v>https://www.youtube.com/watch?v=3eTMbBzVFfM</v>
+        <v>https://www.youtube.com/watch?v=fx8r2CIDE3M</v>
       </c>
       <c r="AH181" t="str">
-        <v>3eTMbBzVFfM</v>
+        <v>fx8r2CIDE3M</v>
       </c>
       <c r="AI181" t="str">
-        <v>The Magical Wildlife of Britain’s Rivers (4K Documentary)</v>
+        <v>Final Species Documentary Green Humphead Parrotfish</v>
       </c>
       <c r="AJ181" t="str">
         <v>4K</v>
@@ -33275,7 +33275,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube</v>
       </c>
       <c r="AM181" t="str">
-        <v>2026-08-01T14:48:42.285Z</v>
+        <v>2026-08-01T16:52:26.926Z</v>
       </c>
       <c r="AN181">
         <v>0.99</v>
@@ -33430,10 +33430,10 @@
         <v/>
       </c>
       <c r="AD182" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/1/1a/Pomacanthus_imperator_263477793.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/6/6a/Pomacanthus_imperator_419190057.jpg</v>
       </c>
       <c r="AE182" t="str">
-        <v>https://www.inaturalist.org/photos/419190072</v>
+        <v>https://commons.wikimedia.org/wiki/File:Pomacanthus_imperator_419190057.jpg</v>
       </c>
       <c r="AF182" t="str">
         <v>CC0</v>
@@ -33457,7 +33457,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube | wikimedia</v>
       </c>
       <c r="AM182" t="str">
-        <v>2026-08-01T15:16:30.354Z</v>
+        <v>2026-08-01T16:52:31.211Z</v>
       </c>
       <c r="AN182">
         <v>0.99</v>
@@ -33505,16 +33505,16 @@
         <v/>
       </c>
       <c r="BC182">
-        <v>2048</v>
+        <v>1386</v>
       </c>
       <c r="BD182">
-        <v>1312</v>
+        <v>1836</v>
       </c>
       <c r="BE182" t="str">
-        <v>Full HD</v>
+        <v>HD</v>
       </c>
       <c r="BF182" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG182" t="str">
         <v>rights-free</v>
@@ -33612,7 +33612,7 @@
         <v/>
       </c>
       <c r="AD183" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/1/13/Odonus_niger_305021796.jpg</v>
+        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/498678646/original.jpg</v>
       </c>
       <c r="AE183" t="str">
         <v>https://www.inaturalist.org/photos/498678646</v>
@@ -33621,13 +33621,13 @@
         <v>CC0</v>
       </c>
       <c r="AG183" t="str">
-        <v>https://www.youtube.com/watch?v=NOgl1nW0NtA</v>
+        <v>https://www.youtube.com/watch?v=Aer5csiwNAU</v>
       </c>
       <c r="AH183" t="str">
-        <v>NOgl1nW0NtA</v>
+        <v>Aer5csiwNAU</v>
       </c>
       <c r="AI183" t="str">
-        <v>A Rhino's Life: Survival in the Jaws of Danger | 4K UHD Documentary</v>
+        <v>Redtoothed triggerfish (Odonus niger) in 4K</v>
       </c>
       <c r="AJ183" t="str">
         <v>4K</v>
@@ -33639,7 +33639,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube | wikimedia</v>
       </c>
       <c r="AM183" t="str">
-        <v>2026-08-01T15:16:32.014Z</v>
+        <v>2026-08-01T16:52:34.518Z</v>
       </c>
       <c r="AN183">
         <v>0.99</v>
@@ -33797,19 +33797,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/7/79/Titan_Triggerfish_imported_from_iNaturalist_photo_262420759_on_2_November_2024.jpg</v>
       </c>
       <c r="AE184" t="str">
-        <v>https://www.inaturalist.org/photos/336149084</v>
+        <v>https://commons.wikimedia.org/wiki/File:Titan_Triggerfish_imported_from_iNaturalist_photo_262420759_on_2_November_2024.jpg</v>
       </c>
       <c r="AF184" t="str">
         <v>CC0</v>
       </c>
       <c r="AG184" t="str">
-        <v>https://www.youtube.com/watch?v=UTuAIid6x28</v>
+        <v>https://www.youtube.com/watch?v=lWowQrrqejk</v>
       </c>
       <c r="AH184" t="str">
-        <v>UTuAIid6x28</v>
+        <v>lWowQrrqejk</v>
       </c>
       <c r="AI184" t="str">
-        <v>Stunning 4K Underwater Nature Footage | BBC Earth</v>
+        <v>Seek, bite, sleep by Titan Triggerfish (Balistoides viridescens) in 4K</v>
       </c>
       <c r="AJ184" t="str">
         <v>4K</v>
@@ -33821,7 +33821,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube | wikimedia</v>
       </c>
       <c r="AM184" t="str">
-        <v>2026-08-01T15:16:34.028Z</v>
+        <v>2026-08-01T16:52:37.895Z</v>
       </c>
       <c r="AN184">
         <v>0.99</v>
@@ -33872,13 +33872,13 @@
         <v>2048</v>
       </c>
       <c r="BD184">
-        <v>1155</v>
+        <v>1434</v>
       </c>
       <c r="BE184" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF184" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG184" t="str">
         <v>rights-free</v>
@@ -33985,13 +33985,13 @@
         <v>CC0</v>
       </c>
       <c r="AG185" t="str">
-        <v>https://www.youtube.com/watch?v=UTuAIid6x28</v>
+        <v>https://www.youtube.com/watch?v=G8ZsA8z4q9k</v>
       </c>
       <c r="AH185" t="str">
-        <v>UTuAIid6x28</v>
+        <v>G8ZsA8z4q9k</v>
       </c>
       <c r="AI185" t="str">
-        <v>Stunning 4K Underwater Nature Footage | BBC Earth</v>
+        <v>Starry puffer (Arothron stellatus) stellate pufferfish, starry toadfish (4K)</v>
       </c>
       <c r="AJ185" t="str">
         <v>4K</v>
@@ -34003,7 +34003,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube</v>
       </c>
       <c r="AM185" t="str">
-        <v>2026-08-01T14:49:27.050Z</v>
+        <v>2026-08-01T16:52:42.007Z</v>
       </c>
       <c r="AN185">
         <v>0.97</v>
@@ -34167,13 +34167,13 @@
         <v>CC0</v>
       </c>
       <c r="AG186" t="str">
-        <v>https://www.youtube.com/watch?v=LkZl4HcVVB8</v>
+        <v>https://www.youtube.com/watch?v=qroO2GMNLVE</v>
       </c>
       <c r="AH186" t="str">
-        <v>LkZl4HcVVB8</v>
+        <v>qroO2GMNLVE</v>
       </c>
       <c r="AI186" t="str">
-        <v>Jungle Animals in 4K UHD 🌿 | Amazing Wildlife Discovery | 60FPS Ultra HD Nature Documentary</v>
+        <v>Climbing Perch (Anabas testudineus) - The Walking Fish</v>
       </c>
       <c r="AJ186" t="str">
         <v>4K</v>
@@ -34185,7 +34185,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | wikidata | youtube</v>
       </c>
       <c r="AM186" t="str">
-        <v>2026-08-01T14:49:37.543Z</v>
+        <v>2026-08-01T16:52:45.518Z</v>
       </c>
       <c r="AN186">
         <v>0.99</v>
@@ -34343,19 +34343,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/7/7a/Mameshiba_hembra_dos_a%C3%B1os.jpg</v>
       </c>
       <c r="AE187" t="str">
-        <v>https://www.inaturalist.org/photos/245572394</v>
+        <v>https://commons.wikimedia.org/wiki/File:Mameshiba_hembra_dos_a%C3%B1os.jpg</v>
       </c>
       <c r="AF187" t="str">
         <v>CC0</v>
       </c>
       <c r="AG187" t="str">
-        <v>https://www.youtube.com/watch?v=-bWVoyw9OU8</v>
+        <v>https://www.youtube.com/watch?v=5i-fkyOfdNM</v>
       </c>
       <c r="AH187" t="str">
-        <v>-bWVoyw9OU8</v>
+        <v>5i-fkyOfdNM</v>
       </c>
       <c r="AI187" t="str">
-        <v>Animals of America 4K - Scenic Wildlife Film With Calming Music</v>
+        <v>Alabai (Canis lupus familiaris) – Ancient Guardian, Strength, and Protective Instincts</v>
       </c>
       <c r="AJ187" t="str">
         <v>4K</v>
@@ -34367,7 +34367,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM187" t="str">
-        <v>2026-08-01T15:16:40.311Z</v>
+        <v>2026-08-01T16:52:49.992Z</v>
       </c>
       <c r="AN187">
         <v>0.98</v>
@@ -34415,16 +34415,16 @@
         <v/>
       </c>
       <c r="BC187">
-        <v>1550</v>
+        <v>739</v>
       </c>
       <c r="BD187">
-        <v>1978</v>
+        <v>800</v>
       </c>
       <c r="BE187" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF187" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG187" t="str">
         <v>rights-free</v>
@@ -34525,19 +34525,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/4/40/Bulgarian_gray_cattle.jpg</v>
       </c>
       <c r="AE188" t="str">
-        <v>https://www.inaturalist.org/photos/342414953</v>
+        <v>https://commons.wikimedia.org/wiki/File:Bulgarian_gray_cattle.jpg</v>
       </c>
       <c r="AF188" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG188" t="str">
-        <v>https://www.youtube.com/watch?v=PI5gBfiWKjg</v>
+        <v>https://www.youtube.com/watch?v=M4Jut4utgS0</v>
       </c>
       <c r="AH188" t="str">
-        <v>PI5gBfiWKjg</v>
+        <v>M4Jut4utgS0</v>
       </c>
       <c r="AI188" t="str">
-        <v>The Hidden Wonders of Wildlife 4k | 10-Hour wildlife documentary #wildlife</v>
+        <v>The Wild Cattle of Cambodia (1957) - FULL DOCUMENTARY</v>
       </c>
       <c r="AJ188" t="str">
         <v>4K</v>
@@ -34549,7 +34549,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM188" t="str">
-        <v>2026-08-01T15:16:42.429Z</v>
+        <v>2026-08-01T16:52:53.953Z</v>
       </c>
       <c r="AN188">
         <v>0.99</v>
@@ -34597,16 +34597,16 @@
         <v/>
       </c>
       <c r="BC188">
-        <v>2048</v>
+        <v>2592</v>
       </c>
       <c r="BD188">
-        <v>1365</v>
+        <v>1944</v>
       </c>
       <c r="BE188" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF188" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG188" t="str">
         <v>rights-free</v>
@@ -34707,19 +34707,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/d/d9/Nine-banded_Armadillo_imported_from_iNaturalist_photo_209640017_on_15_March_2024.jpg</v>
       </c>
       <c r="AE189" t="str">
-        <v>https://www.inaturalist.org/photos/436655911</v>
+        <v>https://commons.wikimedia.org/wiki/File:Nine-banded_Armadillo_imported_from_iNaturalist_photo_209640017_on_15_March_2024.jpg</v>
       </c>
       <c r="AF189" t="str">
         <v>CC0</v>
       </c>
       <c r="AG189" t="str">
-        <v>https://www.youtube.com/watch?v=-JDY5DtM9d8</v>
+        <v>https://www.youtube.com/watch?v=1rTmjsjPiRA</v>
       </c>
       <c r="AH189" t="str">
-        <v>-JDY5DtM9d8</v>
+        <v>1rTmjsjPiRA</v>
       </c>
       <c r="AI189" t="str">
-        <v>Armadillo: Nocturnal Systems &amp; Subsurface Survival | 4K Cinematic Wildlife Documentary</v>
+        <v>Amazing Armadillo Looks for Love | 4K UHD | Mammals | BBC Earth</v>
       </c>
       <c r="AJ189" t="str">
         <v>4K</v>
@@ -34731,7 +34731,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM189" t="str">
-        <v>2026-08-01T15:16:44.507Z</v>
+        <v>2026-08-01T16:52:57.467Z</v>
       </c>
       <c r="AN189">
         <v>0.99</v>
@@ -34782,13 +34782,13 @@
         <v>2048</v>
       </c>
       <c r="BD189">
-        <v>1425</v>
+        <v>1536</v>
       </c>
       <c r="BE189" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF189" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG189" t="str">
         <v>rights-free</v>
@@ -34889,19 +34889,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/6/68/Cambridge_Natural_History_Mammalia_Fig_103.jpg</v>
       </c>
       <c r="AE190" t="str">
-        <v>https://www.inaturalist.org/photos/661540917</v>
+        <v>https://commons.wikimedia.org/wiki/File:Cambridge_Natural_History_Mammalia_Fig_103.jpg</v>
       </c>
       <c r="AF190" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG190" t="str">
-        <v>https://www.youtube.com/watch?v=7ZhdXgRfxHI</v>
+        <v>https://www.youtube.com/watch?v=3lhZZagzUQM</v>
       </c>
       <c r="AH190" t="str">
-        <v>7ZhdXgRfxHI</v>
+        <v>3lhZZagzUQM</v>
       </c>
       <c r="AI190" t="str">
-        <v>Incredible 4K Nature Scenes Narrated By David Attenborough | BBC Earth</v>
+        <v>Brazilian 3 Banded Armadillo (4K)</v>
       </c>
       <c r="AJ190" t="str">
         <v>4K</v>
@@ -34913,7 +34913,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM190" t="str">
-        <v>2026-08-01T15:16:46.412Z</v>
+        <v>2026-08-01T16:53:00.573Z</v>
       </c>
       <c r="AN190">
         <v>0.99</v>
@@ -34961,16 +34961,16 @@
         <v/>
       </c>
       <c r="BC190">
-        <v>1362</v>
+        <v>786</v>
       </c>
       <c r="BD190">
-        <v>2048</v>
+        <v>567</v>
       </c>
       <c r="BE190" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF190" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG190" t="str">
         <v>rights-free</v>
@@ -35077,13 +35077,13 @@
         <v>CC0</v>
       </c>
       <c r="AG191" t="str">
-        <v>https://www.youtube.com/watch?v=W-O5KfQLgO8</v>
+        <v>https://www.youtube.com/watch?v=3fVYhm61Wv4</v>
       </c>
       <c r="AH191" t="str">
-        <v>W-O5KfQLgO8</v>
+        <v>3fVYhm61Wv4</v>
       </c>
       <c r="AI191" t="str">
-        <v>The Incredible Wildlife of Europe's Most Unique Valley | 4K</v>
+        <v>Sunda Colugo / Flying Lemur (Galeopterus variegatus) - Best of Singapore's Wildlife</v>
       </c>
       <c r="AJ191" t="str">
         <v>4K</v>
@@ -35095,7 +35095,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
       </c>
       <c r="AM191" t="str">
-        <v>2026-08-01T14:49:59.123Z</v>
+        <v>2026-08-01T16:53:04.014Z</v>
       </c>
       <c r="AN191">
         <v>0.99</v>
@@ -35253,19 +35253,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/2/22/Kangur.rudy.drs.jpg</v>
       </c>
       <c r="AE192" t="str">
-        <v>https://www.inaturalist.org/photos/439326092</v>
+        <v>https://commons.wikimedia.org/wiki/File:Kangur.rudy.drs.jpg</v>
       </c>
       <c r="AF192" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG192" t="str">
-        <v>https://www.youtube.com/watch?v=t-YFbude0Bs</v>
+        <v>https://www.youtube.com/watch?v=lN7RShkiZMM</v>
       </c>
       <c r="AH192" t="str">
-        <v>t-YFbude0Bs</v>
+        <v>lN7RShkiZMM</v>
       </c>
       <c r="AI192" t="str">
-        <v>Wildlife in 4K Ultra HD | Tigers, Lions, Kangaroos &amp; More</v>
+        <v>Red Kangaroo: The Brutal Fight for Survival | 4K Documentary</v>
       </c>
       <c r="AJ192" t="str">
         <v>4K</v>
@@ -35277,7 +35277,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM192" t="str">
-        <v>2026-08-01T15:16:50.392Z</v>
+        <v>2026-08-01T16:53:10.618Z</v>
       </c>
       <c r="AN192">
         <v>0.99</v>
@@ -35325,16 +35325,16 @@
         <v/>
       </c>
       <c r="BC192">
-        <v>2048</v>
+        <v>500</v>
       </c>
       <c r="BD192">
-        <v>1365</v>
+        <v>330</v>
       </c>
       <c r="BE192" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF192" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG192" t="str">
         <v>rights-free</v>
@@ -35432,7 +35432,7 @@
         <v/>
       </c>
       <c r="AD193" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/c/c4/%D0%91%D0%A1%D0%AD1._%D0%9A%D0%BE%D0%B0%D0%BB%D0%B0.jpg</v>
+        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/334142508/original.jpg</v>
       </c>
       <c r="AE193" t="str">
         <v>https://www.inaturalist.org/photos/334142508</v>
@@ -35441,13 +35441,13 @@
         <v>CC0</v>
       </c>
       <c r="AG193" t="str">
-        <v>https://www.youtube.com/watch?v=iKLcjQKvnNw</v>
+        <v>https://www.youtube.com/watch?v=SCv7n9lwpmk</v>
       </c>
       <c r="AH193" t="str">
-        <v>iKLcjQKvnNw</v>
+        <v>SCv7n9lwpmk</v>
       </c>
       <c r="AI193" t="str">
-        <v>KOALA 4K HDR: Stunning Australian Wildlife in Cinematic Ultra HD | 4K Nature TV Demo</v>
+        <v>The Sleepy Inhabitants of Australia: Koalas 🐨 | 4K Animal Documentary</v>
       </c>
       <c r="AJ193" t="str">
         <v>4K</v>
@@ -35459,7 +35459,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM193" t="str">
-        <v>2026-08-01T15:16:52.680Z</v>
+        <v>2026-08-01T16:53:15.346Z</v>
       </c>
       <c r="AN193">
         <v>0.99</v>
@@ -35623,13 +35623,13 @@
         <v>CC0</v>
       </c>
       <c r="AG194" t="str">
-        <v>https://www.youtube.com/watch?v=d12eMVRPIPs</v>
+        <v>https://www.youtube.com/watch?v=vODrcvHDKGk</v>
       </c>
       <c r="AH194" t="str">
-        <v>d12eMVRPIPs</v>
+        <v>vODrcvHDKGk</v>
       </c>
       <c r="AI194" t="str">
-        <v>WOMBAT 4K HDR: Stunning Australian Wildlife in Cinematic Ultra HD | 4K Nature TV Demo</v>
+        <v>Meet The Wombat: Australia’s Adorable Underground Bulldozer | 4K Animal Documentary</v>
       </c>
       <c r="AJ194" t="str">
         <v>4K</v>
@@ -35641,7 +35641,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
       </c>
       <c r="AM194" t="str">
-        <v>2026-08-01T14:50:14.033Z</v>
+        <v>2026-08-01T16:53:20.061Z</v>
       </c>
       <c r="AN194">
         <v>0.99</v>
@@ -35799,19 +35799,19 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/8/80/Rock_Hyrax_imported_from_iNaturalist_photo_235256101_on_28_February_2024.jpg</v>
       </c>
       <c r="AE195" t="str">
-        <v>https://www.inaturalist.org/photos/569897605</v>
+        <v>https://commons.wikimedia.org/wiki/File:Rock_Hyrax_imported_from_iNaturalist_photo_235256101_on_28_February_2024.jpg</v>
       </c>
       <c r="AF195" t="str">
         <v>CC0</v>
       </c>
       <c r="AG195" t="str">
-        <v>https://www.youtube.com/watch?v=8mJWIw5_np4</v>
+        <v>https://www.youtube.com/watch?v=6JKCbdHVWDs</v>
       </c>
       <c r="AH195" t="str">
-        <v>8mJWIw5_np4</v>
+        <v>6JKCbdHVWDs</v>
       </c>
       <c r="AI195" t="str">
-        <v>The Beavers Are Back 🦫 | Nature’s Master Builders Documentary | FULL DOCUMENTARY in 4K</v>
+        <v>The WILDlife of Filmmaking: Hyrax</v>
       </c>
       <c r="AJ195" t="str">
         <v>4K</v>
@@ -35823,7 +35823,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM195" t="str">
-        <v>2026-08-01T15:16:56.909Z</v>
+        <v>2026-08-01T16:53:23.803Z</v>
       </c>
       <c r="AN195">
         <v>0.99</v>
@@ -35871,16 +35871,16 @@
         <v/>
       </c>
       <c r="BC195">
+        <v>1536</v>
+      </c>
+      <c r="BD195">
         <v>2048</v>
-      </c>
-      <c r="BD195">
-        <v>1365</v>
       </c>
       <c r="BE195" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF195" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG195" t="str">
         <v>rights-free</v>
@@ -35987,13 +35987,13 @@
         <v>CC0</v>
       </c>
       <c r="AG196" t="str">
-        <v>https://www.youtube.com/watch?v=MDIknO9eqjc</v>
+        <v>https://www.youtube.com/watch?v=U5g7x8SVgE8</v>
       </c>
       <c r="AH196" t="str">
-        <v>MDIknO9eqjc</v>
+        <v>U5g7x8SVgE8</v>
       </c>
       <c r="AI196" t="str">
-        <v>Hidden Lives of Australia's Forests | 4K Nature Documentary</v>
+        <v>The Burrowers: Animals Underground - Baby Rabbits | Wildlife Documentary | Natural History</v>
       </c>
       <c r="AJ196" t="str">
         <v>4K</v>
@@ -36005,7 +36005,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
       </c>
       <c r="AM196" t="str">
-        <v>2026-08-01T14:50:21.265Z</v>
+        <v>2026-08-01T16:53:27.992Z</v>
       </c>
       <c r="AN196">
         <v>0.99</v>
@@ -36160,7 +36160,7 @@
         <v/>
       </c>
       <c r="AD197" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/8/8b/Zoo_Leipzig_-_Tou_Feng.jpg</v>
+        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/327361077/original.jpeg</v>
       </c>
       <c r="AE197" t="str">
         <v>https://www.inaturalist.org/photos/327361077</v>
@@ -36169,13 +36169,13 @@
         <v>CC0</v>
       </c>
       <c r="AG197" t="str">
-        <v>https://www.youtube.com/watch?v=axneDmVXBe8</v>
+        <v>https://www.youtube.com/watch?v=dRgsYRNBHBI</v>
       </c>
       <c r="AH197" t="str">
-        <v>axneDmVXBe8</v>
+        <v>dRgsYRNBHBI</v>
       </c>
       <c r="AI197" t="str">
-        <v>Pangolin: A Hidden Wonder | Documentary | 4K</v>
+        <v>Pangolin: The World's Most Trafficked Mammal | 4KUHD | China: Nature's Ancient Kingdom | BBC Earth</v>
       </c>
       <c r="AJ197" t="str">
         <v>4K</v>
@@ -36187,7 +36187,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM197" t="str">
-        <v>2026-08-01T15:17:03.549Z</v>
+        <v>2026-08-01T16:53:31.762Z</v>
       </c>
       <c r="AN197">
         <v>0.99</v>
@@ -36342,25 +36342,25 @@
         <v/>
       </c>
       <c r="AD198" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/d/d6/Max_Fritz_Mpungu_1878.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/1/10/SILVERBACK_GORILLA_01.jpg</v>
       </c>
       <c r="AE198" t="str">
-        <v>https://www.inaturalist.org/photos/447862993</v>
+        <v>https://commons.wikimedia.org/wiki/File:SILVERBACK_GORILLA_01.jpg</v>
       </c>
       <c r="AF198" t="str">
         <v>CC0</v>
       </c>
       <c r="AG198" t="str">
-        <v>https://www.youtube.com/watch?v=MpiHQUCT1Cc</v>
+        <v>https://www.youtube.com/watch?v=s2xhy5cssVQ</v>
       </c>
       <c r="AH198" t="str">
-        <v>MpiHQUCT1Cc</v>
+        <v>s2xhy5cssVQ</v>
       </c>
       <c r="AI198" t="str">
-        <v>Monkeys &amp; Primates 4K - Scenic Wildlife Film With Calming Music</v>
+        <v>Mountain Gorilla - Full Documentary HD</v>
       </c>
       <c r="AJ198" t="str">
-        <v>4K</v>
+        <v>HD</v>
       </c>
       <c r="AK198" t="str">
         <v>https://www.gbif.org/species/2436441 | https://en.wikipedia.org/wiki/Western_gorilla | https://vi.wikipedia.org/wiki/Kh%E1%BB%89_%C4%91%E1%BB%99t | https://www.inaturalist.org/photos/447862993 | https://www.youtube.com/watch?v=MpiHQUCT1Cc</v>
@@ -36369,7 +36369,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM198" t="str">
-        <v>2026-08-01T15:17:07.711Z</v>
+        <v>2026-08-01T16:53:35.942Z</v>
       </c>
       <c r="AN198">
         <v>0.99</v>
@@ -36417,16 +36417,16 @@
         <v/>
       </c>
       <c r="BC198">
-        <v>2048</v>
+        <v>3024</v>
       </c>
       <c r="BD198">
-        <v>1365</v>
+        <v>4032</v>
       </c>
       <c r="BE198" t="str">
-        <v>Full HD</v>
+        <v>4K</v>
       </c>
       <c r="BF198" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>http://creativecommons.org/publicdomain/zero/1.0/deed.en</v>
       </c>
       <c r="BG198" t="str">
         <v>rights-free</v>
@@ -36533,13 +36533,13 @@
         <v>CC0</v>
       </c>
       <c r="AG199" t="str">
-        <v>https://www.youtube.com/watch?v=MpiHQUCT1Cc</v>
+        <v>https://www.youtube.com/watch?v=fX8rWU38TNI</v>
       </c>
       <c r="AH199" t="str">
-        <v>MpiHQUCT1Cc</v>
+        <v>fX8rWU38TNI</v>
       </c>
       <c r="AI199" t="str">
-        <v>Monkeys &amp; Primates 4K - Scenic Wildlife Film With Calming Music</v>
+        <v>Macaques: Life Inside A Japanese Monkey Gang (4K Documentary)</v>
       </c>
       <c r="AJ199" t="str">
         <v>4K</v>
@@ -36551,7 +36551,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
       </c>
       <c r="AM199" t="str">
-        <v>2026-08-01T14:50:37.295Z</v>
+        <v>2026-08-01T16:53:40.082Z</v>
       </c>
       <c r="AN199">
         <v>0.99</v>
@@ -36706,22 +36706,22 @@
         <v/>
       </c>
       <c r="AD200" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/a/a8/Female_elephas_maximus_at_hamburg.JPG</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/f/f8/Three_children_riding_an_elephant_at_New_York_Zoological_Park_LCCN2011661006.tif</v>
       </c>
       <c r="AE200" t="str">
-        <v>https://www.inaturalist.org/photos/109596675</v>
+        <v>https://commons.wikimedia.org/wiki/File:Three_children_riding_an_elephant_at_New_York_Zoological_Park_LCCN2011661006.tif</v>
       </c>
       <c r="AF200" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG200" t="str">
-        <v>https://www.youtube.com/watch?v=BY9outjlQfo</v>
+        <v>https://www.youtube.com/watch?v=Ove5341HI0U</v>
       </c>
       <c r="AH200" t="str">
-        <v>BY9outjlQfo</v>
+        <v>Ove5341HI0U</v>
       </c>
       <c r="AI200" t="str">
-        <v>4K African Wildlife: ELEPHANTS Part #1 - A day in Africa with Giant Elephants - 10-bit Color</v>
+        <v>🐘 The Mighty Asian Elephant of Bandipur | 4K Wildlife Documentary 🌿🐾</v>
       </c>
       <c r="AJ200" t="str">
         <v>4K</v>
@@ -36733,7 +36733,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM200" t="str">
-        <v>2026-08-01T15:17:12.983Z</v>
+        <v>2026-08-01T16:53:44.100Z</v>
       </c>
       <c r="AN200">
         <v>0.99</v>
@@ -36781,16 +36781,16 @@
         <v/>
       </c>
       <c r="BC200">
-        <v>2048</v>
+        <v>1536</v>
       </c>
       <c r="BD200">
-        <v>1791</v>
+        <v>1233</v>
       </c>
       <c r="BE200" t="str">
-        <v>Full HD</v>
+        <v>HD</v>
       </c>
       <c r="BF200" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG200" t="str">
         <v>rights-free</v>
@@ -37070,22 +37070,22 @@
         <v/>
       </c>
       <c r="AD202" t="str">
-        <v>https://inaturalist-open-data.s3.amazonaws.com/photos/469688248/original.jpeg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/d/d4/AcanthochoerusGroteiSmit.jpg</v>
       </c>
       <c r="AE202" t="str">
-        <v>https://www.inaturalist.org/photos/469688248</v>
+        <v>https://commons.wikimedia.org/wiki/File:AcanthochoerusGroteiSmit.jpg</v>
       </c>
       <c r="AF202" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG202" t="str">
-        <v>https://www.youtube.com/watch?v=LgdknvGXVDc</v>
+        <v>https://www.youtube.com/watch?v=sILwIj49-T4</v>
       </c>
       <c r="AH202" t="str">
-        <v>LgdknvGXVDc</v>
+        <v>sILwIj49-T4</v>
       </c>
       <c r="AI202" t="str">
-        <v>Porcupine in Ultra-Realistic 4K | Rare Wildlife Behavior &amp; Cinematic Nature Documentary</v>
+        <v>My Homework is Stuck to the Porcupine's Spikes! 🦔 | 15 Min | Leo the WIldlife Ranger | #backtoschool</v>
       </c>
       <c r="AJ202" t="str">
         <v>4K</v>
@@ -37094,10 +37094,10 @@
         <v>https://www.gbif.org/species/5219890 | https://en.wikipedia.org/wiki/Malayan_porcupine | https://vi.wikipedia.org/wiki/Nh%C3%ADm | https://www.inaturalist.org/photos/469688248 | https://www.youtube.com/watch?v=LgdknvGXVDc</v>
       </c>
       <c r="AL202" t="str">
-        <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube</v>
+        <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM202" t="str">
-        <v>2026-08-01T14:50:47.534Z</v>
+        <v>2026-08-01T16:53:54.256Z</v>
       </c>
       <c r="AN202">
         <v>0.99</v>
@@ -37145,16 +37145,16 @@
         <v/>
       </c>
       <c r="BC202">
-        <v>2048</v>
+        <v>1757</v>
       </c>
       <c r="BD202">
-        <v>1536</v>
+        <v>2188</v>
       </c>
       <c r="BE202" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF202" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG202" t="str">
         <v>rights-free</v>
@@ -37437,10 +37437,10 @@
         <v>https://upload.wikimedia.org/wikipedia/commons/0/0e/Anim1133_-_Flickr_-_NOAA_Photo_Library.jpg</v>
       </c>
       <c r="AE204" t="str">
-        <v>https://www.inaturalist.org/photos/282690764</v>
+        <v>https://commons.wikimedia.org/wiki/File:Anim1133_-_Flickr_-_NOAA_Photo_Library.jpg</v>
       </c>
       <c r="AF204" t="str">
-        <v>CC0</v>
+        <v>Public Domain</v>
       </c>
       <c r="AG204" t="str">
         <v>https://www.youtube.com/watch?v=ZV-KTMEdy3Q</v>
@@ -37461,7 +37461,7 @@
         <v>gbif | inaturalist | wikipedia-en | wikipedia-vi | youtube | wikimedia</v>
       </c>
       <c r="AM204" t="str">
-        <v>2026-08-01T15:17:22.687Z</v>
+        <v>2026-08-01T16:54:02.829Z</v>
       </c>
       <c r="AN204">
         <v>0.99</v>
@@ -37509,16 +37509,16 @@
         <v/>
       </c>
       <c r="BC204">
-        <v>2048</v>
+        <v>3600</v>
       </c>
       <c r="BD204">
-        <v>1365</v>
+        <v>2418</v>
       </c>
       <c r="BE204" t="str">
         <v>Full HD</v>
       </c>
       <c r="BF204" t="str">
-        <v>https://creativecommons.org/publicdomain/zero/1.0/</v>
+        <v>https://creativecommons.org/publicdomain/mark/1.0/</v>
       </c>
       <c r="BG204" t="str">
         <v>rights-free</v>
